--- a/research/traditional_assets/database/data/bulgaria/bulgaria_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_electrical_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bul_monb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05599999999999999</v>
+        <v>0.0512</v>
+      </c>
+      <c r="E2">
+        <v>-0.201</v>
       </c>
       <c r="G2">
-        <v>0.08280020181634713</v>
+        <v>0.08576960309777347</v>
       </c>
       <c r="H2">
-        <v>0.08022199798183653</v>
+        <v>0.0856727976766699</v>
       </c>
       <c r="I2">
-        <v>-0.004031281533804239</v>
+        <v>0.03591481122942885</v>
       </c>
       <c r="J2">
-        <v>-0.004031281533804239</v>
+        <v>0.02804696188567955</v>
       </c>
       <c r="K2">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="L2">
-        <v>-0.009182643794147327</v>
+        <v>0.01176185866408519</v>
       </c>
       <c r="M2">
-        <v>2.77</v>
+        <v>2.197</v>
       </c>
       <c r="N2">
-        <v>0.02815040650406504</v>
+        <v>0.02615476190476191</v>
       </c>
       <c r="O2">
-        <v>-1.521978021978022</v>
+        <v>0.9041152263374486</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>0.02764227642276423</v>
+        <v>0.02571428571428572</v>
       </c>
       <c r="R2">
-        <v>-1.494505494505495</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="S2">
-        <v>0.04999999999999982</v>
+        <v>0.03699999999999992</v>
       </c>
       <c r="T2">
-        <v>0.01805054151624542</v>
+        <v>0.01684114701866177</v>
       </c>
       <c r="U2">
-        <v>5.11</v>
+        <v>3.53</v>
       </c>
       <c r="V2">
-        <v>0.05193089430894309</v>
+        <v>0.04202380952380952</v>
       </c>
       <c r="W2">
-        <v>-0.014</v>
+        <v>0.02294617563739377</v>
       </c>
       <c r="X2">
-        <v>0.2244198375401716</v>
+        <v>0.2065888356128231</v>
       </c>
       <c r="Y2">
-        <v>-0.2384198375401716</v>
+        <v>-0.1836426599754293</v>
       </c>
       <c r="Z2">
-        <v>0.8420641192315209</v>
+        <v>1.04175070592981</v>
       </c>
       <c r="AA2">
-        <v>-0.003394597534137161</v>
+        <v>0.02921794234359316</v>
       </c>
       <c r="AB2">
-        <v>0.1459005420342799</v>
+        <v>0.1251142919052554</v>
       </c>
       <c r="AC2">
-        <v>-0.149295139568417</v>
+        <v>-0.09589634956166228</v>
       </c>
       <c r="AD2">
-        <v>102.5</v>
+        <v>111.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>102.5</v>
+        <v>111.7</v>
       </c>
       <c r="AG2">
-        <v>97.39</v>
+        <v>108.17</v>
       </c>
       <c r="AH2">
-        <v>0.5102040816326531</v>
+        <v>0.5707715891670926</v>
       </c>
       <c r="AI2">
-        <v>0.4794200187090739</v>
+        <v>0.4787826832404629</v>
       </c>
       <c r="AJ2">
-        <v>0.4974207058583175</v>
+        <v>0.5628870271114117</v>
       </c>
       <c r="AK2">
-        <v>0.4666730557285926</v>
+        <v>0.4707751229490361</v>
       </c>
       <c r="AL2">
-        <v>3.56</v>
+        <v>6.15</v>
       </c>
       <c r="AM2">
-        <v>2.892</v>
+        <v>5.04</v>
       </c>
       <c r="AN2">
-        <v>11.87717265353418</v>
+        <v>6.137362637362638</v>
       </c>
       <c r="AO2">
-        <v>-0.224438202247191</v>
+        <v>1.20650406504065</v>
       </c>
       <c r="AP2">
-        <v>11.28505214368482</v>
+        <v>5.943406593406594</v>
       </c>
       <c r="AQ2">
-        <v>-0.2762793914246197</v>
+        <v>1.472222222222222</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05599999999999999</v>
+        <v>0.0512</v>
+      </c>
+      <c r="E3">
+        <v>-0.201</v>
       </c>
       <c r="G3">
-        <v>0.08280020181634713</v>
+        <v>0.08576960309777347</v>
       </c>
       <c r="H3">
-        <v>0.08022199798183653</v>
+        <v>0.0856727976766699</v>
       </c>
       <c r="I3">
-        <v>-0.004031281533804239</v>
+        <v>0.03591481122942885</v>
       </c>
       <c r="J3">
-        <v>-0.004031281533804239</v>
+        <v>0.02804696188567955</v>
       </c>
       <c r="K3">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="L3">
-        <v>-0.009182643794147327</v>
+        <v>0.01176185866408519</v>
       </c>
       <c r="M3">
-        <v>2.77</v>
+        <v>2.197</v>
       </c>
       <c r="N3">
-        <v>0.02815040650406504</v>
+        <v>0.02615476190476191</v>
       </c>
       <c r="O3">
-        <v>-1.521978021978022</v>
+        <v>0.9041152263374486</v>
       </c>
       <c r="P3">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>0.02764227642276423</v>
+        <v>0.02571428571428572</v>
       </c>
       <c r="R3">
-        <v>-1.494505494505495</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="S3">
-        <v>0.04999999999999982</v>
+        <v>0.03699999999999992</v>
       </c>
       <c r="T3">
-        <v>0.01805054151624542</v>
+        <v>0.01684114701866177</v>
       </c>
       <c r="U3">
-        <v>5.11</v>
+        <v>3.53</v>
       </c>
       <c r="V3">
-        <v>0.05193089430894309</v>
+        <v>0.04202380952380952</v>
       </c>
       <c r="W3">
-        <v>-0.014</v>
+        <v>0.02294617563739377</v>
       </c>
       <c r="X3">
-        <v>0.2244198375401716</v>
+        <v>0.2065888356128231</v>
       </c>
       <c r="Y3">
-        <v>-0.2384198375401716</v>
+        <v>-0.1836426599754293</v>
       </c>
       <c r="Z3">
-        <v>0.8420641192315209</v>
+        <v>1.04175070592981</v>
       </c>
       <c r="AA3">
-        <v>-0.003394597534137161</v>
+        <v>0.02921794234359316</v>
       </c>
       <c r="AB3">
-        <v>0.1459005420342799</v>
+        <v>0.1251142919052554</v>
       </c>
       <c r="AC3">
-        <v>-0.149295139568417</v>
+        <v>-0.09589634956166228</v>
       </c>
       <c r="AD3">
-        <v>102.5</v>
+        <v>111.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>102.5</v>
+        <v>111.7</v>
       </c>
       <c r="AG3">
-        <v>97.39</v>
+        <v>108.17</v>
       </c>
       <c r="AH3">
-        <v>0.5102040816326531</v>
+        <v>0.5707715891670926</v>
       </c>
       <c r="AI3">
-        <v>0.4794200187090739</v>
+        <v>0.4787826832404629</v>
       </c>
       <c r="AJ3">
-        <v>0.4974207058583175</v>
+        <v>0.5628870271114117</v>
       </c>
       <c r="AK3">
-        <v>0.4666730557285926</v>
+        <v>0.4707751229490361</v>
       </c>
       <c r="AL3">
-        <v>3.56</v>
+        <v>6.15</v>
       </c>
       <c r="AM3">
-        <v>2.892</v>
+        <v>5.04</v>
       </c>
       <c r="AN3">
-        <v>11.87717265353418</v>
+        <v>6.137362637362638</v>
       </c>
       <c r="AO3">
-        <v>-0.224438202247191</v>
+        <v>1.20650406504065</v>
       </c>
       <c r="AP3">
-        <v>11.28505214368482</v>
+        <v>5.943406593406594</v>
       </c>
       <c r="AQ3">
-        <v>-0.2762793914246197</v>
+        <v>1.472222222222222</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Monbat AD (BUL:MONB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUL:MONB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.894308943089431</v>
+      </c>
+      <c r="F2">
+        <v>10.3543898561272</v>
+      </c>
+      <c r="G2">
+        <v>6.13736263736264</v>
+      </c>
+      <c r="H2">
+        <v>2.04302197802198</v>
+      </c>
+      <c r="I2">
+        <v>0.570771589167092</v>
+      </c>
+      <c r="J2">
+        <v>0.19</v>
+      </c>
+      <c r="K2">
+        <v>84</v>
+      </c>
+      <c r="L2">
+        <v>186.369453077035</v>
+      </c>
+      <c r="M2">
+        <v>192.17</v>
+      </c>
+      <c r="N2">
+        <v>220.022453077035</v>
+      </c>
+      <c r="O2">
+        <v>111.7</v>
+      </c>
+      <c r="P2">
+        <v>37.183</v>
+      </c>
+      <c r="Q2">
+        <v>0.125114291905255</v>
+      </c>
+      <c r="R2">
+        <v>0.114187839938433</v>
+      </c>
+      <c r="S2">
+        <v>0.06384426798909</v>
+      </c>
+      <c r="T2">
+        <v>0.04122</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.206588835612823</v>
+      </c>
+      <c r="X2">
+        <v>0.131303753010411</v>
+      </c>
+      <c r="Y2">
+        <v>2.41849608276565</v>
+      </c>
+      <c r="Z2">
+        <v>1.33334237334503</v>
+      </c>
+      <c r="AA2">
+        <v>111.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.07093807554343334</v>
+      </c>
+      <c r="AC2">
+        <v>0.8943089430894309</v>
+      </c>
+      <c r="AD2">
+        <v>111.7</v>
+      </c>
+      <c r="AE2">
+        <v>6.15</v>
+      </c>
+      <c r="AF2">
+        <v>12.7</v>
+      </c>
+      <c r="AG2">
+        <v>18.2</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>84</v>
+      </c>
+      <c r="AK2">
+        <v>0.06937734437880483</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.1</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>14.16</v>
+      </c>
+      <c r="AR2">
+        <v>6.15</v>
+      </c>
+      <c r="AS2">
+        <v>111.7</v>
+      </c>
+      <c r="AT2">
+        <v>3.53</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1151792456049268</v>
+      </c>
+      <c r="C2">
+        <v>220.696552825484</v>
+      </c>
+      <c r="D2">
+        <v>217.166552825484</v>
+      </c>
+      <c r="E2">
+        <v>-111.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.53</v>
+      </c>
+      <c r="H2">
+        <v>84</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K2">
+        <v>12.7</v>
+      </c>
+      <c r="L2">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="O2">
+        <v>1.763333333333333</v>
+      </c>
+      <c r="P2">
+        <v>15.87</v>
+      </c>
+      <c r="Q2">
+        <v>28.57</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1151792456049268</v>
+      </c>
+      <c r="T2">
+        <v>1.100924895422504</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.1</v>
+      </c>
+      <c r="W2">
+        <v>0.04023</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1151171663593218</v>
+      </c>
+      <c r="C3">
+        <v>218.9162042449897</v>
+      </c>
+      <c r="D3">
+        <v>217.3432042449897</v>
+      </c>
+      <c r="E3">
+        <v>-109.743</v>
+      </c>
+      <c r="F3">
+        <v>1.957</v>
+      </c>
+      <c r="G3">
+        <v>3.53</v>
+      </c>
+      <c r="H3">
+        <v>84</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K3">
+        <v>12.7</v>
+      </c>
+      <c r="L3">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M3">
+        <v>0.08747790000000003</v>
+      </c>
+      <c r="N3">
+        <v>17.54585543333333</v>
+      </c>
+      <c r="O3">
+        <v>1.754585543333333</v>
+      </c>
+      <c r="P3">
+        <v>15.79126989</v>
+      </c>
+      <c r="Q3">
+        <v>28.49126989</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1158736023831534</v>
+      </c>
+      <c r="T3">
+        <v>1.110933303562709</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.1</v>
+      </c>
+      <c r="W3">
+        <v>0.04023</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>201.5747215391925</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1150550871137169</v>
+      </c>
+      <c r="C4">
+        <v>217.1361432882402</v>
+      </c>
+      <c r="D4">
+        <v>217.5201432882402</v>
+      </c>
+      <c r="E4">
+        <v>-107.786</v>
+      </c>
+      <c r="F4">
+        <v>3.914000000000001</v>
+      </c>
+      <c r="G4">
+        <v>3.53</v>
+      </c>
+      <c r="H4">
+        <v>84</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K4">
+        <v>12.7</v>
+      </c>
+      <c r="L4">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M4">
+        <v>0.1749558000000001</v>
+      </c>
+      <c r="N4">
+        <v>17.45837753333333</v>
+      </c>
+      <c r="O4">
+        <v>1.745837753333333</v>
+      </c>
+      <c r="P4">
+        <v>15.71253978</v>
+      </c>
+      <c r="Q4">
+        <v>28.41253978</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1165821297078744</v>
+      </c>
+      <c r="T4">
+        <v>1.121145964930265</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.1</v>
+      </c>
+      <c r="W4">
+        <v>0.04023</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>100.7873607695963</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.114993007868112</v>
+      </c>
+      <c r="C5">
+        <v>215.3563706582711</v>
+      </c>
+      <c r="D5">
+        <v>217.6973706582711</v>
+      </c>
+      <c r="E5">
+        <v>-105.829</v>
+      </c>
+      <c r="F5">
+        <v>5.871</v>
+      </c>
+      <c r="G5">
+        <v>3.53</v>
+      </c>
+      <c r="H5">
+        <v>84</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K5">
+        <v>12.7</v>
+      </c>
+      <c r="L5">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M5">
+        <v>0.2624337</v>
+      </c>
+      <c r="N5">
+        <v>17.37089963333333</v>
+      </c>
+      <c r="O5">
+        <v>1.737089963333333</v>
+      </c>
+      <c r="P5">
+        <v>15.63380967</v>
+      </c>
+      <c r="Q5">
+        <v>28.33380967</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1173052658434144</v>
+      </c>
+      <c r="T5">
+        <v>1.131569196635296</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.1</v>
+      </c>
+      <c r="W5">
+        <v>0.04023</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>67.19157384639752</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1149309286225071</v>
+      </c>
+      <c r="C6">
+        <v>213.576887060411</v>
+      </c>
+      <c r="D6">
+        <v>217.874887060411</v>
+      </c>
+      <c r="E6">
+        <v>-103.872</v>
+      </c>
+      <c r="F6">
+        <v>7.828000000000001</v>
+      </c>
+      <c r="G6">
+        <v>3.53</v>
+      </c>
+      <c r="H6">
+        <v>84</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K6">
+        <v>12.7</v>
+      </c>
+      <c r="L6">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M6">
+        <v>0.3499116000000001</v>
+      </c>
+      <c r="N6">
+        <v>17.28342173333333</v>
+      </c>
+      <c r="O6">
+        <v>1.728342173333334</v>
+      </c>
+      <c r="P6">
+        <v>15.55507956</v>
+      </c>
+      <c r="Q6">
+        <v>28.25507956</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1180434673151115</v>
+      </c>
+      <c r="T6">
+        <v>1.142209579000848</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.1</v>
+      </c>
+      <c r="W6">
+        <v>0.04023</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>50.39368038479813</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1148688493769021</v>
+      </c>
+      <c r="C7">
+        <v>211.7976932022913</v>
+      </c>
+      <c r="D7">
+        <v>218.0526932022913</v>
+      </c>
+      <c r="E7">
+        <v>-101.915</v>
+      </c>
+      <c r="F7">
+        <v>9.785000000000002</v>
+      </c>
+      <c r="G7">
+        <v>3.53</v>
+      </c>
+      <c r="H7">
+        <v>84</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K7">
+        <v>12.7</v>
+      </c>
+      <c r="L7">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M7">
+        <v>0.4373895000000001</v>
+      </c>
+      <c r="N7">
+        <v>17.19594383333333</v>
+      </c>
+      <c r="O7">
+        <v>1.719594383333333</v>
+      </c>
+      <c r="P7">
+        <v>15.47634945</v>
+      </c>
+      <c r="Q7">
+        <v>28.17634945</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1187972098704233</v>
+      </c>
+      <c r="T7">
+        <v>1.153073969416202</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.1</v>
+      </c>
+      <c r="W7">
+        <v>0.04023</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>40.3149443078385</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1148067701312972</v>
+      </c>
+      <c r="C8">
+        <v>210.0187897938546</v>
+      </c>
+      <c r="D8">
+        <v>218.2307897938545</v>
+      </c>
+      <c r="E8">
+        <v>-99.95800000000001</v>
+      </c>
+      <c r="F8">
+        <v>11.742</v>
+      </c>
+      <c r="G8">
+        <v>3.53</v>
+      </c>
+      <c r="H8">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K8">
+        <v>12.7</v>
+      </c>
+      <c r="L8">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M8">
+        <v>0.5248674000000001</v>
+      </c>
+      <c r="N8">
+        <v>17.10846593333333</v>
+      </c>
+      <c r="O8">
+        <v>1.710846593333333</v>
+      </c>
+      <c r="P8">
+        <v>15.39761934</v>
+      </c>
+      <c r="Q8">
+        <v>28.09761934</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.11956698950138</v>
+      </c>
+      <c r="T8">
+        <v>1.164169517074436</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.1</v>
+      </c>
+      <c r="W8">
+        <v>0.04023</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>33.59578692319875</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1147446908856923</v>
+      </c>
+      <c r="C9">
+        <v>208.2401775473653</v>
+      </c>
+      <c r="D9">
+        <v>218.4091775473653</v>
+      </c>
+      <c r="E9">
+        <v>-98.00100000000002</v>
+      </c>
+      <c r="F9">
+        <v>13.699</v>
+      </c>
+      <c r="G9">
+        <v>3.53</v>
+      </c>
+      <c r="H9">
+        <v>84</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K9">
+        <v>12.7</v>
+      </c>
+      <c r="L9">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M9">
+        <v>0.6123453000000001</v>
+      </c>
+      <c r="N9">
+        <v>17.02098803333333</v>
+      </c>
+      <c r="O9">
+        <v>1.702098803333333</v>
+      </c>
+      <c r="P9">
+        <v>15.31888923</v>
+      </c>
+      <c r="Q9">
+        <v>28.01888923</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1203533235330025</v>
+      </c>
+      <c r="T9">
+        <v>1.175503678660803</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.1</v>
+      </c>
+      <c r="W9">
+        <v>0.04023</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>28.79638879131322</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1146826116400874</v>
+      </c>
+      <c r="C10">
+        <v>206.4618571774187</v>
+      </c>
+      <c r="D10">
+        <v>218.5878571774187</v>
+      </c>
+      <c r="E10">
+        <v>-96.04400000000001</v>
+      </c>
+      <c r="F10">
+        <v>15.656</v>
+      </c>
+      <c r="G10">
+        <v>3.53</v>
+      </c>
+      <c r="H10">
+        <v>84</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K10">
+        <v>12.7</v>
+      </c>
+      <c r="L10">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M10">
+        <v>0.6998232000000002</v>
+      </c>
+      <c r="N10">
+        <v>16.93351013333333</v>
+      </c>
+      <c r="O10">
+        <v>1.693351013333333</v>
+      </c>
+      <c r="P10">
+        <v>15.24015912</v>
+      </c>
+      <c r="Q10">
+        <v>27.94015912</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1211567517827037</v>
+      </c>
+      <c r="T10">
+        <v>1.187084235064266</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.1</v>
+      </c>
+      <c r="W10">
+        <v>0.04023</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>25.19684019239906</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1146205323944824</v>
+      </c>
+      <c r="C11">
+        <v>204.68382940095</v>
+      </c>
+      <c r="D11">
+        <v>218.76682940095</v>
+      </c>
+      <c r="E11">
+        <v>-94.08700000000002</v>
+      </c>
+      <c r="F11">
+        <v>17.613</v>
+      </c>
+      <c r="G11">
+        <v>3.53</v>
+      </c>
+      <c r="H11">
+        <v>84</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K11">
+        <v>12.7</v>
+      </c>
+      <c r="L11">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M11">
+        <v>0.7873011000000001</v>
+      </c>
+      <c r="N11">
+        <v>16.84603223333333</v>
+      </c>
+      <c r="O11">
+        <v>1.684603223333333</v>
+      </c>
+      <c r="P11">
+        <v>15.16142901</v>
+      </c>
+      <c r="Q11">
+        <v>27.86142901</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1219778377961345</v>
+      </c>
+      <c r="T11">
+        <v>1.198919309190881</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.1</v>
+      </c>
+      <c r="W11">
+        <v>0.04023</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>22.3971912821325</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1145584531488775</v>
+      </c>
+      <c r="C12">
+        <v>202.9060949372447</v>
+      </c>
+      <c r="D12">
+        <v>218.9460949372447</v>
+      </c>
+      <c r="E12">
+        <v>-92.13000000000001</v>
+      </c>
+      <c r="F12">
+        <v>19.57</v>
+      </c>
+      <c r="G12">
+        <v>3.53</v>
+      </c>
+      <c r="H12">
+        <v>84</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K12">
+        <v>12.7</v>
+      </c>
+      <c r="L12">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M12">
+        <v>0.8747790000000002</v>
+      </c>
+      <c r="N12">
+        <v>16.75855433333333</v>
+      </c>
+      <c r="O12">
+        <v>1.675855433333333</v>
+      </c>
+      <c r="P12">
+        <v>15.0826989</v>
+      </c>
+      <c r="Q12">
+        <v>27.7826989</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1228171701654195</v>
+      </c>
+      <c r="T12">
+        <v>1.211017384964755</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.1</v>
+      </c>
+      <c r="W12">
+        <v>0.04023</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>20.15747215391925</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1144963739032726</v>
+      </c>
+      <c r="C13">
+        <v>201.1286545079478</v>
+      </c>
+      <c r="D13">
+        <v>219.1256545079478</v>
+      </c>
+      <c r="E13">
+        <v>-90.17300000000002</v>
+      </c>
+      <c r="F13">
+        <v>21.527</v>
+      </c>
+      <c r="G13">
+        <v>3.53</v>
+      </c>
+      <c r="H13">
+        <v>84</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K13">
+        <v>12.7</v>
+      </c>
+      <c r="L13">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M13">
+        <v>0.9622569000000001</v>
+      </c>
+      <c r="N13">
+        <v>16.67107643333333</v>
+      </c>
+      <c r="O13">
+        <v>1.667107643333333</v>
+      </c>
+      <c r="P13">
+        <v>15.00396879</v>
+      </c>
+      <c r="Q13">
+        <v>27.70396879</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1236753639362613</v>
+      </c>
+      <c r="T13">
+        <v>1.223387327609951</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.1</v>
+      </c>
+      <c r="W13">
+        <v>0.04023</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.32497468538114</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1144342946576677</v>
+      </c>
+      <c r="C14">
+        <v>199.3515088370733</v>
+      </c>
+      <c r="D14">
+        <v>219.3055088370733</v>
+      </c>
+      <c r="E14">
+        <v>-88.21600000000001</v>
+      </c>
+      <c r="F14">
+        <v>23.484</v>
+      </c>
+      <c r="G14">
+        <v>3.53</v>
+      </c>
+      <c r="H14">
+        <v>84</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K14">
+        <v>12.7</v>
+      </c>
+      <c r="L14">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M14">
+        <v>1.0497348</v>
+      </c>
+      <c r="N14">
+        <v>16.58359853333333</v>
+      </c>
+      <c r="O14">
+        <v>1.658359853333333</v>
+      </c>
+      <c r="P14">
+        <v>14.92523868</v>
+      </c>
+      <c r="Q14">
+        <v>27.62523868</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.124553062110986</v>
+      </c>
+      <c r="T14">
+        <v>1.236038405315266</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.1</v>
+      </c>
+      <c r="W14">
+        <v>0.04023</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>16.79789346159938</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1143722154120627</v>
+      </c>
+      <c r="C15">
+        <v>197.5746586510146</v>
+      </c>
+      <c r="D15">
+        <v>219.4856586510146</v>
+      </c>
+      <c r="E15">
+        <v>-86.25900000000001</v>
+      </c>
+      <c r="F15">
+        <v>25.441</v>
+      </c>
+      <c r="G15">
+        <v>3.53</v>
+      </c>
+      <c r="H15">
+        <v>84</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K15">
+        <v>12.7</v>
+      </c>
+      <c r="L15">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M15">
+        <v>1.1372127</v>
+      </c>
+      <c r="N15">
+        <v>16.49612063333333</v>
+      </c>
+      <c r="O15">
+        <v>1.649612063333334</v>
+      </c>
+      <c r="P15">
+        <v>14.84650857</v>
+      </c>
+      <c r="Q15">
+        <v>27.54650857</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1254509372552445</v>
+      </c>
+      <c r="T15">
+        <v>1.248980312393117</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.1</v>
+      </c>
+      <c r="W15">
+        <v>0.04023</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.50574781070712</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1143101361664578</v>
+      </c>
+      <c r="C16">
+        <v>195.7981046785534</v>
+      </c>
+      <c r="D16">
+        <v>219.6661046785534</v>
+      </c>
+      <c r="E16">
+        <v>-84.30200000000002</v>
+      </c>
+      <c r="F16">
+        <v>27.398</v>
+      </c>
+      <c r="G16">
+        <v>3.53</v>
+      </c>
+      <c r="H16">
+        <v>84</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K16">
+        <v>12.7</v>
+      </c>
+      <c r="L16">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M16">
+        <v>1.2246906</v>
+      </c>
+      <c r="N16">
+        <v>16.40864273333333</v>
+      </c>
+      <c r="O16">
+        <v>1.640864273333333</v>
+      </c>
+      <c r="P16">
+        <v>14.76777846</v>
+      </c>
+      <c r="Q16">
+        <v>27.46777846</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1263696932168114</v>
+      </c>
+      <c r="T16">
+        <v>1.262223194054173</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.1</v>
+      </c>
+      <c r="W16">
+        <v>0.04023</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.39819439565661</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1142480569208529</v>
+      </c>
+      <c r="C17">
+        <v>194.0218476508704</v>
+      </c>
+      <c r="D17">
+        <v>219.8468476508704</v>
+      </c>
+      <c r="E17">
+        <v>-82.34500000000001</v>
+      </c>
+      <c r="F17">
+        <v>29.355</v>
+      </c>
+      <c r="G17">
+        <v>3.53</v>
+      </c>
+      <c r="H17">
+        <v>84</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K17">
+        <v>12.7</v>
+      </c>
+      <c r="L17">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M17">
+        <v>1.3121685</v>
+      </c>
+      <c r="N17">
+        <v>16.32116483333333</v>
+      </c>
+      <c r="O17">
+        <v>1.632116483333333</v>
+      </c>
+      <c r="P17">
+        <v>14.68904835</v>
+      </c>
+      <c r="Q17">
+        <v>27.38904835</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1273100669657093</v>
+      </c>
+      <c r="T17">
+        <v>1.275777672930785</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.1</v>
+      </c>
+      <c r="W17">
+        <v>0.04023</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.4383147692795</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.114344377675248</v>
+      </c>
+      <c r="C18">
+        <v>191.7845380518141</v>
+      </c>
+      <c r="D18">
+        <v>219.5665380518141</v>
+      </c>
+      <c r="E18">
+        <v>-80.38800000000001</v>
+      </c>
+      <c r="F18">
+        <v>31.312</v>
+      </c>
+      <c r="G18">
+        <v>3.53</v>
+      </c>
+      <c r="H18">
+        <v>84</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K18">
+        <v>12.7</v>
+      </c>
+      <c r="L18">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M18">
+        <v>1.4340896</v>
+      </c>
+      <c r="N18">
+        <v>16.19924373333333</v>
+      </c>
+      <c r="O18">
+        <v>1.619924373333333</v>
+      </c>
+      <c r="P18">
+        <v>14.57931936</v>
+      </c>
+      <c r="Q18">
+        <v>27.27931936</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1282728305657714</v>
+      </c>
+      <c r="T18">
+        <v>1.289654877494934</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.1</v>
+      </c>
+      <c r="W18">
+        <v>0.04122</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>12.29583795415107</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.114292198429643</v>
+      </c>
+      <c r="C19">
+        <v>189.9792996451171</v>
+      </c>
+      <c r="D19">
+        <v>219.7182996451171</v>
+      </c>
+      <c r="E19">
+        <v>-78.43100000000001</v>
+      </c>
+      <c r="F19">
+        <v>33.26900000000001</v>
+      </c>
+      <c r="G19">
+        <v>3.53</v>
+      </c>
+      <c r="H19">
+        <v>84</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K19">
+        <v>12.7</v>
+      </c>
+      <c r="L19">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M19">
+        <v>1.5237202</v>
+      </c>
+      <c r="N19">
+        <v>16.10961313333333</v>
+      </c>
+      <c r="O19">
+        <v>1.610961313333333</v>
+      </c>
+      <c r="P19">
+        <v>14.49865182</v>
+      </c>
+      <c r="Q19">
+        <v>27.19865182</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1292587932887265</v>
+      </c>
+      <c r="T19">
+        <v>1.303866472530508</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.1</v>
+      </c>
+      <c r="W19">
+        <v>0.04122</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.57255336861278</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1142400191840381</v>
+      </c>
+      <c r="C20">
+        <v>188.1742711748845</v>
+      </c>
+      <c r="D20">
+        <v>219.8702711748845</v>
+      </c>
+      <c r="E20">
+        <v>-76.47400000000002</v>
+      </c>
+      <c r="F20">
+        <v>35.226</v>
+      </c>
+      <c r="G20">
+        <v>3.53</v>
+      </c>
+      <c r="H20">
+        <v>84</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K20">
+        <v>12.7</v>
+      </c>
+      <c r="L20">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M20">
+        <v>1.6133508</v>
+      </c>
+      <c r="N20">
+        <v>16.01998253333333</v>
+      </c>
+      <c r="O20">
+        <v>1.601998253333333</v>
+      </c>
+      <c r="P20">
+        <v>14.41798428</v>
+      </c>
+      <c r="Q20">
+        <v>27.11798428</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1302688038829733</v>
+      </c>
+      <c r="T20">
+        <v>1.318424691835243</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.1</v>
+      </c>
+      <c r="W20">
+        <v>0.04122</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.92963373702318</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1141878399384332</v>
+      </c>
+      <c r="C21">
+        <v>186.3694530770351</v>
+      </c>
+      <c r="D21">
+        <v>220.0224530770351</v>
+      </c>
+      <c r="E21">
+        <v>-74.51700000000001</v>
+      </c>
+      <c r="F21">
+        <v>37.18300000000001</v>
+      </c>
+      <c r="G21">
+        <v>3.53</v>
+      </c>
+      <c r="H21">
+        <v>84</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K21">
+        <v>12.7</v>
+      </c>
+      <c r="L21">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M21">
+        <v>1.7029814</v>
+      </c>
+      <c r="N21">
+        <v>15.93035193333333</v>
+      </c>
+      <c r="O21">
+        <v>1.593035193333333</v>
+      </c>
+      <c r="P21">
+        <v>14.33731674</v>
+      </c>
+      <c r="Q21">
+        <v>27.03731674</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1313037530104113</v>
+      </c>
+      <c r="T21">
+        <v>1.333342373345033</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+      <c r="W21">
+        <v>0.04122</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>10.35438985612722</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1145316606928282</v>
+      </c>
+      <c r="C22">
+        <v>183.4135540022131</v>
+      </c>
+      <c r="D22">
+        <v>219.0235540022131</v>
+      </c>
+      <c r="E22">
+        <v>-72.56</v>
+      </c>
+      <c r="F22">
+        <v>39.14000000000001</v>
+      </c>
+      <c r="G22">
+        <v>3.53</v>
+      </c>
+      <c r="H22">
+        <v>84</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K22">
+        <v>12.7</v>
+      </c>
+      <c r="L22">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M22">
+        <v>1.87872</v>
+      </c>
+      <c r="N22">
+        <v>15.75461333333333</v>
+      </c>
+      <c r="O22">
+        <v>1.575461333333333</v>
+      </c>
+      <c r="P22">
+        <v>14.179152</v>
+      </c>
+      <c r="Q22">
+        <v>26.879152</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1323645758660353</v>
+      </c>
+      <c r="T22">
+        <v>1.348632996892568</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.1</v>
+      </c>
+      <c r="W22">
+        <v>0.0432</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>9.385822971668651</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1144992814472233</v>
+      </c>
+      <c r="C23">
+        <v>181.5502380810143</v>
+      </c>
+      <c r="D23">
+        <v>219.1172380810143</v>
+      </c>
+      <c r="E23">
+        <v>-70.60300000000001</v>
+      </c>
+      <c r="F23">
+        <v>41.097</v>
+      </c>
+      <c r="G23">
+        <v>3.53</v>
+      </c>
+      <c r="H23">
+        <v>84</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K23">
+        <v>12.7</v>
+      </c>
+      <c r="L23">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M23">
+        <v>1.972656</v>
+      </c>
+      <c r="N23">
+        <v>15.66067733333333</v>
+      </c>
+      <c r="O23">
+        <v>1.566067733333333</v>
+      </c>
+      <c r="P23">
+        <v>14.0946096</v>
+      </c>
+      <c r="Q23">
+        <v>26.7946096</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1334522549964852</v>
+      </c>
+      <c r="T23">
+        <v>1.364310724833711</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+      <c r="W23">
+        <v>0.0432</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.938879020636811</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1144669022016184</v>
+      </c>
+      <c r="C24">
+        <v>179.6870023380629</v>
+      </c>
+      <c r="D24">
+        <v>219.2110023380629</v>
+      </c>
+      <c r="E24">
+        <v>-68.64600000000002</v>
+      </c>
+      <c r="F24">
+        <v>43.054</v>
+      </c>
+      <c r="G24">
+        <v>3.53</v>
+      </c>
+      <c r="H24">
+        <v>84</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K24">
+        <v>12.7</v>
+      </c>
+      <c r="L24">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M24">
+        <v>2.066592</v>
+      </c>
+      <c r="N24">
+        <v>15.56674133333333</v>
+      </c>
+      <c r="O24">
+        <v>1.556674133333333</v>
+      </c>
+      <c r="P24">
+        <v>14.0100672</v>
+      </c>
+      <c r="Q24">
+        <v>26.7100672</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1345678233354082</v>
+      </c>
+      <c r="T24">
+        <v>1.380390445798986</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+      <c r="W24">
+        <v>0.0432</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.532566337880594</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1144345229560135</v>
+      </c>
+      <c r="C25">
+        <v>177.823846876332</v>
+      </c>
+      <c r="D25">
+        <v>219.304846876332</v>
+      </c>
+      <c r="E25">
+        <v>-66.68900000000002</v>
+      </c>
+      <c r="F25">
+        <v>45.011</v>
+      </c>
+      <c r="G25">
+        <v>3.53</v>
+      </c>
+      <c r="H25">
+        <v>84</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K25">
+        <v>12.7</v>
+      </c>
+      <c r="L25">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M25">
+        <v>2.160528</v>
+      </c>
+      <c r="N25">
+        <v>15.47280533333333</v>
+      </c>
+      <c r="O25">
+        <v>1.547280533333333</v>
+      </c>
+      <c r="P25">
+        <v>13.9255248</v>
+      </c>
+      <c r="Q25">
+        <v>26.6255248</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1357123674753422</v>
+      </c>
+      <c r="T25">
+        <v>1.396887821854269</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+      <c r="W25">
+        <v>0.0432</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.16158519275535</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1144021437104085</v>
+      </c>
+      <c r="C26">
+        <v>175.9607717989712</v>
+      </c>
+      <c r="D26">
+        <v>219.3987717989712</v>
+      </c>
+      <c r="E26">
+        <v>-64.73200000000001</v>
+      </c>
+      <c r="F26">
+        <v>46.968</v>
+      </c>
+      <c r="G26">
+        <v>3.53</v>
+      </c>
+      <c r="H26">
+        <v>84</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K26">
+        <v>12.7</v>
+      </c>
+      <c r="L26">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M26">
+        <v>2.254464</v>
+      </c>
+      <c r="N26">
+        <v>15.37886933333333</v>
+      </c>
+      <c r="O26">
+        <v>1.537886933333333</v>
+      </c>
+      <c r="P26">
+        <v>13.8409824</v>
+      </c>
+      <c r="Q26">
+        <v>26.5409824</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.136887031197906</v>
+      </c>
+      <c r="T26">
+        <v>1.41381933938469</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+      <c r="W26">
+        <v>0.0432</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.821519143057211</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1147072644648036</v>
+      </c>
+      <c r="C27">
+        <v>173.1218651825669</v>
+      </c>
+      <c r="D27">
+        <v>218.5168651825669</v>
+      </c>
+      <c r="E27">
+        <v>-62.77500000000001</v>
+      </c>
+      <c r="F27">
+        <v>48.925</v>
+      </c>
+      <c r="G27">
+        <v>3.53</v>
+      </c>
+      <c r="H27">
+        <v>84</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K27">
+        <v>12.7</v>
+      </c>
+      <c r="L27">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M27">
+        <v>2.4217875</v>
+      </c>
+      <c r="N27">
+        <v>15.21154583333333</v>
+      </c>
+      <c r="O27">
+        <v>1.521154583333333</v>
+      </c>
+      <c r="P27">
+        <v>13.69039125</v>
+      </c>
+      <c r="Q27">
+        <v>26.39039125</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1380930192864048</v>
+      </c>
+      <c r="T27">
+        <v>1.431202364049256</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.1</v>
+      </c>
+      <c r="W27">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>7.281123274991439</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1146883852191987</v>
+      </c>
+      <c r="C28">
+        <v>171.2192270398483</v>
+      </c>
+      <c r="D28">
+        <v>218.5712270398483</v>
+      </c>
+      <c r="E28">
+        <v>-60.81800000000001</v>
+      </c>
+      <c r="F28">
+        <v>50.88200000000001</v>
+      </c>
+      <c r="G28">
+        <v>3.53</v>
+      </c>
+      <c r="H28">
+        <v>84</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K28">
+        <v>12.7</v>
+      </c>
+      <c r="L28">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M28">
+        <v>2.518659</v>
+      </c>
+      <c r="N28">
+        <v>15.11467433333333</v>
+      </c>
+      <c r="O28">
+        <v>1.511467433333333</v>
+      </c>
+      <c r="P28">
+        <v>13.6032069</v>
+      </c>
+      <c r="Q28">
+        <v>26.3032069</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1393316016475658</v>
+      </c>
+      <c r="T28">
+        <v>1.449055200191242</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.1</v>
+      </c>
+      <c r="W28">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>7.001080072107153</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1146695059735938</v>
+      </c>
+      <c r="C29">
+        <v>169.3166159517636</v>
+      </c>
+      <c r="D29">
+        <v>218.6256159517636</v>
+      </c>
+      <c r="E29">
+        <v>-58.86100000000001</v>
+      </c>
+      <c r="F29">
+        <v>52.83900000000001</v>
+      </c>
+      <c r="G29">
+        <v>3.53</v>
+      </c>
+      <c r="H29">
+        <v>84</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K29">
+        <v>12.7</v>
+      </c>
+      <c r="L29">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M29">
+        <v>2.6155305</v>
+      </c>
+      <c r="N29">
+        <v>15.01780283333333</v>
+      </c>
+      <c r="O29">
+        <v>1.501780283333333</v>
+      </c>
+      <c r="P29">
+        <v>13.51602255</v>
+      </c>
+      <c r="Q29">
+        <v>26.21602255</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1406041177720463</v>
+      </c>
+      <c r="T29">
+        <v>1.46739715513164</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.1</v>
+      </c>
+      <c r="W29">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.741780810177259</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1146506267279888</v>
+      </c>
+      <c r="C30">
+        <v>167.4140319385145</v>
+      </c>
+      <c r="D30">
+        <v>218.6800319385146</v>
+      </c>
+      <c r="E30">
+        <v>-56.90400000000001</v>
+      </c>
+      <c r="F30">
+        <v>54.79600000000001</v>
+      </c>
+      <c r="G30">
+        <v>3.53</v>
+      </c>
+      <c r="H30">
+        <v>84</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K30">
+        <v>12.7</v>
+      </c>
+      <c r="L30">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M30">
+        <v>2.712402</v>
+      </c>
+      <c r="N30">
+        <v>14.92093133333333</v>
+      </c>
+      <c r="O30">
+        <v>1.492093133333333</v>
+      </c>
+      <c r="P30">
+        <v>13.4288382</v>
+      </c>
+      <c r="Q30">
+        <v>26.1288382</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1419119815666512</v>
+      </c>
+      <c r="T30">
+        <v>1.486248608820381</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.1</v>
+      </c>
+      <c r="W30">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.501002924099499</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1146317474823839</v>
+      </c>
+      <c r="C31">
+        <v>165.511475020323</v>
+      </c>
+      <c r="D31">
+        <v>218.734475020323</v>
+      </c>
+      <c r="E31">
+        <v>-54.94700000000002</v>
+      </c>
+      <c r="F31">
+        <v>56.753</v>
+      </c>
+      <c r="G31">
+        <v>3.53</v>
+      </c>
+      <c r="H31">
+        <v>84</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K31">
+        <v>12.7</v>
+      </c>
+      <c r="L31">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M31">
+        <v>2.8092735</v>
+      </c>
+      <c r="N31">
+        <v>14.82405983333333</v>
+      </c>
+      <c r="O31">
+        <v>1.482405983333333</v>
+      </c>
+      <c r="P31">
+        <v>13.34165385</v>
+      </c>
+      <c r="Q31">
+        <v>26.04165385</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1432566865949069</v>
+      </c>
+      <c r="T31">
+        <v>1.505631089373594</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.1</v>
+      </c>
+      <c r="W31">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.276830409475379</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.114990868236779</v>
+      </c>
+      <c r="C32">
+        <v>162.5234841483278</v>
+      </c>
+      <c r="D32">
+        <v>217.7034841483278</v>
+      </c>
+      <c r="E32">
+        <v>-52.99000000000002</v>
+      </c>
+      <c r="F32">
+        <v>58.71</v>
+      </c>
+      <c r="G32">
+        <v>3.53</v>
+      </c>
+      <c r="H32">
+        <v>84</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K32">
+        <v>12.7</v>
+      </c>
+      <c r="L32">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M32">
+        <v>2.988339</v>
+      </c>
+      <c r="N32">
+        <v>14.64499433333333</v>
+      </c>
+      <c r="O32">
+        <v>1.464499433333333</v>
+      </c>
+      <c r="P32">
+        <v>13.1804949</v>
+      </c>
+      <c r="Q32">
+        <v>25.8804949</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1446398117668271</v>
+      </c>
+      <c r="T32">
+        <v>1.52556735508547</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.1</v>
+      </c>
+      <c r="W32">
+        <v>0.04581</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.900713852522532</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1149845889911741</v>
+      </c>
+      <c r="C33">
+        <v>160.5844275889123</v>
+      </c>
+      <c r="D33">
+        <v>217.7214275889123</v>
+      </c>
+      <c r="E33">
+        <v>-51.03300000000002</v>
+      </c>
+      <c r="F33">
+        <v>60.667</v>
+      </c>
+      <c r="G33">
+        <v>3.53</v>
+      </c>
+      <c r="H33">
+        <v>84</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K33">
+        <v>12.7</v>
+      </c>
+      <c r="L33">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M33">
+        <v>3.0879503</v>
+      </c>
+      <c r="N33">
+        <v>14.54538303333333</v>
+      </c>
+      <c r="O33">
+        <v>1.454538303333333</v>
+      </c>
+      <c r="P33">
+        <v>13.09084473</v>
+      </c>
+      <c r="Q33">
+        <v>25.79084473</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1460630275234407</v>
+      </c>
+      <c r="T33">
+        <v>1.546081483571604</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.1</v>
+      </c>
+      <c r="W33">
+        <v>0.04581</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.710368244376644</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1149783097455691</v>
+      </c>
+      <c r="C34">
+        <v>158.6453739875899</v>
+      </c>
+      <c r="D34">
+        <v>217.73937398759</v>
+      </c>
+      <c r="E34">
+        <v>-49.07600000000001</v>
+      </c>
+      <c r="F34">
+        <v>62.62400000000001</v>
+      </c>
+      <c r="G34">
+        <v>3.53</v>
+      </c>
+      <c r="H34">
+        <v>84</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K34">
+        <v>12.7</v>
+      </c>
+      <c r="L34">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M34">
+        <v>3.1875616</v>
+      </c>
+      <c r="N34">
+        <v>14.44577173333333</v>
+      </c>
+      <c r="O34">
+        <v>1.444577173333333</v>
+      </c>
+      <c r="P34">
+        <v>13.00119456</v>
+      </c>
+      <c r="Q34">
+        <v>25.70119456</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1475281025670134</v>
+      </c>
+      <c r="T34">
+        <v>1.567198968777918</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.1</v>
+      </c>
+      <c r="W34">
+        <v>0.04581</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.531919236739873</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1149720304999642</v>
+      </c>
+      <c r="C35">
+        <v>156.7063233450925</v>
+      </c>
+      <c r="D35">
+        <v>217.7573233450925</v>
+      </c>
+      <c r="E35">
+        <v>-47.11900000000001</v>
+      </c>
+      <c r="F35">
+        <v>64.581</v>
+      </c>
+      <c r="G35">
+        <v>3.53</v>
+      </c>
+      <c r="H35">
+        <v>84</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K35">
+        <v>12.7</v>
+      </c>
+      <c r="L35">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M35">
+        <v>3.2871729</v>
+      </c>
+      <c r="N35">
+        <v>14.34616043333333</v>
+      </c>
+      <c r="O35">
+        <v>1.434616043333333</v>
+      </c>
+      <c r="P35">
+        <v>12.91154439</v>
+      </c>
+      <c r="Q35">
+        <v>25.61154439</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1490369111939764</v>
+      </c>
+      <c r="T35">
+        <v>1.588946826676958</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.1</v>
+      </c>
+      <c r="W35">
+        <v>0.04581</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.364285320475029</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1149657512543593</v>
+      </c>
+      <c r="C36">
+        <v>154.7672756621514</v>
+      </c>
+      <c r="D36">
+        <v>217.7752756621514</v>
+      </c>
+      <c r="E36">
+        <v>-45.16200000000001</v>
+      </c>
+      <c r="F36">
+        <v>66.53800000000001</v>
+      </c>
+      <c r="G36">
+        <v>3.53</v>
+      </c>
+      <c r="H36">
+        <v>84</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K36">
+        <v>12.7</v>
+      </c>
+      <c r="L36">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M36">
+        <v>3.386784200000001</v>
+      </c>
+      <c r="N36">
+        <v>14.24654913333333</v>
+      </c>
+      <c r="O36">
+        <v>1.424654913333333</v>
+      </c>
+      <c r="P36">
+        <v>12.82189422</v>
+      </c>
+      <c r="Q36">
+        <v>25.52189422</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1505914412944838</v>
+      </c>
+      <c r="T36">
+        <v>1.611353710572939</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.1</v>
+      </c>
+      <c r="W36">
+        <v>0.04581</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.206512222813998</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1149594720087543</v>
+      </c>
+      <c r="C37">
+        <v>152.828230939499</v>
+      </c>
+      <c r="D37">
+        <v>217.793230939499</v>
+      </c>
+      <c r="E37">
+        <v>-43.205</v>
+      </c>
+      <c r="F37">
+        <v>68.49500000000002</v>
+      </c>
+      <c r="G37">
+        <v>3.53</v>
+      </c>
+      <c r="H37">
+        <v>84</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K37">
+        <v>12.7</v>
+      </c>
+      <c r="L37">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M37">
+        <v>3.486395500000001</v>
+      </c>
+      <c r="N37">
+        <v>14.14693783333333</v>
+      </c>
+      <c r="O37">
+        <v>1.414693783333333</v>
+      </c>
+      <c r="P37">
+        <v>12.73224405</v>
+      </c>
+      <c r="Q37">
+        <v>25.43224405</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1521938030903913</v>
+      </c>
+      <c r="T37">
+        <v>1.634450037050333</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.1</v>
+      </c>
+      <c r="W37">
+        <v>0.04581</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.057754730733598</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1149531927631494</v>
+      </c>
+      <c r="C38">
+        <v>150.8891891778674</v>
+      </c>
+      <c r="D38">
+        <v>217.8111891778674</v>
+      </c>
+      <c r="E38">
+        <v>-41.24800000000002</v>
+      </c>
+      <c r="F38">
+        <v>70.452</v>
+      </c>
+      <c r="G38">
+        <v>3.53</v>
+      </c>
+      <c r="H38">
+        <v>84</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K38">
+        <v>12.7</v>
+      </c>
+      <c r="L38">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M38">
+        <v>3.5860068</v>
+      </c>
+      <c r="N38">
+        <v>14.04732653333333</v>
+      </c>
+      <c r="O38">
+        <v>1.404732653333333</v>
+      </c>
+      <c r="P38">
+        <v>12.64259388</v>
+      </c>
+      <c r="Q38">
+        <v>25.34259388</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.153846238692421</v>
+      </c>
+      <c r="T38">
+        <v>1.658268123730147</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.1</v>
+      </c>
+      <c r="W38">
+        <v>0.04581</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.917261543768777</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1149469135175445</v>
+      </c>
+      <c r="C39">
+        <v>148.9501503779893</v>
+      </c>
+      <c r="D39">
+        <v>217.8291503779893</v>
+      </c>
+      <c r="E39">
+        <v>-39.29100000000001</v>
+      </c>
+      <c r="F39">
+        <v>72.40900000000001</v>
+      </c>
+      <c r="G39">
+        <v>3.53</v>
+      </c>
+      <c r="H39">
+        <v>84</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K39">
+        <v>12.7</v>
+      </c>
+      <c r="L39">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M39">
+        <v>3.685618100000001</v>
+      </c>
+      <c r="N39">
+        <v>13.94771523333333</v>
+      </c>
+      <c r="O39">
+        <v>1.394771523333333</v>
+      </c>
+      <c r="P39">
+        <v>12.55294371</v>
+      </c>
+      <c r="Q39">
+        <v>25.25294371</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1555511325675309</v>
+      </c>
+      <c r="T39">
+        <v>1.682842340145828</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.1</v>
+      </c>
+      <c r="W39">
+        <v>0.04581</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.784362583126377</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1149406342719396</v>
+      </c>
+      <c r="C40">
+        <v>147.0111145405972</v>
+      </c>
+      <c r="D40">
+        <v>217.8471145405973</v>
+      </c>
+      <c r="E40">
+        <v>-37.334</v>
+      </c>
+      <c r="F40">
+        <v>74.36600000000001</v>
+      </c>
+      <c r="G40">
+        <v>3.53</v>
+      </c>
+      <c r="H40">
+        <v>84</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K40">
+        <v>12.7</v>
+      </c>
+      <c r="L40">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M40">
+        <v>3.785229400000001</v>
+      </c>
+      <c r="N40">
+        <v>13.84810393333333</v>
+      </c>
+      <c r="O40">
+        <v>1.384810393333333</v>
+      </c>
+      <c r="P40">
+        <v>12.46329354</v>
+      </c>
+      <c r="Q40">
+        <v>25.16329354</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1573110230192574</v>
+      </c>
+      <c r="T40">
+        <v>1.70820927322008</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.1</v>
+      </c>
+      <c r="W40">
+        <v>0.04581</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.658458304623052</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1149343550263346</v>
+      </c>
+      <c r="C41">
+        <v>145.0720816664244</v>
+      </c>
+      <c r="D41">
+        <v>217.8650816664244</v>
+      </c>
+      <c r="E41">
+        <v>-35.37700000000001</v>
+      </c>
+      <c r="F41">
+        <v>76.32300000000001</v>
+      </c>
+      <c r="G41">
+        <v>3.53</v>
+      </c>
+      <c r="H41">
+        <v>84</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K41">
+        <v>12.7</v>
+      </c>
+      <c r="L41">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M41">
+        <v>3.8848407</v>
+      </c>
+      <c r="N41">
+        <v>13.74849263333333</v>
+      </c>
+      <c r="O41">
+        <v>1.374849263333333</v>
+      </c>
+      <c r="P41">
+        <v>12.37364337</v>
+      </c>
+      <c r="Q41">
+        <v>25.07364337</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1591286147972699</v>
+      </c>
+      <c r="T41">
+        <v>1.734407909018077</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.1</v>
+      </c>
+      <c r="W41">
+        <v>0.04581</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.539010655786564</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1158640757807297</v>
+      </c>
+      <c r="C42">
+        <v>140.4867015031486</v>
+      </c>
+      <c r="D42">
+        <v>215.2367015031486</v>
+      </c>
+      <c r="E42">
+        <v>-33.42</v>
+      </c>
+      <c r="F42">
+        <v>78.28000000000002</v>
+      </c>
+      <c r="G42">
+        <v>3.53</v>
+      </c>
+      <c r="H42">
+        <v>84</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K42">
+        <v>12.7</v>
+      </c>
+      <c r="L42">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M42">
+        <v>4.18798</v>
+      </c>
+      <c r="N42">
+        <v>13.44535333333333</v>
+      </c>
+      <c r="O42">
+        <v>1.344535333333333</v>
+      </c>
+      <c r="P42">
+        <v>12.100818</v>
+      </c>
+      <c r="Q42">
+        <v>24.800818</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1610067929678828</v>
+      </c>
+      <c r="T42">
+        <v>1.761479832676007</v>
+      </c>
+      <c r="U42">
+        <v>0.0535</v>
+      </c>
+      <c r="V42">
+        <v>0.1</v>
+      </c>
+      <c r="W42">
+        <v>0.04815</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.210462641496218</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1158811965351248</v>
+      </c>
+      <c r="C43">
+        <v>138.4818945817607</v>
+      </c>
+      <c r="D43">
+        <v>215.1888945817607</v>
+      </c>
+      <c r="E43">
+        <v>-31.46300000000001</v>
+      </c>
+      <c r="F43">
+        <v>80.23700000000001</v>
+      </c>
+      <c r="G43">
+        <v>3.53</v>
+      </c>
+      <c r="H43">
+        <v>84</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K43">
+        <v>12.7</v>
+      </c>
+      <c r="L43">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M43">
+        <v>4.2926795</v>
+      </c>
+      <c r="N43">
+        <v>13.34065383333333</v>
+      </c>
+      <c r="O43">
+        <v>1.334065383333333</v>
+      </c>
+      <c r="P43">
+        <v>12.00658845</v>
+      </c>
+      <c r="Q43">
+        <v>24.70658845</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1629486381951268</v>
+      </c>
+      <c r="T43">
+        <v>1.789469448661325</v>
+      </c>
+      <c r="U43">
+        <v>0.0535</v>
+      </c>
+      <c r="V43">
+        <v>0.1</v>
+      </c>
+      <c r="W43">
+        <v>0.04815</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.107768430728018</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1158983172895199</v>
+      </c>
+      <c r="C44">
+        <v>136.4771088927573</v>
+      </c>
+      <c r="D44">
+        <v>215.1411088927573</v>
+      </c>
+      <c r="E44">
+        <v>-29.50600000000001</v>
+      </c>
+      <c r="F44">
+        <v>82.194</v>
+      </c>
+      <c r="G44">
+        <v>3.53</v>
+      </c>
+      <c r="H44">
+        <v>84</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K44">
+        <v>12.7</v>
+      </c>
+      <c r="L44">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M44">
+        <v>4.397379</v>
+      </c>
+      <c r="N44">
+        <v>13.23595433333333</v>
+      </c>
+      <c r="O44">
+        <v>1.323595433333333</v>
+      </c>
+      <c r="P44">
+        <v>11.9123589</v>
+      </c>
+      <c r="Q44">
+        <v>24.6123589</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1649574436026204</v>
+      </c>
+      <c r="T44">
+        <v>1.81842422381855</v>
+      </c>
+      <c r="U44">
+        <v>0.0535</v>
+      </c>
+      <c r="V44">
+        <v>0.1</v>
+      </c>
+      <c r="W44">
+        <v>0.04815</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.009964420472588</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1169603380439149</v>
+      </c>
+      <c r="C45">
+        <v>131.5968318383604</v>
+      </c>
+      <c r="D45">
+        <v>212.2178318383604</v>
+      </c>
+      <c r="E45">
+        <v>-27.54900000000001</v>
+      </c>
+      <c r="F45">
+        <v>84.15100000000001</v>
+      </c>
+      <c r="G45">
+        <v>3.53</v>
+      </c>
+      <c r="H45">
+        <v>84</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K45">
+        <v>12.7</v>
+      </c>
+      <c r="L45">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M45">
+        <v>4.729286200000001</v>
+      </c>
+      <c r="N45">
+        <v>12.90404713333333</v>
+      </c>
+      <c r="O45">
+        <v>1.290404713333333</v>
+      </c>
+      <c r="P45">
+        <v>11.61364242</v>
+      </c>
+      <c r="Q45">
+        <v>24.31364242</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1670367334103771</v>
+      </c>
+      <c r="T45">
+        <v>1.848394955998836</v>
+      </c>
+      <c r="U45">
+        <v>0.0562</v>
+      </c>
+      <c r="V45">
+        <v>0.1</v>
+      </c>
+      <c r="W45">
+        <v>0.05058</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.728540119507534</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.11700175879831</v>
+      </c>
+      <c r="C46">
+        <v>129.5274274266706</v>
+      </c>
+      <c r="D46">
+        <v>212.1054274266706</v>
+      </c>
+      <c r="E46">
+        <v>-25.59200000000001</v>
+      </c>
+      <c r="F46">
+        <v>86.108</v>
+      </c>
+      <c r="G46">
+        <v>3.53</v>
+      </c>
+      <c r="H46">
+        <v>84</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K46">
+        <v>12.7</v>
+      </c>
+      <c r="L46">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M46">
+        <v>4.839269600000001</v>
+      </c>
+      <c r="N46">
+        <v>12.79406373333333</v>
+      </c>
+      <c r="O46">
+        <v>1.279406373333333</v>
+      </c>
+      <c r="P46">
+        <v>11.51465736</v>
+      </c>
+      <c r="Q46">
+        <v>24.21465736</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1691902835684107</v>
+      </c>
+      <c r="T46">
+        <v>1.879436071471275</v>
+      </c>
+      <c r="U46">
+        <v>0.0562</v>
+      </c>
+      <c r="V46">
+        <v>0.1</v>
+      </c>
+      <c r="W46">
+        <v>0.05058</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.643800571336908</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1170431795527051</v>
+      </c>
+      <c r="C47">
+        <v>127.4581420253676</v>
+      </c>
+      <c r="D47">
+        <v>211.9931420253676</v>
+      </c>
+      <c r="E47">
+        <v>-23.63500000000001</v>
+      </c>
+      <c r="F47">
+        <v>88.06500000000001</v>
+      </c>
+      <c r="G47">
+        <v>3.53</v>
+      </c>
+      <c r="H47">
+        <v>84</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K47">
+        <v>12.7</v>
+      </c>
+      <c r="L47">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M47">
+        <v>4.949253000000001</v>
+      </c>
+      <c r="N47">
+        <v>12.68408033333333</v>
+      </c>
+      <c r="O47">
+        <v>1.268408033333333</v>
+      </c>
+      <c r="P47">
+        <v>11.4156723</v>
+      </c>
+      <c r="Q47">
+        <v>24.1156723</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1714221446412819</v>
+      </c>
+      <c r="T47">
+        <v>1.911605954779076</v>
+      </c>
+      <c r="U47">
+        <v>0.0562</v>
+      </c>
+      <c r="V47">
+        <v>0.1</v>
+      </c>
+      <c r="W47">
+        <v>0.05058</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.562827225307199</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1190304003071002</v>
+      </c>
+      <c r="C48">
+        <v>120.2502998257811</v>
+      </c>
+      <c r="D48">
+        <v>206.7422998257811</v>
+      </c>
+      <c r="E48">
+        <v>-21.67800000000001</v>
+      </c>
+      <c r="F48">
+        <v>90.02200000000001</v>
+      </c>
+      <c r="G48">
+        <v>3.53</v>
+      </c>
+      <c r="H48">
+        <v>84</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K48">
+        <v>12.7</v>
+      </c>
+      <c r="L48">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M48">
+        <v>5.482339800000001</v>
+      </c>
+      <c r="N48">
+        <v>12.15099353333333</v>
+      </c>
+      <c r="O48">
+        <v>1.215099353333333</v>
+      </c>
+      <c r="P48">
+        <v>10.93589418</v>
+      </c>
+      <c r="Q48">
+        <v>23.63589418</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1737366672353707</v>
+      </c>
+      <c r="T48">
+        <v>1.944967315246424</v>
+      </c>
+      <c r="U48">
+        <v>0.0609</v>
+      </c>
+      <c r="V48">
+        <v>0.1</v>
+      </c>
+      <c r="W48">
+        <v>0.05481</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.2163882533026</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1191141210614952</v>
+      </c>
+      <c r="C49">
+        <v>118.0777882684358</v>
+      </c>
+      <c r="D49">
+        <v>206.5267882684358</v>
+      </c>
+      <c r="E49">
+        <v>-19.721</v>
+      </c>
+      <c r="F49">
+        <v>91.97900000000001</v>
+      </c>
+      <c r="G49">
+        <v>3.53</v>
+      </c>
+      <c r="H49">
+        <v>84</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K49">
+        <v>12.7</v>
+      </c>
+      <c r="L49">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M49">
+        <v>5.601521100000001</v>
+      </c>
+      <c r="N49">
+        <v>12.03181223333333</v>
+      </c>
+      <c r="O49">
+        <v>1.203181223333333</v>
+      </c>
+      <c r="P49">
+        <v>10.82863101</v>
+      </c>
+      <c r="Q49">
+        <v>23.52863101</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.176138530304708</v>
+      </c>
+      <c r="T49">
+        <v>1.979587594976692</v>
+      </c>
+      <c r="U49">
+        <v>0.0609</v>
+      </c>
+      <c r="V49">
+        <v>0.1</v>
+      </c>
+      <c r="W49">
+        <v>0.05481</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.147954460679141</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1191978418158903</v>
+      </c>
+      <c r="C50">
+        <v>115.9057255487645</v>
+      </c>
+      <c r="D50">
+        <v>206.3117255487645</v>
+      </c>
+      <c r="E50">
+        <v>-17.76400000000001</v>
+      </c>
+      <c r="F50">
+        <v>93.93600000000001</v>
+      </c>
+      <c r="G50">
+        <v>3.53</v>
+      </c>
+      <c r="H50">
+        <v>84</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K50">
+        <v>12.7</v>
+      </c>
+      <c r="L50">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M50">
+        <v>5.7207024</v>
+      </c>
+      <c r="N50">
+        <v>11.91263093333333</v>
+      </c>
+      <c r="O50">
+        <v>1.191263093333333</v>
+      </c>
+      <c r="P50">
+        <v>10.72136784</v>
+      </c>
+      <c r="Q50">
+        <v>23.42136784</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1786327727228659</v>
+      </c>
+      <c r="T50">
+        <v>2.015539423927354</v>
+      </c>
+      <c r="U50">
+        <v>0.0609</v>
+      </c>
+      <c r="V50">
+        <v>0.1</v>
+      </c>
+      <c r="W50">
+        <v>0.05481</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.08237207608166</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1192815625702854</v>
+      </c>
+      <c r="C51">
+        <v>113.7341102660604</v>
+      </c>
+      <c r="D51">
+        <v>206.0971102660604</v>
+      </c>
+      <c r="E51">
+        <v>-15.80700000000002</v>
+      </c>
+      <c r="F51">
+        <v>95.893</v>
+      </c>
+      <c r="G51">
+        <v>3.53</v>
+      </c>
+      <c r="H51">
+        <v>84</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K51">
+        <v>12.7</v>
+      </c>
+      <c r="L51">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M51">
+        <v>5.839883700000001</v>
+      </c>
+      <c r="N51">
+        <v>11.79344963333333</v>
+      </c>
+      <c r="O51">
+        <v>1.179344963333333</v>
+      </c>
+      <c r="P51">
+        <v>10.61410467</v>
+      </c>
+      <c r="Q51">
+        <v>23.31410467</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.181224828569187</v>
+      </c>
+      <c r="T51">
+        <v>2.05290112852314</v>
+      </c>
+      <c r="U51">
+        <v>0.0609</v>
+      </c>
+      <c r="V51">
+        <v>0.1</v>
+      </c>
+      <c r="W51">
+        <v>0.05481</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.019466523508564</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1235502833246804</v>
+      </c>
+      <c r="C52">
+        <v>101.3963660667383</v>
+      </c>
+      <c r="D52">
+        <v>195.7163660667383</v>
+      </c>
+      <c r="E52">
+        <v>-13.85000000000001</v>
+      </c>
+      <c r="F52">
+        <v>97.85000000000001</v>
+      </c>
+      <c r="G52">
+        <v>3.53</v>
+      </c>
+      <c r="H52">
+        <v>84</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K52">
+        <v>12.7</v>
+      </c>
+      <c r="L52">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M52">
+        <v>6.869070000000001</v>
+      </c>
+      <c r="N52">
+        <v>10.76426333333333</v>
+      </c>
+      <c r="O52">
+        <v>1.076426333333333</v>
+      </c>
+      <c r="P52">
+        <v>9.687836999999998</v>
+      </c>
+      <c r="Q52">
+        <v>22.387837</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1839205666493609</v>
+      </c>
+      <c r="T52">
+        <v>2.091757301302758</v>
+      </c>
+      <c r="U52">
+        <v>0.0702</v>
+      </c>
+      <c r="V52">
+        <v>0.1</v>
+      </c>
+      <c r="W52">
+        <v>0.06318</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.567062693105957</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1237177040790755</v>
+      </c>
+      <c r="C53">
+        <v>99.05349857291344</v>
+      </c>
+      <c r="D53">
+        <v>195.3304985729135</v>
+      </c>
+      <c r="E53">
+        <v>-11.893</v>
+      </c>
+      <c r="F53">
+        <v>99.80700000000002</v>
+      </c>
+      <c r="G53">
+        <v>3.53</v>
+      </c>
+      <c r="H53">
+        <v>84</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K53">
+        <v>12.7</v>
+      </c>
+      <c r="L53">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M53">
+        <v>7.006451400000001</v>
+      </c>
+      <c r="N53">
+        <v>10.62688193333333</v>
+      </c>
+      <c r="O53">
+        <v>1.062688193333333</v>
+      </c>
+      <c r="P53">
+        <v>9.564193739999999</v>
+      </c>
+      <c r="Q53">
+        <v>22.26419374</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1867263348552561</v>
+      </c>
+      <c r="T53">
+        <v>2.132199440318279</v>
+      </c>
+      <c r="U53">
+        <v>0.0702</v>
+      </c>
+      <c r="V53">
+        <v>0.1</v>
+      </c>
+      <c r="W53">
+        <v>0.06318</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.516728130496035</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1260847248334706</v>
+      </c>
+      <c r="C54">
+        <v>91.79945095123006</v>
+      </c>
+      <c r="D54">
+        <v>190.0334509512301</v>
+      </c>
+      <c r="E54">
+        <v>-9.936000000000007</v>
+      </c>
+      <c r="F54">
+        <v>101.764</v>
+      </c>
+      <c r="G54">
+        <v>3.53</v>
+      </c>
+      <c r="H54">
+        <v>84</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K54">
+        <v>12.7</v>
+      </c>
+      <c r="L54">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M54">
+        <v>7.6221236</v>
+      </c>
+      <c r="N54">
+        <v>10.01120973333333</v>
+      </c>
+      <c r="O54">
+        <v>1.001120973333333</v>
+      </c>
+      <c r="P54">
+        <v>9.010088759999999</v>
+      </c>
+      <c r="Q54">
+        <v>21.71008876</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1896490100697304</v>
+      </c>
+      <c r="T54">
+        <v>2.174326668459446</v>
+      </c>
+      <c r="U54">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V54">
+        <v>0.1</v>
+      </c>
+      <c r="W54">
+        <v>0.06741</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.313441011811109</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1262944455878657</v>
+      </c>
+      <c r="C55">
+        <v>89.38694822273094</v>
+      </c>
+      <c r="D55">
+        <v>189.577948222731</v>
+      </c>
+      <c r="E55">
+        <v>-7.978999999999999</v>
+      </c>
+      <c r="F55">
+        <v>103.721</v>
+      </c>
+      <c r="G55">
+        <v>3.53</v>
+      </c>
+      <c r="H55">
+        <v>84</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K55">
+        <v>12.7</v>
+      </c>
+      <c r="L55">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M55">
+        <v>7.768702900000001</v>
+      </c>
+      <c r="N55">
+        <v>9.864630433333332</v>
+      </c>
+      <c r="O55">
+        <v>0.9864630433333332</v>
+      </c>
+      <c r="P55">
+        <v>8.878167389999998</v>
+      </c>
+      <c r="Q55">
+        <v>21.57816739</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1926960544422673</v>
+      </c>
+      <c r="T55">
+        <v>2.21824654460662</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.1</v>
+      </c>
+      <c r="W55">
+        <v>0.06741</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.269791181399579</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1265041663422607</v>
+      </c>
+      <c r="C56">
+        <v>86.97662391698712</v>
+      </c>
+      <c r="D56">
+        <v>189.1246239169871</v>
+      </c>
+      <c r="E56">
+        <v>-6.022000000000006</v>
+      </c>
+      <c r="F56">
+        <v>105.678</v>
+      </c>
+      <c r="G56">
+        <v>3.53</v>
+      </c>
+      <c r="H56">
+        <v>84</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K56">
+        <v>12.7</v>
+      </c>
+      <c r="L56">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M56">
+        <v>7.9152822</v>
+      </c>
+      <c r="N56">
+        <v>9.718051133333333</v>
+      </c>
+      <c r="O56">
+        <v>0.9718051133333333</v>
+      </c>
+      <c r="P56">
+        <v>8.746246019999999</v>
+      </c>
+      <c r="Q56">
+        <v>21.44624602</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1958755790049147</v>
+      </c>
+      <c r="T56">
+        <v>2.264075980586281</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.1</v>
+      </c>
+      <c r="W56">
+        <v>0.06741</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.227758011373661</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1267138870966558</v>
+      </c>
+      <c r="C57">
+        <v>84.56846244395447</v>
+      </c>
+      <c r="D57">
+        <v>188.6734624439545</v>
+      </c>
+      <c r="E57">
+        <v>-4.064999999999998</v>
+      </c>
+      <c r="F57">
+        <v>107.635</v>
+      </c>
+      <c r="G57">
+        <v>3.53</v>
+      </c>
+      <c r="H57">
+        <v>84</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K57">
+        <v>12.7</v>
+      </c>
+      <c r="L57">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M57">
+        <v>8.061861500000001</v>
+      </c>
+      <c r="N57">
+        <v>9.571471833333332</v>
+      </c>
+      <c r="O57">
+        <v>0.9571471833333333</v>
+      </c>
+      <c r="P57">
+        <v>8.614324649999999</v>
+      </c>
+      <c r="Q57">
+        <v>21.31432465</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1991964157703463</v>
+      </c>
+      <c r="T57">
+        <v>2.31194228038726</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.1</v>
+      </c>
+      <c r="W57">
+        <v>0.06741</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.187253320257776</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1269236078510509</v>
+      </c>
+      <c r="C58">
+        <v>82.16244836199641</v>
+      </c>
+      <c r="D58">
+        <v>188.2244483619964</v>
+      </c>
+      <c r="E58">
+        <v>-2.108000000000004</v>
+      </c>
+      <c r="F58">
+        <v>109.592</v>
+      </c>
+      <c r="G58">
+        <v>3.53</v>
+      </c>
+      <c r="H58">
+        <v>84</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K58">
+        <v>12.7</v>
+      </c>
+      <c r="L58">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M58">
+        <v>8.2084408</v>
+      </c>
+      <c r="N58">
+        <v>9.424892533333333</v>
+      </c>
+      <c r="O58">
+        <v>0.9424892533333333</v>
+      </c>
+      <c r="P58">
+        <v>8.48240328</v>
+      </c>
+      <c r="Q58">
+        <v>21.18240328</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2026681996614793</v>
+      </c>
+      <c r="T58">
+        <v>2.361984321088282</v>
+      </c>
+      <c r="U58">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V58">
+        <v>0.1</v>
+      </c>
+      <c r="W58">
+        <v>0.06741</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.148195225253173</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.127133328605446</v>
+      </c>
+      <c r="C59">
+        <v>79.7585663761222</v>
+      </c>
+      <c r="D59">
+        <v>187.7775663761222</v>
+      </c>
+      <c r="E59">
+        <v>-0.1509999999999962</v>
+      </c>
+      <c r="F59">
+        <v>111.549</v>
+      </c>
+      <c r="G59">
+        <v>3.53</v>
+      </c>
+      <c r="H59">
+        <v>84</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K59">
+        <v>12.7</v>
+      </c>
+      <c r="L59">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M59">
+        <v>8.355020100000001</v>
+      </c>
+      <c r="N59">
+        <v>9.278313233333332</v>
+      </c>
+      <c r="O59">
+        <v>0.9278313233333333</v>
+      </c>
+      <c r="P59">
+        <v>8.350481909999999</v>
+      </c>
+      <c r="Q59">
+        <v>21.05048191</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2063014618731301</v>
+      </c>
+      <c r="T59">
+        <v>2.414353898566097</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.1</v>
+      </c>
+      <c r="W59">
+        <v>0.06741</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.110507589722415</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.127343049359841</v>
+      </c>
+      <c r="C60">
+        <v>77.35680133625075</v>
+      </c>
+      <c r="D60">
+        <v>187.3328013362508</v>
+      </c>
+      <c r="E60">
+        <v>1.805999999999983</v>
+      </c>
+      <c r="F60">
+        <v>113.506</v>
+      </c>
+      <c r="G60">
+        <v>3.53</v>
+      </c>
+      <c r="H60">
+        <v>84</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K60">
+        <v>12.7</v>
+      </c>
+      <c r="L60">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M60">
+        <v>8.5015994</v>
+      </c>
+      <c r="N60">
+        <v>9.131733933333333</v>
+      </c>
+      <c r="O60">
+        <v>0.9131733933333334</v>
+      </c>
+      <c r="P60">
+        <v>8.21856054</v>
+      </c>
+      <c r="Q60">
+        <v>20.91856054</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2101077365710501</v>
+      </c>
+      <c r="T60">
+        <v>2.469217265447617</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.1</v>
+      </c>
+      <c r="W60">
+        <v>0.06741</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.074119527830649</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1275527701142361</v>
+      </c>
+      <c r="C61">
+        <v>74.95713823549782</v>
+      </c>
+      <c r="D61">
+        <v>186.8901382354978</v>
+      </c>
+      <c r="E61">
+        <v>3.762999999999991</v>
+      </c>
+      <c r="F61">
+        <v>115.463</v>
+      </c>
+      <c r="G61">
+        <v>3.53</v>
+      </c>
+      <c r="H61">
+        <v>84</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K61">
+        <v>12.7</v>
+      </c>
+      <c r="L61">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M61">
+        <v>8.648178700000001</v>
+      </c>
+      <c r="N61">
+        <v>8.985154633333332</v>
+      </c>
+      <c r="O61">
+        <v>0.8985154633333332</v>
+      </c>
+      <c r="P61">
+        <v>8.086639169999998</v>
+      </c>
+      <c r="Q61">
+        <v>20.78663917</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2140996832054539</v>
+      </c>
+      <c r="T61">
+        <v>2.526756894128236</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.1</v>
+      </c>
+      <c r="W61">
+        <v>0.06741</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.038964959562333</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1277624908686312</v>
+      </c>
+      <c r="C62">
+        <v>72.55956220848857</v>
+      </c>
+      <c r="D62">
+        <v>186.4495622084886</v>
+      </c>
+      <c r="E62">
+        <v>5.719999999999985</v>
+      </c>
+      <c r="F62">
+        <v>117.42</v>
+      </c>
+      <c r="G62">
+        <v>3.53</v>
+      </c>
+      <c r="H62">
+        <v>84</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K62">
+        <v>12.7</v>
+      </c>
+      <c r="L62">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M62">
+        <v>8.794758</v>
+      </c>
+      <c r="N62">
+        <v>8.838575333333333</v>
+      </c>
+      <c r="O62">
+        <v>0.8838575333333334</v>
+      </c>
+      <c r="P62">
+        <v>7.954717799999999</v>
+      </c>
+      <c r="Q62">
+        <v>20.6547178</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2182912271715779</v>
+      </c>
+      <c r="T62">
+        <v>2.587173504242885</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.1</v>
+      </c>
+      <c r="W62">
+        <v>0.06741</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.004982210236294</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1369209116230263</v>
+      </c>
+      <c r="C63">
+        <v>53.19971186871064</v>
+      </c>
+      <c r="D63">
+        <v>169.0467118687106</v>
+      </c>
+      <c r="E63">
+        <v>7.676999999999992</v>
+      </c>
+      <c r="F63">
+        <v>119.377</v>
+      </c>
+      <c r="G63">
+        <v>3.53</v>
+      </c>
+      <c r="H63">
+        <v>84</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K63">
+        <v>12.7</v>
+      </c>
+      <c r="L63">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M63">
+        <v>10.8871824</v>
+      </c>
+      <c r="N63">
+        <v>6.746150933333331</v>
+      </c>
+      <c r="O63">
+        <v>0.6746150933333331</v>
+      </c>
+      <c r="P63">
+        <v>6.071535839999997</v>
+      </c>
+      <c r="Q63">
+        <v>18.77153584</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2226977221103237</v>
+      </c>
+      <c r="T63">
+        <v>2.650688402055723</v>
+      </c>
+      <c r="U63">
+        <v>0.0912</v>
+      </c>
+      <c r="V63">
+        <v>0.1</v>
+      </c>
+      <c r="W63">
+        <v>0.08208</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>1.619641582686566</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1372773323774213</v>
+      </c>
+      <c r="C64">
+        <v>50.63087810841617</v>
+      </c>
+      <c r="D64">
+        <v>168.4348781084162</v>
+      </c>
+      <c r="E64">
+        <v>9.633999999999986</v>
+      </c>
+      <c r="F64">
+        <v>121.334</v>
+      </c>
+      <c r="G64">
+        <v>3.53</v>
+      </c>
+      <c r="H64">
+        <v>84</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K64">
+        <v>12.7</v>
+      </c>
+      <c r="L64">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M64">
+        <v>11.0656608</v>
+      </c>
+      <c r="N64">
+        <v>6.567672533333333</v>
+      </c>
+      <c r="O64">
+        <v>0.6567672533333333</v>
+      </c>
+      <c r="P64">
+        <v>5.91090528</v>
+      </c>
+      <c r="Q64">
+        <v>18.61090528</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2273361378353193</v>
+      </c>
+      <c r="T64">
+        <v>2.717546189227129</v>
+      </c>
+      <c r="U64">
+        <v>0.0912</v>
+      </c>
+      <c r="V64">
+        <v>0.1</v>
+      </c>
+      <c r="W64">
+        <v>0.08208</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.593518331352912</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1376337531318164</v>
+      </c>
+      <c r="C65">
+        <v>48.06645721808756</v>
+      </c>
+      <c r="D65">
+        <v>167.8274572180876</v>
+      </c>
+      <c r="E65">
+        <v>11.59099999999999</v>
+      </c>
+      <c r="F65">
+        <v>123.291</v>
+      </c>
+      <c r="G65">
+        <v>3.53</v>
+      </c>
+      <c r="H65">
+        <v>84</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K65">
+        <v>12.7</v>
+      </c>
+      <c r="L65">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M65">
+        <v>11.2441392</v>
+      </c>
+      <c r="N65">
+        <v>6.389194133333332</v>
+      </c>
+      <c r="O65">
+        <v>0.6389194133333332</v>
+      </c>
+      <c r="P65">
+        <v>5.750274719999998</v>
+      </c>
+      <c r="Q65">
+        <v>18.45027472</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2322252787346389</v>
+      </c>
+      <c r="T65">
+        <v>2.788017910840234</v>
+      </c>
+      <c r="U65">
+        <v>0.0912</v>
+      </c>
+      <c r="V65">
+        <v>0.1</v>
+      </c>
+      <c r="W65">
+        <v>0.08208</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.568224389585406</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1379901738862115</v>
+      </c>
+      <c r="C66">
+        <v>45.50640162733421</v>
+      </c>
+      <c r="D66">
+        <v>167.2244016273342</v>
+      </c>
+      <c r="E66">
+        <v>13.548</v>
+      </c>
+      <c r="F66">
+        <v>125.248</v>
+      </c>
+      <c r="G66">
+        <v>3.53</v>
+      </c>
+      <c r="H66">
+        <v>84</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K66">
+        <v>12.7</v>
+      </c>
+      <c r="L66">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M66">
+        <v>11.4226176</v>
+      </c>
+      <c r="N66">
+        <v>6.21071573333333</v>
+      </c>
+      <c r="O66">
+        <v>0.6210715733333331</v>
+      </c>
+      <c r="P66">
+        <v>5.589644159999997</v>
+      </c>
+      <c r="Q66">
+        <v>18.28964415999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2373860385728096</v>
+      </c>
+      <c r="T66">
+        <v>2.862404728098511</v>
+      </c>
+      <c r="U66">
+        <v>0.0912</v>
+      </c>
+      <c r="V66">
+        <v>0.1</v>
+      </c>
+      <c r="W66">
+        <v>0.08208</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>1.543720883498134</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1383465946406065</v>
+      </c>
+      <c r="C67">
+        <v>42.95066444705739</v>
+      </c>
+      <c r="D67">
+        <v>166.6256644470574</v>
+      </c>
+      <c r="E67">
+        <v>15.505</v>
+      </c>
+      <c r="F67">
+        <v>127.205</v>
+      </c>
+      <c r="G67">
+        <v>3.53</v>
+      </c>
+      <c r="H67">
+        <v>84</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K67">
+        <v>12.7</v>
+      </c>
+      <c r="L67">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M67">
+        <v>11.601096</v>
+      </c>
+      <c r="N67">
+        <v>6.032237333333331</v>
+      </c>
+      <c r="O67">
+        <v>0.6032237333333331</v>
+      </c>
+      <c r="P67">
+        <v>5.429013599999998</v>
+      </c>
+      <c r="Q67">
+        <v>18.1290136</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2428416989731615</v>
+      </c>
+      <c r="T67">
+        <v>2.94104222062869</v>
+      </c>
+      <c r="U67">
+        <v>0.0912</v>
+      </c>
+      <c r="V67">
+        <v>0.1</v>
+      </c>
+      <c r="W67">
+        <v>0.08208</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>1.519971331444316</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1795221761470218</v>
+      </c>
+      <c r="C68">
+        <v>-7.761327945416454</v>
+      </c>
+      <c r="D68">
+        <v>117.8706720545836</v>
+      </c>
+      <c r="E68">
+        <v>17.46199999999999</v>
+      </c>
+      <c r="F68">
+        <v>129.162</v>
+      </c>
+      <c r="G68">
+        <v>3.53</v>
+      </c>
+      <c r="H68">
+        <v>84</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K68">
+        <v>12.7</v>
+      </c>
+      <c r="L68">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M68">
+        <v>20.2267692</v>
+      </c>
+      <c r="N68">
+        <v>-2.59343586666667</v>
+      </c>
+      <c r="O68">
+        <v>-0.2593435866666671</v>
+      </c>
+      <c r="P68">
+        <v>-2.334092280000003</v>
+      </c>
+      <c r="Q68">
+        <v>10.36590772</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2505193123524226</v>
+      </c>
+      <c r="T68">
+        <v>3.051706781920353</v>
+      </c>
+      <c r="U68">
+        <v>0.1566</v>
+      </c>
+      <c r="V68">
+        <v>0.08717820013160249</v>
+      </c>
+      <c r="W68">
+        <v>0.1429478938593911</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.8717820013160248</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1807001761470218</v>
+      </c>
+      <c r="C69">
+        <v>-10.69684436062116</v>
+      </c>
+      <c r="D69">
+        <v>116.8921556393789</v>
+      </c>
+      <c r="E69">
+        <v>19.41900000000001</v>
+      </c>
+      <c r="F69">
+        <v>131.119</v>
+      </c>
+      <c r="G69">
+        <v>3.53</v>
+      </c>
+      <c r="H69">
+        <v>84</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K69">
+        <v>12.7</v>
+      </c>
+      <c r="L69">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M69">
+        <v>20.53323540000001</v>
+      </c>
+      <c r="N69">
+        <v>-2.899902066666673</v>
+      </c>
+      <c r="O69">
+        <v>-0.2899902066666673</v>
+      </c>
+      <c r="P69">
+        <v>-2.609911860000006</v>
+      </c>
+      <c r="Q69">
+        <v>10.09008813999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2569350490903748</v>
+      </c>
+      <c r="T69">
+        <v>3.144182745008849</v>
+      </c>
+      <c r="U69">
+        <v>0.1566</v>
+      </c>
+      <c r="V69">
+        <v>0.08587703296545916</v>
+      </c>
+      <c r="W69">
+        <v>0.1431516566376091</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.8587703296545914</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1818781761470218</v>
+      </c>
+      <c r="C70">
+        <v>-13.61624801330467</v>
+      </c>
+      <c r="D70">
+        <v>115.9297519866954</v>
+      </c>
+      <c r="E70">
+        <v>21.376</v>
+      </c>
+      <c r="F70">
+        <v>133.076</v>
+      </c>
+      <c r="G70">
+        <v>3.53</v>
+      </c>
+      <c r="H70">
+        <v>84</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K70">
+        <v>12.7</v>
+      </c>
+      <c r="L70">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M70">
+        <v>20.83970160000001</v>
+      </c>
+      <c r="N70">
+        <v>-3.206368266666672</v>
+      </c>
+      <c r="O70">
+        <v>-0.3206368266666673</v>
+      </c>
+      <c r="P70">
+        <v>-2.885731440000005</v>
+      </c>
+      <c r="Q70">
+        <v>9.814268559999995</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.263751769374449</v>
+      </c>
+      <c r="T70">
+        <v>3.242438455790376</v>
+      </c>
+      <c r="U70">
+        <v>0.1566</v>
+      </c>
+      <c r="V70">
+        <v>0.08461413542184947</v>
+      </c>
+      <c r="W70">
+        <v>0.1433494263929384</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.8461413542184946</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1830561761470218</v>
+      </c>
+      <c r="C71">
+        <v>-16.51993363528555</v>
+      </c>
+      <c r="D71">
+        <v>114.9830663647145</v>
+      </c>
+      <c r="E71">
+        <v>23.333</v>
+      </c>
+      <c r="F71">
+        <v>135.033</v>
+      </c>
+      <c r="G71">
+        <v>3.53</v>
+      </c>
+      <c r="H71">
+        <v>84</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K71">
+        <v>12.7</v>
+      </c>
+      <c r="L71">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M71">
+        <v>21.1461678</v>
+      </c>
+      <c r="N71">
+        <v>-3.512834466666671</v>
+      </c>
+      <c r="O71">
+        <v>-0.3512834466666672</v>
+      </c>
+      <c r="P71">
+        <v>-3.161551020000004</v>
+      </c>
+      <c r="Q71">
+        <v>9.538448979999995</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2710082780639474</v>
+      </c>
+      <c r="T71">
+        <v>3.347033244686839</v>
+      </c>
+      <c r="U71">
+        <v>0.1566</v>
+      </c>
+      <c r="V71">
+        <v>0.0833878436041415</v>
+      </c>
+      <c r="W71">
+        <v>0.1435414636915915</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.833878436041415</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1842341761470218</v>
+      </c>
+      <c r="C72">
+        <v>-19.40828316925418</v>
+      </c>
+      <c r="D72">
+        <v>114.0517168307459</v>
+      </c>
+      <c r="E72">
+        <v>25.29000000000002</v>
+      </c>
+      <c r="F72">
+        <v>136.99</v>
+      </c>
+      <c r="G72">
+        <v>3.53</v>
+      </c>
+      <c r="H72">
+        <v>84</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K72">
+        <v>12.7</v>
+      </c>
+      <c r="L72">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M72">
+        <v>21.45263400000001</v>
+      </c>
+      <c r="N72">
+        <v>-3.819300666666674</v>
+      </c>
+      <c r="O72">
+        <v>-0.3819300666666674</v>
+      </c>
+      <c r="P72">
+        <v>-3.437370600000007</v>
+      </c>
+      <c r="Q72">
+        <v>9.262629399999993</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2787485539994123</v>
+      </c>
+      <c r="T72">
+        <v>3.458601019509734</v>
+      </c>
+      <c r="U72">
+        <v>0.1566</v>
+      </c>
+      <c r="V72">
+        <v>0.0821965886955109</v>
+      </c>
+      <c r="W72">
+        <v>0.143728014210283</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.821965886955109</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1854121761470218</v>
+      </c>
+      <c r="C73">
+        <v>-22.28166628256312</v>
+      </c>
+      <c r="D73">
+        <v>113.1353337174369</v>
+      </c>
+      <c r="E73">
+        <v>27.24699999999999</v>
+      </c>
+      <c r="F73">
+        <v>138.947</v>
+      </c>
+      <c r="G73">
+        <v>3.53</v>
+      </c>
+      <c r="H73">
+        <v>84</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K73">
+        <v>12.7</v>
+      </c>
+      <c r="L73">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M73">
+        <v>21.7591002</v>
+      </c>
+      <c r="N73">
+        <v>-4.12576686666667</v>
+      </c>
+      <c r="O73">
+        <v>-0.412576686666667</v>
+      </c>
+      <c r="P73">
+        <v>-3.713190180000002</v>
+      </c>
+      <c r="Q73">
+        <v>8.986809819999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2870226420683575</v>
+      </c>
+      <c r="T73">
+        <v>3.577863123630758</v>
+      </c>
+      <c r="U73">
+        <v>0.1566</v>
+      </c>
+      <c r="V73">
+        <v>0.08103889026317979</v>
+      </c>
+      <c r="W73">
+        <v>0.1439093097847861</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.8103889026317977</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2252728459982976</v>
+      </c>
+      <c r="C74">
+        <v>-48.42261736499489</v>
+      </c>
+      <c r="D74">
+        <v>88.9513826350051</v>
+      </c>
+      <c r="E74">
+        <v>29.20399999999998</v>
+      </c>
+      <c r="F74">
+        <v>140.904</v>
+      </c>
+      <c r="G74">
+        <v>3.53</v>
+      </c>
+      <c r="H74">
+        <v>84</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K74">
+        <v>12.7</v>
+      </c>
+      <c r="L74">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M74">
+        <v>29.4207552</v>
+      </c>
+      <c r="N74">
+        <v>-11.78742186666667</v>
+      </c>
+      <c r="O74">
+        <v>-1.178742186666667</v>
+      </c>
+      <c r="P74">
+        <v>-10.60867968</v>
+      </c>
+      <c r="Q74">
+        <v>2.091320319999998</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2998115573253551</v>
+      </c>
+      <c r="T74">
+        <v>3.762201618733271</v>
+      </c>
+      <c r="U74">
+        <v>0.2088</v>
+      </c>
+      <c r="V74">
+        <v>0.05993501259047671</v>
+      </c>
+      <c r="W74">
+        <v>0.1962855693711085</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5993501259047671</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2269728459982975</v>
+      </c>
+      <c r="C75">
+        <v>-51.18322614115635</v>
+      </c>
+      <c r="D75">
+        <v>88.14777385884366</v>
+      </c>
+      <c r="E75">
+        <v>31.161</v>
+      </c>
+      <c r="F75">
+        <v>142.861</v>
+      </c>
+      <c r="G75">
+        <v>3.53</v>
+      </c>
+      <c r="H75">
+        <v>84</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K75">
+        <v>12.7</v>
+      </c>
+      <c r="L75">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M75">
+        <v>29.82937680000001</v>
+      </c>
+      <c r="N75">
+        <v>-12.19604346666667</v>
+      </c>
+      <c r="O75">
+        <v>-1.219604346666667</v>
+      </c>
+      <c r="P75">
+        <v>-10.97643912000001</v>
+      </c>
+      <c r="Q75">
+        <v>1.723560879999994</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.309478652041109</v>
+      </c>
+      <c r="T75">
+        <v>3.901542419427096</v>
+      </c>
+      <c r="U75">
+        <v>0.2088</v>
+      </c>
+      <c r="V75">
+        <v>0.05911398502074414</v>
+      </c>
+      <c r="W75">
+        <v>0.1964569999276686</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5911398502074414</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2286728459982975</v>
+      </c>
+      <c r="C76">
+        <v>-53.9294449195033</v>
+      </c>
+      <c r="D76">
+        <v>87.35855508049671</v>
+      </c>
+      <c r="E76">
+        <v>33.11799999999999</v>
+      </c>
+      <c r="F76">
+        <v>144.818</v>
+      </c>
+      <c r="G76">
+        <v>3.53</v>
+      </c>
+      <c r="H76">
+        <v>84</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K76">
+        <v>12.7</v>
+      </c>
+      <c r="L76">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M76">
+        <v>30.23799840000001</v>
+      </c>
+      <c r="N76">
+        <v>-12.60466506666667</v>
+      </c>
+      <c r="O76">
+        <v>-1.260466506666667</v>
+      </c>
+      <c r="P76">
+        <v>-11.34419856000001</v>
+      </c>
+      <c r="Q76">
+        <v>1.355801439999993</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3198893694273055</v>
+      </c>
+      <c r="T76">
+        <v>4.051601743251215</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.05831514738532868</v>
+      </c>
+      <c r="W76">
+        <v>0.1966237972259434</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5831514738532868</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2303728459982975</v>
+      </c>
+      <c r="C77">
+        <v>-56.66165678662858</v>
+      </c>
+      <c r="D77">
+        <v>86.58334321337142</v>
+      </c>
+      <c r="E77">
+        <v>35.07499999999999</v>
+      </c>
+      <c r="F77">
+        <v>146.775</v>
+      </c>
+      <c r="G77">
+        <v>3.53</v>
+      </c>
+      <c r="H77">
+        <v>84</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K77">
+        <v>12.7</v>
+      </c>
+      <c r="L77">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M77">
+        <v>30.64662</v>
+      </c>
+      <c r="N77">
+        <v>-13.01328666666667</v>
+      </c>
+      <c r="O77">
+        <v>-1.301328666666667</v>
+      </c>
+      <c r="P77">
+        <v>-11.711958</v>
+      </c>
+      <c r="Q77">
+        <v>0.9880419999999965</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3311329442043978</v>
+      </c>
+      <c r="T77">
+        <v>4.213665812981264</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.05753761208685764</v>
+      </c>
+      <c r="W77">
+        <v>0.1967861465962641</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5753761208685764</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2320728459982976</v>
+      </c>
+      <c r="C78">
+        <v>-59.38023135082803</v>
+      </c>
+      <c r="D78">
+        <v>85.821768649172</v>
+      </c>
+      <c r="E78">
+        <v>37.03200000000001</v>
+      </c>
+      <c r="F78">
+        <v>148.732</v>
+      </c>
+      <c r="G78">
+        <v>3.53</v>
+      </c>
+      <c r="H78">
+        <v>84</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K78">
+        <v>12.7</v>
+      </c>
+      <c r="L78">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M78">
+        <v>31.05524160000001</v>
+      </c>
+      <c r="N78">
+        <v>-13.42190826666668</v>
+      </c>
+      <c r="O78">
+        <v>-1.342190826666668</v>
+      </c>
+      <c r="P78">
+        <v>-12.07971744000001</v>
+      </c>
+      <c r="Q78">
+        <v>0.6202825599999908</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3433134835462477</v>
+      </c>
+      <c r="T78">
+        <v>4.389235221855484</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.05678053824360951</v>
+      </c>
+      <c r="W78">
+        <v>0.1969442236147343</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.567805382436095</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2337728459982976</v>
+      </c>
+      <c r="C79">
+        <v>-62.08552532969759</v>
+      </c>
+      <c r="D79">
+        <v>85.07347467030243</v>
+      </c>
+      <c r="E79">
+        <v>38.989</v>
+      </c>
+      <c r="F79">
+        <v>150.689</v>
+      </c>
+      <c r="G79">
+        <v>3.53</v>
+      </c>
+      <c r="H79">
+        <v>84</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K79">
+        <v>12.7</v>
+      </c>
+      <c r="L79">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M79">
+        <v>31.46386320000001</v>
+      </c>
+      <c r="N79">
+        <v>-13.83052986666667</v>
+      </c>
+      <c r="O79">
+        <v>-1.383052986666667</v>
+      </c>
+      <c r="P79">
+        <v>-12.44747688000001</v>
+      </c>
+      <c r="Q79">
+        <v>0.252523119999994</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3565532002221715</v>
+      </c>
+      <c r="T79">
+        <v>4.5800715358492</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.05604312865603017</v>
+      </c>
+      <c r="W79">
+        <v>0.1970981947366209</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5604312865603016</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2354728459982975</v>
+      </c>
+      <c r="C80">
+        <v>-64.7778831072566</v>
+      </c>
+      <c r="D80">
+        <v>84.33811689274341</v>
+      </c>
+      <c r="E80">
+        <v>40.946</v>
+      </c>
+      <c r="F80">
+        <v>152.646</v>
+      </c>
+      <c r="G80">
+        <v>3.53</v>
+      </c>
+      <c r="H80">
+        <v>84</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K80">
+        <v>12.7</v>
+      </c>
+      <c r="L80">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M80">
+        <v>31.87248480000001</v>
+      </c>
+      <c r="N80">
+        <v>-14.23915146666667</v>
+      </c>
+      <c r="O80">
+        <v>-1.423915146666667</v>
+      </c>
+      <c r="P80">
+        <v>-12.81523632000001</v>
+      </c>
+      <c r="Q80">
+        <v>-0.1152363200000064</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3709965275049976</v>
+      </c>
+      <c r="T80">
+        <v>4.788256605660528</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.05532462700659389</v>
+      </c>
+      <c r="W80">
+        <v>0.1972482178810232</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5532462700659388</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2371728459982975</v>
+      </c>
+      <c r="C81">
+        <v>-67.45763726242404</v>
+      </c>
+      <c r="D81">
+        <v>83.61536273757596</v>
+      </c>
+      <c r="E81">
+        <v>42.90299999999999</v>
+      </c>
+      <c r="F81">
+        <v>154.603</v>
+      </c>
+      <c r="G81">
+        <v>3.53</v>
+      </c>
+      <c r="H81">
+        <v>84</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K81">
+        <v>12.7</v>
+      </c>
+      <c r="L81">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M81">
+        <v>32.28110640000001</v>
+      </c>
+      <c r="N81">
+        <v>-14.64777306666667</v>
+      </c>
+      <c r="O81">
+        <v>-1.464777306666667</v>
+      </c>
+      <c r="P81">
+        <v>-13.18299576000001</v>
+      </c>
+      <c r="Q81">
+        <v>-0.4829957600000068</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3868154097671403</v>
+      </c>
+      <c r="T81">
+        <v>5.016268824977696</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.0546243152723332</v>
+      </c>
+      <c r="W81">
+        <v>0.1973944429711368</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.546243152723332</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2388728459982976</v>
+      </c>
+      <c r="C82">
+        <v>-70.12510907055284</v>
+      </c>
+      <c r="D82">
+        <v>82.90489092944719</v>
+      </c>
+      <c r="E82">
+        <v>44.86000000000001</v>
+      </c>
+      <c r="F82">
+        <v>156.56</v>
+      </c>
+      <c r="G82">
+        <v>3.53</v>
+      </c>
+      <c r="H82">
+        <v>84</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K82">
+        <v>12.7</v>
+      </c>
+      <c r="L82">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M82">
+        <v>32.68972800000001</v>
+      </c>
+      <c r="N82">
+        <v>-15.05639466666668</v>
+      </c>
+      <c r="O82">
+        <v>-1.505639466666668</v>
+      </c>
+      <c r="P82">
+        <v>-13.55075520000001</v>
+      </c>
+      <c r="Q82">
+        <v>-0.8507552000000089</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4042161802554973</v>
+      </c>
+      <c r="T82">
+        <v>5.267082266226581</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.05394151133142903</v>
+      </c>
+      <c r="W82">
+        <v>0.1975370124339976</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5394151133142903</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2405728459982976</v>
+      </c>
+      <c r="C83">
+        <v>-72.78060897961021</v>
+      </c>
+      <c r="D83">
+        <v>82.20639102038982</v>
+      </c>
+      <c r="E83">
+        <v>46.81700000000001</v>
+      </c>
+      <c r="F83">
+        <v>158.517</v>
+      </c>
+      <c r="G83">
+        <v>3.53</v>
+      </c>
+      <c r="H83">
+        <v>84</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K83">
+        <v>12.7</v>
+      </c>
+      <c r="L83">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M83">
+        <v>33.09834960000001</v>
+      </c>
+      <c r="N83">
+        <v>-15.46501626666667</v>
+      </c>
+      <c r="O83">
+        <v>-1.546501626666667</v>
+      </c>
+      <c r="P83">
+        <v>-13.91851464000001</v>
+      </c>
+      <c r="Q83">
+        <v>-1.218514640000006</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4234486107952604</v>
+      </c>
+      <c r="T83">
+        <v>5.54429712234377</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.05327556674709041</v>
+      </c>
+      <c r="W83">
+        <v>0.1976760616632075</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.532755667470904</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2422728459982976</v>
+      </c>
+      <c r="C84">
+        <v>-75.42443706248781</v>
+      </c>
+      <c r="D84">
+        <v>81.51956293751221</v>
+      </c>
+      <c r="E84">
+        <v>48.774</v>
+      </c>
+      <c r="F84">
+        <v>160.474</v>
+      </c>
+      <c r="G84">
+        <v>3.53</v>
+      </c>
+      <c r="H84">
+        <v>84</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K84">
+        <v>12.7</v>
+      </c>
+      <c r="L84">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M84">
+        <v>33.5069712</v>
+      </c>
+      <c r="N84">
+        <v>-15.87363786666667</v>
+      </c>
+      <c r="O84">
+        <v>-1.587363786666667</v>
+      </c>
+      <c r="P84">
+        <v>-14.28627408</v>
+      </c>
+      <c r="Q84">
+        <v>-1.586274080000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4448179780616637</v>
+      </c>
+      <c r="T84">
+        <v>5.852313629140647</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.05262586471358931</v>
+      </c>
+      <c r="W84">
+        <v>0.1978117194478026</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.526258647135893</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2439728459982976</v>
+      </c>
+      <c r="C85">
+        <v>-78.0568834468253</v>
+      </c>
+      <c r="D85">
+        <v>80.84411655317474</v>
+      </c>
+      <c r="E85">
+        <v>50.73100000000002</v>
+      </c>
+      <c r="F85">
+        <v>162.431</v>
+      </c>
+      <c r="G85">
+        <v>3.53</v>
+      </c>
+      <c r="H85">
+        <v>84</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K85">
+        <v>12.7</v>
+      </c>
+      <c r="L85">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M85">
+        <v>33.91559280000001</v>
+      </c>
+      <c r="N85">
+        <v>-16.28225946666668</v>
+      </c>
+      <c r="O85">
+        <v>-1.628225946666668</v>
+      </c>
+      <c r="P85">
+        <v>-14.65403352000001</v>
+      </c>
+      <c r="Q85">
+        <v>-1.954033520000014</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4687013885358793</v>
+      </c>
+      <c r="T85">
+        <v>6.196567372031274</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.05199181815077496</v>
+      </c>
+      <c r="W85">
+        <v>0.1979441083701182</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5199181815077496</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2456728459982975</v>
+      </c>
+      <c r="C86">
+        <v>-80.67822872364096</v>
+      </c>
+      <c r="D86">
+        <v>80.17977127635905</v>
+      </c>
+      <c r="E86">
+        <v>52.68799999999999</v>
+      </c>
+      <c r="F86">
+        <v>164.388</v>
+      </c>
+      <c r="G86">
+        <v>3.53</v>
+      </c>
+      <c r="H86">
+        <v>84</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K86">
+        <v>12.7</v>
+      </c>
+      <c r="L86">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M86">
+        <v>34.3242144</v>
+      </c>
+      <c r="N86">
+        <v>-16.69088106666667</v>
+      </c>
+      <c r="O86">
+        <v>-1.669088106666667</v>
+      </c>
+      <c r="P86">
+        <v>-15.02179296</v>
+      </c>
+      <c r="Q86">
+        <v>-2.321792960000003</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4955702253193715</v>
+      </c>
+      <c r="T86">
+        <v>6.583852832783225</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.05137286793469432</v>
+      </c>
+      <c r="W86">
+        <v>0.1980733451752358</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5137286793469432</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2473728459982975</v>
+      </c>
+      <c r="C87">
+        <v>-83.28874433597969</v>
+      </c>
+      <c r="D87">
+        <v>79.52625566402031</v>
+      </c>
+      <c r="E87">
+        <v>54.64499999999998</v>
+      </c>
+      <c r="F87">
+        <v>166.345</v>
+      </c>
+      <c r="G87">
+        <v>3.53</v>
+      </c>
+      <c r="H87">
+        <v>84</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K87">
+        <v>12.7</v>
+      </c>
+      <c r="L87">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M87">
+        <v>34.732836</v>
+      </c>
+      <c r="N87">
+        <v>-17.09950266666667</v>
+      </c>
+      <c r="O87">
+        <v>-1.709950266666667</v>
+      </c>
+      <c r="P87">
+        <v>-15.3895524</v>
+      </c>
+      <c r="Q87">
+        <v>-2.6895524</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5260215736739963</v>
+      </c>
+      <c r="T87">
+        <v>7.022776354968773</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.05076848125310969</v>
+      </c>
+      <c r="W87">
+        <v>0.1981995411143507</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5076848125310969</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2490728459982976</v>
+      </c>
+      <c r="C88">
+        <v>-85.88869294870707</v>
+      </c>
+      <c r="D88">
+        <v>78.88330705129295</v>
+      </c>
+      <c r="E88">
+        <v>56.602</v>
+      </c>
+      <c r="F88">
+        <v>168.302</v>
+      </c>
+      <c r="G88">
+        <v>3.53</v>
+      </c>
+      <c r="H88">
+        <v>84</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K88">
+        <v>12.7</v>
+      </c>
+      <c r="L88">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M88">
+        <v>35.14145760000001</v>
+      </c>
+      <c r="N88">
+        <v>-17.50812426666668</v>
+      </c>
+      <c r="O88">
+        <v>-1.750812426666668</v>
+      </c>
+      <c r="P88">
+        <v>-15.75731184000001</v>
+      </c>
+      <c r="Q88">
+        <v>-3.057311840000009</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5608231146507103</v>
+      </c>
+      <c r="T88">
+        <v>7.524403237466544</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.05017815007574793</v>
+      </c>
+      <c r="W88">
+        <v>0.1983228022641839</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5017815007574793</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2772869175502859</v>
+      </c>
+      <c r="C89">
+        <v>-97.17794182954289</v>
+      </c>
+      <c r="D89">
+        <v>69.55105817045713</v>
+      </c>
+      <c r="E89">
+        <v>58.559</v>
+      </c>
+      <c r="F89">
+        <v>170.259</v>
+      </c>
+      <c r="G89">
+        <v>3.53</v>
+      </c>
+      <c r="H89">
+        <v>84</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K89">
+        <v>12.7</v>
+      </c>
+      <c r="L89">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M89">
+        <v>40.65784920000001</v>
+      </c>
+      <c r="N89">
+        <v>-23.02451586666668</v>
+      </c>
+      <c r="O89">
+        <v>-2.302451586666668</v>
+      </c>
+      <c r="P89">
+        <v>-20.72206428000001</v>
+      </c>
+      <c r="Q89">
+        <v>-8.022064280000009</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6041639046391369</v>
+      </c>
+      <c r="T89">
+        <v>8.149114234644282</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04337005936195299</v>
+      </c>
+      <c r="W89">
+        <v>0.2284432298243656</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.43370059361953</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2792869175502859</v>
+      </c>
+      <c r="C90">
+        <v>-99.71336047184523</v>
+      </c>
+      <c r="D90">
+        <v>68.97263952815477</v>
+      </c>
+      <c r="E90">
+        <v>60.51599999999999</v>
+      </c>
+      <c r="F90">
+        <v>172.216</v>
+      </c>
+      <c r="G90">
+        <v>3.53</v>
+      </c>
+      <c r="H90">
+        <v>84</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K90">
+        <v>12.7</v>
+      </c>
+      <c r="L90">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M90">
+        <v>41.1251808</v>
+      </c>
+      <c r="N90">
+        <v>-23.49184746666667</v>
+      </c>
+      <c r="O90">
+        <v>-2.349184746666667</v>
+      </c>
+      <c r="P90">
+        <v>-21.14266272</v>
+      </c>
+      <c r="Q90">
+        <v>-8.442662720000005</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6512775633590653</v>
+      </c>
+      <c r="T90">
+        <v>8.828207087531309</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04287721777829444</v>
+      </c>
+      <c r="W90">
+        <v>0.2285609203945433</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4287721777829444</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2812869175502859</v>
+      </c>
+      <c r="C91">
+        <v>-102.239237673345</v>
+      </c>
+      <c r="D91">
+        <v>68.403762326655</v>
+      </c>
+      <c r="E91">
+        <v>62.47300000000001</v>
+      </c>
+      <c r="F91">
+        <v>174.173</v>
+      </c>
+      <c r="G91">
+        <v>3.53</v>
+      </c>
+      <c r="H91">
+        <v>84</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K91">
+        <v>12.7</v>
+      </c>
+      <c r="L91">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M91">
+        <v>41.59251240000001</v>
+      </c>
+      <c r="N91">
+        <v>-23.95917906666668</v>
+      </c>
+      <c r="O91">
+        <v>-2.395917906666668</v>
+      </c>
+      <c r="P91">
+        <v>-21.56326116000001</v>
+      </c>
+      <c r="Q91">
+        <v>-8.863261160000011</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7069573418462527</v>
+      </c>
+      <c r="T91">
+        <v>9.630771368215971</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04239545128640348</v>
+      </c>
+      <c r="W91">
+        <v>0.2286759662328068</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4239545128640348</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2832869175502859</v>
+      </c>
+      <c r="C92">
+        <v>-104.7558075923579</v>
+      </c>
+      <c r="D92">
+        <v>67.84419240764217</v>
+      </c>
+      <c r="E92">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="F92">
+        <v>176.13</v>
+      </c>
+      <c r="G92">
+        <v>3.53</v>
+      </c>
+      <c r="H92">
+        <v>84</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K92">
+        <v>12.7</v>
+      </c>
+      <c r="L92">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M92">
+        <v>42.05984400000001</v>
+      </c>
+      <c r="N92">
+        <v>-24.42651066666667</v>
+      </c>
+      <c r="O92">
+        <v>-2.442651066666667</v>
+      </c>
+      <c r="P92">
+        <v>-21.98385960000001</v>
+      </c>
+      <c r="Q92">
+        <v>-9.283859600000007</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7737730760308783</v>
+      </c>
+      <c r="T92">
+        <v>10.59384850503757</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04192439071655456</v>
+      </c>
+      <c r="W92">
+        <v>0.2287884554968868</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4192439071655456</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2852869175502859</v>
+      </c>
+      <c r="C93">
+        <v>-107.2632967873375</v>
+      </c>
+      <c r="D93">
+        <v>67.29370321266248</v>
+      </c>
+      <c r="E93">
+        <v>66.387</v>
+      </c>
+      <c r="F93">
+        <v>178.087</v>
+      </c>
+      <c r="G93">
+        <v>3.53</v>
+      </c>
+      <c r="H93">
+        <v>84</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K93">
+        <v>12.7</v>
+      </c>
+      <c r="L93">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M93">
+        <v>42.52717560000001</v>
+      </c>
+      <c r="N93">
+        <v>-24.89384226666667</v>
+      </c>
+      <c r="O93">
+        <v>-2.489384226666667</v>
+      </c>
+      <c r="P93">
+        <v>-22.40445804000001</v>
+      </c>
+      <c r="Q93">
+        <v>-9.704458040000006</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8554367511454202</v>
+      </c>
+      <c r="T93">
+        <v>11.77094278337508</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04146368312626275</v>
+      </c>
+      <c r="W93">
+        <v>0.2288984724694485</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.4146368312626275</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2872869175502859</v>
+      </c>
+      <c r="C94">
+        <v>-109.7619245227216</v>
+      </c>
+      <c r="D94">
+        <v>66.75207547727842</v>
+      </c>
+      <c r="E94">
+        <v>68.34399999999999</v>
+      </c>
+      <c r="F94">
+        <v>180.044</v>
+      </c>
+      <c r="G94">
+        <v>3.53</v>
+      </c>
+      <c r="H94">
+        <v>84</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K94">
+        <v>12.7</v>
+      </c>
+      <c r="L94">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M94">
+        <v>42.99450720000001</v>
+      </c>
+      <c r="N94">
+        <v>-25.36117386666668</v>
+      </c>
+      <c r="O94">
+        <v>-2.536117386666668</v>
+      </c>
+      <c r="P94">
+        <v>-22.82505648000001</v>
+      </c>
+      <c r="Q94">
+        <v>-10.12505648000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9575163450385979</v>
+      </c>
+      <c r="T94">
+        <v>13.24231063129697</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0410129909183686</v>
+      </c>
+      <c r="W94">
+        <v>0.2290060977686936</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4101299091836859</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2892869175502859</v>
+      </c>
+      <c r="C95">
+        <v>-112.2519030601247</v>
+      </c>
+      <c r="D95">
+        <v>66.21909693987534</v>
+      </c>
+      <c r="E95">
+        <v>70.30100000000002</v>
+      </c>
+      <c r="F95">
+        <v>182.001</v>
+      </c>
+      <c r="G95">
+        <v>3.53</v>
+      </c>
+      <c r="H95">
+        <v>84</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K95">
+        <v>12.7</v>
+      </c>
+      <c r="L95">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M95">
+        <v>43.46183880000001</v>
+      </c>
+      <c r="N95">
+        <v>-25.82850546666668</v>
+      </c>
+      <c r="O95">
+        <v>-2.582850546666668</v>
+      </c>
+      <c r="P95">
+        <v>-23.24565492000001</v>
+      </c>
+      <c r="Q95">
+        <v>-10.54565492000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.088761537186969</v>
+      </c>
+      <c r="T95">
+        <v>15.13406929291082</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04057199101602054</v>
+      </c>
+      <c r="W95">
+        <v>0.2291114085453743</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4057199101602054</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2912869175502859</v>
+      </c>
+      <c r="C96">
+        <v>-114.7334379356925</v>
+      </c>
+      <c r="D96">
+        <v>65.69456206430748</v>
+      </c>
+      <c r="E96">
+        <v>72.25800000000001</v>
+      </c>
+      <c r="F96">
+        <v>183.958</v>
+      </c>
+      <c r="G96">
+        <v>3.53</v>
+      </c>
+      <c r="H96">
+        <v>84</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K96">
+        <v>12.7</v>
+      </c>
+      <c r="L96">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M96">
+        <v>43.92917040000001</v>
+      </c>
+      <c r="N96">
+        <v>-26.29583706666668</v>
+      </c>
+      <c r="O96">
+        <v>-2.629583706666668</v>
+      </c>
+      <c r="P96">
+        <v>-23.66625336000001</v>
+      </c>
+      <c r="Q96">
+        <v>-10.96625336000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.263755126718131</v>
+      </c>
+      <c r="T96">
+        <v>17.65641417506263</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0401403740903182</v>
+      </c>
+      <c r="W96">
+        <v>0.229214478667232</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.4014037409031819</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2932869175502859</v>
+      </c>
+      <c r="C97">
+        <v>-117.2067282243776</v>
+      </c>
+      <c r="D97">
+        <v>65.17827177562241</v>
+      </c>
+      <c r="E97">
+        <v>74.215</v>
+      </c>
+      <c r="F97">
+        <v>185.915</v>
+      </c>
+      <c r="G97">
+        <v>3.53</v>
+      </c>
+      <c r="H97">
+        <v>84</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K97">
+        <v>12.7</v>
+      </c>
+      <c r="L97">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M97">
+        <v>44.39650200000001</v>
+      </c>
+      <c r="N97">
+        <v>-26.76316866666667</v>
+      </c>
+      <c r="O97">
+        <v>-2.676316866666667</v>
+      </c>
+      <c r="P97">
+        <v>-24.08685180000001</v>
+      </c>
+      <c r="Q97">
+        <v>-11.38685180000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.508746152061758</v>
+      </c>
+      <c r="T97">
+        <v>21.18769701007517</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03971784383673591</v>
+      </c>
+      <c r="W97">
+        <v>0.2293153788917875</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.397178438367359</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2952869175502859</v>
+      </c>
+      <c r="C98">
+        <v>-119.6719667918503</v>
+      </c>
+      <c r="D98">
+        <v>64.6700332081497</v>
+      </c>
+      <c r="E98">
+        <v>76.172</v>
+      </c>
+      <c r="F98">
+        <v>187.872</v>
+      </c>
+      <c r="G98">
+        <v>3.53</v>
+      </c>
+      <c r="H98">
+        <v>84</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K98">
+        <v>12.7</v>
+      </c>
+      <c r="L98">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M98">
+        <v>44.86383360000001</v>
+      </c>
+      <c r="N98">
+        <v>-27.23050026666667</v>
+      </c>
+      <c r="O98">
+        <v>-2.723050026666668</v>
+      </c>
+      <c r="P98">
+        <v>-24.50745024</v>
+      </c>
+      <c r="Q98">
+        <v>-11.80745024</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.876232690077194</v>
+      </c>
+      <c r="T98">
+        <v>26.4846212625939</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0393041162967699</v>
+      </c>
+      <c r="W98">
+        <v>0.2294141770283314</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.393041162967699</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2972869175502859</v>
+      </c>
+      <c r="C99">
+        <v>-122.1293405347154</v>
+      </c>
+      <c r="D99">
+        <v>64.16965946528461</v>
+      </c>
+      <c r="E99">
+        <v>78.12899999999999</v>
+      </c>
+      <c r="F99">
+        <v>189.829</v>
+      </c>
+      <c r="G99">
+        <v>3.53</v>
+      </c>
+      <c r="H99">
+        <v>84</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K99">
+        <v>12.7</v>
+      </c>
+      <c r="L99">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M99">
+        <v>45.3311652</v>
+      </c>
+      <c r="N99">
+        <v>-27.69783186666667</v>
+      </c>
+      <c r="O99">
+        <v>-2.769783186666667</v>
+      </c>
+      <c r="P99">
+        <v>-24.92804868</v>
+      </c>
+      <c r="Q99">
+        <v>-12.22804868</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.488710253436258</v>
+      </c>
+      <c r="T99">
+        <v>35.3128283501252</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03889891922154548</v>
+      </c>
+      <c r="W99">
+        <v>0.229510938089895</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3889891922154547</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2992869175502859</v>
+      </c>
+      <c r="C100">
+        <v>-124.5790306096624</v>
+      </c>
+      <c r="D100">
+        <v>63.67696939033759</v>
+      </c>
+      <c r="E100">
+        <v>80.08599999999998</v>
+      </c>
+      <c r="F100">
+        <v>191.786</v>
+      </c>
+      <c r="G100">
+        <v>3.53</v>
+      </c>
+      <c r="H100">
+        <v>84</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K100">
+        <v>12.7</v>
+      </c>
+      <c r="L100">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M100">
+        <v>45.7984968</v>
+      </c>
+      <c r="N100">
+        <v>-28.16516346666667</v>
+      </c>
+      <c r="O100">
+        <v>-2.816516346666667</v>
+      </c>
+      <c r="P100">
+        <v>-25.34864712</v>
+      </c>
+      <c r="Q100">
+        <v>-12.64864712</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.713665380154387</v>
+      </c>
+      <c r="T100">
+        <v>52.96924252518779</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03850199147438685</v>
+      </c>
+      <c r="W100">
+        <v>0.2296057244359164</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3850199147438684</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3012869175502859</v>
+      </c>
+      <c r="C101">
+        <v>-127.02121265214</v>
+      </c>
+      <c r="D101">
+        <v>63.19178734786007</v>
+      </c>
+      <c r="E101">
+        <v>82.04300000000001</v>
+      </c>
+      <c r="F101">
+        <v>193.743</v>
+      </c>
+      <c r="G101">
+        <v>3.53</v>
+      </c>
+      <c r="H101">
+        <v>84</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="K101">
+        <v>12.7</v>
+      </c>
+      <c r="L101">
+        <v>17.63333333333333</v>
+      </c>
+      <c r="M101">
+        <v>46.26582840000001</v>
+      </c>
+      <c r="N101">
+        <v>-28.63249506666668</v>
+      </c>
+      <c r="O101">
+        <v>-2.863249506666668</v>
+      </c>
+      <c r="P101">
+        <v>-25.76924556000001</v>
+      </c>
+      <c r="Q101">
+        <v>-13.06924556000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.388530760308774</v>
+      </c>
+      <c r="T101">
+        <v>105.9384850503756</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03811308246959505</v>
+      </c>
+      <c r="W101">
+        <v>0.2296985959062607</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3811308246959505</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_electrical_equipment.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1169666146812001</v>
+        <v>0.1168901480665189</v>
       </c>
       <c r="C2">
-        <v>184.3663607315094</v>
+        <v>182.907172706497</v>
       </c>
       <c r="D2">
-        <v>175.5363607315094</v>
+        <v>175.725172706497</v>
       </c>
       <c r="E2">
-        <v>-110.2</v>
+        <v>-108.552</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.648</v>
       </c>
       <c r="G2">
         <v>8.83</v>
@@ -1445,28 +1445,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08289440000000001</v>
       </c>
       <c r="N2">
-        <v>20.26666666666667</v>
+        <v>20.18377226666667</v>
       </c>
       <c r="O2">
-        <v>2.026666666666667</v>
+        <v>2.018377226666666</v>
       </c>
       <c r="P2">
-        <v>18.24</v>
+        <v>18.16539504</v>
       </c>
       <c r="Q2">
-        <v>31.64</v>
+        <v>31.56539504</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1169666146812001</v>
+        <v>0.1176135839055747</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.110933303562709</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>244.487765960869</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1168901480665189</v>
+        <v>0.1168136814518377</v>
       </c>
       <c r="C3">
-        <v>182.907172706497</v>
+        <v>181.4483913020749</v>
       </c>
       <c r="D3">
-        <v>175.725172706497</v>
+        <v>175.9143913020749</v>
       </c>
       <c r="E3">
-        <v>-108.552</v>
+        <v>-106.904</v>
       </c>
       <c r="F3">
-        <v>1.648</v>
+        <v>3.296</v>
       </c>
       <c r="G3">
         <v>8.83</v>
@@ -1527,28 +1527,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M3">
-        <v>0.08289440000000001</v>
+        <v>0.1657888</v>
       </c>
       <c r="N3">
-        <v>20.18377226666667</v>
+        <v>20.10087786666666</v>
       </c>
       <c r="O3">
-        <v>2.018377226666666</v>
+        <v>2.010087786666666</v>
       </c>
       <c r="P3">
-        <v>18.16539504</v>
+        <v>18.09079008</v>
       </c>
       <c r="Q3">
-        <v>31.56539504</v>
+        <v>31.49079008</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1176135839055747</v>
+        <v>0.1182737565835079</v>
       </c>
       <c r="T3">
-        <v>1.110933303562709</v>
+        <v>1.121145964930265</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>244.487765960869</v>
+        <v>122.2438829804345</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1168136814518377</v>
+        <v>0.1167372148371565</v>
       </c>
       <c r="C4">
-        <v>181.4483913020749</v>
+        <v>179.9900178331906</v>
       </c>
       <c r="D4">
-        <v>175.9143913020749</v>
+        <v>176.1040178331905</v>
       </c>
       <c r="E4">
-        <v>-106.904</v>
+        <v>-105.256</v>
       </c>
       <c r="F4">
-        <v>3.296</v>
+        <v>4.944</v>
       </c>
       <c r="G4">
         <v>8.83</v>
@@ -1609,28 +1609,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M4">
-        <v>0.1657888</v>
+        <v>0.2486832</v>
       </c>
       <c r="N4">
-        <v>20.10087786666666</v>
+        <v>20.01798346666667</v>
       </c>
       <c r="O4">
-        <v>2.010087786666666</v>
+        <v>2.001798346666667</v>
       </c>
       <c r="P4">
-        <v>18.09079008</v>
+        <v>18.01618512</v>
       </c>
       <c r="Q4">
-        <v>31.49079008</v>
+        <v>31.41618512</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1182737565835079</v>
+        <v>0.1189475410692335</v>
       </c>
       <c r="T4">
-        <v>1.121145964930265</v>
+        <v>1.131569196635296</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>122.2438829804345</v>
+        <v>81.49592198695636</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1167372148371565</v>
+        <v>0.1166607482224753</v>
       </c>
       <c r="C5">
-        <v>179.9900178331906</v>
+        <v>178.532053620467</v>
       </c>
       <c r="D5">
-        <v>176.1040178331905</v>
+        <v>176.294053620467</v>
       </c>
       <c r="E5">
-        <v>-105.256</v>
+        <v>-103.608</v>
       </c>
       <c r="F5">
-        <v>4.944</v>
+        <v>6.592000000000001</v>
       </c>
       <c r="G5">
         <v>8.83</v>
@@ -1691,28 +1691,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M5">
-        <v>0.2486832</v>
+        <v>0.3315776</v>
       </c>
       <c r="N5">
-        <v>20.01798346666667</v>
+        <v>19.93508906666667</v>
       </c>
       <c r="O5">
-        <v>2.001798346666667</v>
+        <v>1.993508906666667</v>
       </c>
       <c r="P5">
-        <v>18.01618512</v>
+        <v>17.94158016</v>
       </c>
       <c r="Q5">
-        <v>31.41618512</v>
+        <v>31.34158016</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1189475410692335</v>
+        <v>0.1196353627317451</v>
       </c>
       <c r="T5">
-        <v>1.131569196635296</v>
+        <v>1.142209579000848</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>81.49592198695636</v>
+        <v>61.12194149021727</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1166607482224753</v>
+        <v>0.1165842816077941</v>
       </c>
       <c r="C6">
-        <v>178.532053620467</v>
+        <v>177.0744999902343</v>
       </c>
       <c r="D6">
-        <v>176.294053620467</v>
+        <v>176.4844999902343</v>
       </c>
       <c r="E6">
-        <v>-103.608</v>
+        <v>-101.96</v>
       </c>
       <c r="F6">
-        <v>6.592000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="G6">
         <v>8.83</v>
@@ -1773,28 +1773,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M6">
-        <v>0.3315776</v>
+        <v>0.414472</v>
       </c>
       <c r="N6">
-        <v>19.93508906666667</v>
+        <v>19.85219466666667</v>
       </c>
       <c r="O6">
-        <v>1.993508906666667</v>
+        <v>1.985219466666667</v>
       </c>
       <c r="P6">
-        <v>17.94158016</v>
+        <v>17.8669752</v>
       </c>
       <c r="Q6">
-        <v>31.34158016</v>
+        <v>31.2669752</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1196353627317451</v>
+        <v>0.1203376648503096</v>
       </c>
       <c r="T6">
-        <v>1.142209579000848</v>
+        <v>1.153073969416202</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.12194149021727</v>
+        <v>48.89755319217382</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1165842816077941</v>
+        <v>0.1165078149931129</v>
       </c>
       <c r="C7">
-        <v>177.0744999902343</v>
+        <v>175.6173582745593</v>
       </c>
       <c r="D7">
-        <v>176.4844999902343</v>
+        <v>176.6753582745593</v>
       </c>
       <c r="E7">
-        <v>-101.96</v>
+        <v>-100.312</v>
       </c>
       <c r="F7">
-        <v>8.24</v>
+        <v>9.888000000000002</v>
       </c>
       <c r="G7">
         <v>8.83</v>
@@ -1855,28 +1855,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M7">
-        <v>0.414472</v>
+        <v>0.4973664</v>
       </c>
       <c r="N7">
-        <v>19.85219466666667</v>
+        <v>19.76930026666667</v>
       </c>
       <c r="O7">
-        <v>1.985219466666667</v>
+        <v>1.976930026666667</v>
       </c>
       <c r="P7">
-        <v>17.8669752</v>
+        <v>17.79237024</v>
       </c>
       <c r="Q7">
-        <v>31.2669752</v>
+        <v>31.19237024</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1203376648503096</v>
+        <v>0.1210549095671414</v>
       </c>
       <c r="T7">
-        <v>1.153073969416202</v>
+        <v>1.164169517074436</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.89755319217382</v>
+        <v>40.74796099347817</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1165078149931129</v>
+        <v>0.1164313483784317</v>
       </c>
       <c r="C8">
-        <v>175.6173582745593</v>
+        <v>174.1606298112778</v>
       </c>
       <c r="D8">
-        <v>176.6753582745593</v>
+        <v>176.8666298112778</v>
       </c>
       <c r="E8">
-        <v>-100.312</v>
+        <v>-98.664</v>
       </c>
       <c r="F8">
-        <v>9.888</v>
+        <v>11.536</v>
       </c>
       <c r="G8">
         <v>8.83</v>
@@ -1937,28 +1937,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M8">
-        <v>0.4973664</v>
+        <v>0.5802607999999999</v>
       </c>
       <c r="N8">
-        <v>19.76930026666667</v>
+        <v>19.68640586666666</v>
       </c>
       <c r="O8">
-        <v>1.976930026666667</v>
+        <v>1.968640586666667</v>
       </c>
       <c r="P8">
-        <v>17.79237024</v>
+        <v>17.71776528</v>
       </c>
       <c r="Q8">
-        <v>31.19237024</v>
+        <v>31.11776528</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1210549095671414</v>
+        <v>0.1217875789015395</v>
       </c>
       <c r="T8">
-        <v>1.164169517074436</v>
+        <v>1.175503678660803</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.74796099347818</v>
+        <v>34.92682370869559</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1164313483784317</v>
+        <v>0.1163548817637505</v>
       </c>
       <c r="C9">
-        <v>174.1606298112778</v>
+        <v>172.7043159440252</v>
       </c>
       <c r="D9">
-        <v>176.8666298112778</v>
+        <v>177.0583159440251</v>
       </c>
       <c r="E9">
-        <v>-98.664</v>
+        <v>-97.01600000000001</v>
       </c>
       <c r="F9">
-        <v>11.536</v>
+        <v>13.184</v>
       </c>
       <c r="G9">
         <v>8.83</v>
@@ -2019,28 +2019,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M9">
-        <v>0.5802608</v>
+        <v>0.6631552000000001</v>
       </c>
       <c r="N9">
-        <v>19.68640586666666</v>
+        <v>19.60351146666667</v>
       </c>
       <c r="O9">
-        <v>1.968640586666667</v>
+        <v>1.960351146666667</v>
       </c>
       <c r="P9">
-        <v>17.71776528</v>
+        <v>17.64316032</v>
       </c>
       <c r="Q9">
-        <v>31.11776528</v>
+        <v>31.04316032</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1217875789015395</v>
+        <v>0.1225361758301636</v>
       </c>
       <c r="T9">
-        <v>1.175503678660803</v>
+        <v>1.187084235064266</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.92682370869558</v>
+        <v>30.56097074510863</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1163548817637505</v>
+        <v>0.1162784151490693</v>
       </c>
       <c r="C10">
-        <v>172.7043159440252</v>
+        <v>171.248418022268</v>
       </c>
       <c r="D10">
-        <v>177.0583159440251</v>
+        <v>177.250418022268</v>
       </c>
       <c r="E10">
-        <v>-97.01600000000001</v>
+        <v>-95.36799999999999</v>
       </c>
       <c r="F10">
-        <v>13.184</v>
+        <v>14.832</v>
       </c>
       <c r="G10">
         <v>8.83</v>
@@ -2101,28 +2101,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M10">
-        <v>0.6631552000000001</v>
+        <v>0.7460496</v>
       </c>
       <c r="N10">
-        <v>19.60351146666667</v>
+        <v>19.52061706666667</v>
       </c>
       <c r="O10">
-        <v>1.960351146666667</v>
+        <v>1.952061706666667</v>
       </c>
       <c r="P10">
-        <v>17.64316032</v>
+        <v>17.56855536</v>
       </c>
       <c r="Q10">
-        <v>31.04316032</v>
+        <v>30.96855536</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1225361758301636</v>
+        <v>0.1233012254385377</v>
       </c>
       <c r="T10">
-        <v>1.187084235064266</v>
+        <v>1.198919309190881</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.56097074510863</v>
+        <v>27.16530732898546</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1162784151490693</v>
+        <v>0.1162019485343881</v>
       </c>
       <c r="C11">
-        <v>171.248418022268</v>
+        <v>169.7929374013356</v>
       </c>
       <c r="D11">
-        <v>177.250418022268</v>
+        <v>177.4429374013355</v>
       </c>
       <c r="E11">
-        <v>-95.36799999999999</v>
+        <v>-93.72</v>
       </c>
       <c r="F11">
-        <v>14.832</v>
+        <v>16.48</v>
       </c>
       <c r="G11">
         <v>8.83</v>
@@ -2183,28 +2183,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M11">
-        <v>0.7460496</v>
+        <v>0.828944</v>
       </c>
       <c r="N11">
-        <v>19.52061706666667</v>
+        <v>19.43772266666667</v>
       </c>
       <c r="O11">
-        <v>1.952061706666667</v>
+        <v>1.943772266666667</v>
       </c>
       <c r="P11">
-        <v>17.56855536</v>
+        <v>17.4939504</v>
       </c>
       <c r="Q11">
-        <v>30.96855536</v>
+        <v>30.8939504</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1233012254385377</v>
+        <v>0.1240832761493201</v>
       </c>
       <c r="T11">
-        <v>1.198919309190881</v>
+        <v>1.211017384964755</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.16530732898546</v>
+        <v>24.44877659608691</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1162019485343881</v>
+        <v>0.1161254819197069</v>
       </c>
       <c r="C12">
-        <v>169.7929374013356</v>
+        <v>168.3378754424522</v>
       </c>
       <c r="D12">
-        <v>177.4429374013355</v>
+        <v>177.6358754424521</v>
       </c>
       <c r="E12">
-        <v>-93.72</v>
+        <v>-92.072</v>
       </c>
       <c r="F12">
-        <v>16.48</v>
+        <v>18.128</v>
       </c>
       <c r="G12">
         <v>8.83</v>
@@ -2265,28 +2265,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M12">
-        <v>0.828944</v>
+        <v>0.9118383999999999</v>
       </c>
       <c r="N12">
-        <v>19.43772266666667</v>
+        <v>19.35482826666667</v>
       </c>
       <c r="O12">
-        <v>1.943772266666667</v>
+        <v>1.935482826666667</v>
       </c>
       <c r="P12">
-        <v>17.4939504</v>
+        <v>17.41934544</v>
       </c>
       <c r="Q12">
-        <v>30.8939504</v>
+        <v>30.81934544</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1240832761493201</v>
+        <v>0.1248829010333786</v>
       </c>
       <c r="T12">
-        <v>1.211017384964755</v>
+        <v>1.223387327609951</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.44877659608691</v>
+        <v>22.22616054189719</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1161254819197069</v>
+        <v>0.1160490153050257</v>
       </c>
       <c r="C13">
-        <v>168.3378754424522</v>
+        <v>166.8832335127686</v>
       </c>
       <c r="D13">
-        <v>177.6358754424521</v>
+        <v>177.8292335127686</v>
       </c>
       <c r="E13">
-        <v>-92.072</v>
+        <v>-90.42400000000001</v>
       </c>
       <c r="F13">
-        <v>18.128</v>
+        <v>19.776</v>
       </c>
       <c r="G13">
         <v>8.83</v>
@@ -2347,28 +2347,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M13">
-        <v>0.9118383999999999</v>
+        <v>0.9947328</v>
       </c>
       <c r="N13">
-        <v>19.35482826666667</v>
+        <v>19.27193386666666</v>
       </c>
       <c r="O13">
-        <v>1.935482826666667</v>
+        <v>1.927193386666667</v>
       </c>
       <c r="P13">
-        <v>17.41934544</v>
+        <v>17.34474048</v>
       </c>
       <c r="Q13">
-        <v>30.81934544</v>
+        <v>30.74474048</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1248829010333786</v>
+        <v>0.1257006992102565</v>
       </c>
       <c r="T13">
-        <v>1.223387327609951</v>
+        <v>1.236038405315266</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.22616054189719</v>
+        <v>20.37398049673909</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1160490153050257</v>
+        <v>0.1159725486903445</v>
       </c>
       <c r="C14">
-        <v>166.8832335127686</v>
+        <v>165.4290129853952</v>
       </c>
       <c r="D14">
-        <v>177.8292335127686</v>
+        <v>178.0230129853952</v>
       </c>
       <c r="E14">
-        <v>-90.42400000000001</v>
+        <v>-88.776</v>
       </c>
       <c r="F14">
-        <v>19.776</v>
+        <v>21.424</v>
       </c>
       <c r="G14">
         <v>8.83</v>
@@ -2429,28 +2429,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M14">
-        <v>0.9947328</v>
+        <v>1.0776272</v>
       </c>
       <c r="N14">
-        <v>19.27193386666666</v>
+        <v>19.18903946666667</v>
       </c>
       <c r="O14">
-        <v>1.927193386666667</v>
+        <v>1.918903946666667</v>
       </c>
       <c r="P14">
-        <v>17.34474048</v>
+        <v>17.27013552</v>
       </c>
       <c r="Q14">
-        <v>30.74474048</v>
+        <v>30.67013552</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1257006992102565</v>
+        <v>0.1265372973452236</v>
       </c>
       <c r="T14">
-        <v>1.236038405315266</v>
+        <v>1.248980312393117</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.37398049673909</v>
+        <v>18.80675122775916</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1159725486903445</v>
+        <v>0.1158960820756633</v>
       </c>
       <c r="C15">
-        <v>165.4290129853952</v>
+        <v>163.9752152394334</v>
       </c>
       <c r="D15">
-        <v>178.0230129853952</v>
+        <v>178.2172152394334</v>
       </c>
       <c r="E15">
-        <v>-88.776</v>
+        <v>-87.128</v>
       </c>
       <c r="F15">
-        <v>21.424</v>
+        <v>23.072</v>
       </c>
       <c r="G15">
         <v>8.83</v>
@@ -2511,28 +2511,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M15">
-        <v>1.0776272</v>
+        <v>1.1605216</v>
       </c>
       <c r="N15">
-        <v>19.18903946666667</v>
+        <v>19.10614506666667</v>
       </c>
       <c r="O15">
-        <v>1.918903946666667</v>
+        <v>1.910614506666667</v>
       </c>
       <c r="P15">
-        <v>17.27013552</v>
+        <v>17.19553056</v>
       </c>
       <c r="Q15">
-        <v>30.67013552</v>
+        <v>30.59553056</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1265372973452236</v>
+        <v>0.1273933512507713</v>
       </c>
       <c r="T15">
-        <v>1.248980312393117</v>
+        <v>1.262223194054173</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.80675122775916</v>
+        <v>17.46341185434779</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1158960820756633</v>
+        <v>0.1158196154609821</v>
       </c>
       <c r="C16">
-        <v>163.9752152394334</v>
+        <v>162.5218416600092</v>
       </c>
       <c r="D16">
-        <v>178.2172152394334</v>
+        <v>178.4118416600092</v>
       </c>
       <c r="E16">
-        <v>-87.128</v>
+        <v>-85.47999999999999</v>
       </c>
       <c r="F16">
-        <v>23.072</v>
+        <v>24.72000000000001</v>
       </c>
       <c r="G16">
         <v>8.83</v>
@@ -2593,28 +2593,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M16">
-        <v>1.1605216</v>
+        <v>1.243416</v>
       </c>
       <c r="N16">
-        <v>19.10614506666667</v>
+        <v>19.02325066666667</v>
       </c>
       <c r="O16">
-        <v>1.910614506666667</v>
+        <v>1.902325066666667</v>
       </c>
       <c r="P16">
-        <v>17.19553056</v>
+        <v>17.1209256</v>
       </c>
       <c r="Q16">
-        <v>30.59553056</v>
+        <v>30.5209256</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1273933512507713</v>
+        <v>0.1282695476011554</v>
       </c>
       <c r="T16">
-        <v>1.262223194054173</v>
+        <v>1.275777672930785</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.46341185434779</v>
+        <v>16.29918439739127</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1158196154609821</v>
+        <v>0.1157431488463009</v>
       </c>
       <c r="C17">
-        <v>162.5218416600092</v>
+        <v>161.0688936383061</v>
       </c>
       <c r="D17">
-        <v>178.4118416600092</v>
+        <v>178.606893638306</v>
       </c>
       <c r="E17">
-        <v>-85.48</v>
+        <v>-83.83199999999999</v>
       </c>
       <c r="F17">
-        <v>24.72</v>
+        <v>26.368</v>
       </c>
       <c r="G17">
         <v>8.83</v>
@@ -2675,28 +2675,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M17">
-        <v>1.243416</v>
+        <v>1.3263104</v>
       </c>
       <c r="N17">
-        <v>19.02325066666667</v>
+        <v>18.94035626666667</v>
       </c>
       <c r="O17">
-        <v>1.902325066666667</v>
+        <v>1.894035626666667</v>
       </c>
       <c r="P17">
-        <v>17.1209256</v>
+        <v>17.04632064</v>
       </c>
       <c r="Q17">
-        <v>30.5209256</v>
+        <v>30.44632064</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1282695476011554</v>
+        <v>0.1291666057694059</v>
       </c>
       <c r="T17">
-        <v>1.275777672930785</v>
+        <v>1.289654877494934</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.29918439739127</v>
+        <v>15.28048537255432</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1157431488463009</v>
+        <v>0.1156666822316197</v>
       </c>
       <c r="C18">
-        <v>161.0688936383061</v>
+        <v>159.6163725715975</v>
       </c>
       <c r="D18">
-        <v>178.606893638306</v>
+        <v>178.8023725715975</v>
       </c>
       <c r="E18">
-        <v>-83.83199999999999</v>
+        <v>-82.184</v>
       </c>
       <c r="F18">
-        <v>26.368</v>
+        <v>28.01600000000001</v>
       </c>
       <c r="G18">
         <v>8.83</v>
@@ -2757,28 +2757,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M18">
-        <v>1.3263104</v>
+        <v>1.4092048</v>
       </c>
       <c r="N18">
-        <v>18.94035626666667</v>
+        <v>18.85746186666666</v>
       </c>
       <c r="O18">
-        <v>1.894035626666667</v>
+        <v>1.885746186666666</v>
       </c>
       <c r="P18">
-        <v>17.04632064</v>
+        <v>16.97171568</v>
       </c>
       <c r="Q18">
-        <v>30.44632064</v>
+        <v>30.37171568</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1291666057694059</v>
+        <v>0.1300852797971322</v>
       </c>
       <c r="T18">
-        <v>1.289654877494934</v>
+        <v>1.303866472530508</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.28048537255432</v>
+        <v>14.38163329181583</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1156666822316197</v>
+        <v>0.1155902156169385</v>
       </c>
       <c r="C19">
-        <v>159.6163725715975</v>
+        <v>158.164279863281</v>
       </c>
       <c r="D19">
-        <v>178.8023725715975</v>
+        <v>178.998279863281</v>
       </c>
       <c r="E19">
-        <v>-82.184</v>
+        <v>-80.536</v>
       </c>
       <c r="F19">
-        <v>28.01600000000001</v>
+        <v>29.66400000000001</v>
       </c>
       <c r="G19">
         <v>8.83</v>
@@ -2839,28 +2839,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M19">
-        <v>1.4092048</v>
+        <v>1.4920992</v>
       </c>
       <c r="N19">
-        <v>18.85746186666666</v>
+        <v>18.77456746666667</v>
       </c>
       <c r="O19">
-        <v>1.885746186666666</v>
+        <v>1.877456746666667</v>
       </c>
       <c r="P19">
-        <v>16.97171568</v>
+        <v>16.89711072</v>
       </c>
       <c r="Q19">
-        <v>30.37171568</v>
+        <v>30.29711072</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1300852797971322</v>
+        <v>0.1310263605084616</v>
       </c>
       <c r="T19">
-        <v>1.303866472530508</v>
+        <v>1.318424691835243</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.38163329181583</v>
+        <v>13.58265366449273</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1155902156169385</v>
+        <v>0.1157702490022573</v>
       </c>
       <c r="C20">
-        <v>158.164279863281</v>
+        <v>156.0557174564072</v>
       </c>
       <c r="D20">
-        <v>178.998279863281</v>
+        <v>178.5377174564072</v>
       </c>
       <c r="E20">
-        <v>-80.536</v>
+        <v>-78.88800000000001</v>
       </c>
       <c r="F20">
-        <v>29.664</v>
+        <v>31.312</v>
       </c>
       <c r="G20">
         <v>8.83</v>
@@ -2921,45 +2921,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M20">
-        <v>1.4920992</v>
+        <v>1.6219616</v>
       </c>
       <c r="N20">
-        <v>18.77456746666667</v>
+        <v>18.64470506666667</v>
       </c>
       <c r="O20">
-        <v>1.877456746666667</v>
+        <v>1.864470506666667</v>
       </c>
       <c r="P20">
-        <v>16.89711072</v>
+        <v>16.78023456</v>
       </c>
       <c r="Q20">
-        <v>30.29711072</v>
+        <v>30.18023456</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1310263605084616</v>
+        <v>0.1319906777805646</v>
       </c>
       <c r="T20">
-        <v>1.318424691835243</v>
+        <v>1.333342373345033</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.58265366449273</v>
+        <v>12.49515812622609</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1157702490022573</v>
+        <v>0.1157072823875761</v>
       </c>
       <c r="C21">
-        <v>156.0557174564072</v>
+        <v>154.5685292527922</v>
       </c>
       <c r="D21">
-        <v>178.5377174564072</v>
+        <v>178.6985292527922</v>
       </c>
       <c r="E21">
-        <v>-78.88800000000001</v>
+        <v>-77.24000000000001</v>
       </c>
       <c r="F21">
-        <v>31.312</v>
+        <v>32.96</v>
       </c>
       <c r="G21">
         <v>8.83</v>
@@ -3003,28 +3003,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M21">
-        <v>1.6219616</v>
+        <v>1.707328</v>
       </c>
       <c r="N21">
-        <v>18.64470506666667</v>
+        <v>18.55933866666667</v>
       </c>
       <c r="O21">
-        <v>1.864470506666667</v>
+        <v>1.855933866666667</v>
       </c>
       <c r="P21">
-        <v>16.78023456</v>
+        <v>16.7034048</v>
       </c>
       <c r="Q21">
-        <v>30.18023456</v>
+        <v>30.1034048</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1319906777805646</v>
+        <v>0.1329791029844702</v>
       </c>
       <c r="T21">
-        <v>1.333342373345033</v>
+        <v>1.348632996892568</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.49515812622609</v>
+        <v>11.87040021991478</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1157072823875761</v>
+        <v>0.1156443157728949</v>
       </c>
       <c r="C22">
-        <v>154.5685292527922</v>
+        <v>153.0816310018901</v>
       </c>
       <c r="D22">
-        <v>178.6985292527922</v>
+        <v>178.8596310018901</v>
       </c>
       <c r="E22">
-        <v>-77.24000000000001</v>
+        <v>-75.592</v>
       </c>
       <c r="F22">
-        <v>32.96</v>
+        <v>34.608</v>
       </c>
       <c r="G22">
         <v>8.83</v>
@@ -3085,28 +3085,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M22">
-        <v>1.707328</v>
+        <v>1.7926944</v>
       </c>
       <c r="N22">
-        <v>18.55933866666667</v>
+        <v>18.47397226666666</v>
       </c>
       <c r="O22">
-        <v>1.855933866666667</v>
+        <v>1.847397226666667</v>
       </c>
       <c r="P22">
-        <v>16.7034048</v>
+        <v>16.62657504</v>
       </c>
       <c r="Q22">
-        <v>30.1034048</v>
+        <v>30.02657504</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1329791029844702</v>
+        <v>0.1339925516112594</v>
       </c>
       <c r="T22">
-        <v>1.348632996892568</v>
+        <v>1.364310724833711</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.87040021991478</v>
+        <v>11.3051430665855</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1156443157728949</v>
+        <v>0.1155813491582137</v>
       </c>
       <c r="C23">
-        <v>153.0816310018901</v>
+        <v>151.5950234886101</v>
       </c>
       <c r="D23">
-        <v>178.8596310018901</v>
+        <v>179.02102348861</v>
       </c>
       <c r="E23">
-        <v>-75.592</v>
+        <v>-73.944</v>
       </c>
       <c r="F23">
-        <v>34.608</v>
+        <v>36.256</v>
       </c>
       <c r="G23">
         <v>8.83</v>
@@ -3167,28 +3167,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M23">
-        <v>1.7926944</v>
+        <v>1.8780608</v>
       </c>
       <c r="N23">
-        <v>18.47397226666666</v>
+        <v>18.38860586666667</v>
       </c>
       <c r="O23">
-        <v>1.847397226666667</v>
+        <v>1.838860586666667</v>
       </c>
       <c r="P23">
-        <v>16.62657504</v>
+        <v>16.54974528</v>
       </c>
       <c r="Q23">
-        <v>30.02657504</v>
+        <v>29.94974528</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1339925516112594</v>
+        <v>0.135031986100274</v>
       </c>
       <c r="T23">
-        <v>1.364310724833711</v>
+        <v>1.380390445798986</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.3051430665855</v>
+        <v>10.79127292719526</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1155813491582137</v>
+        <v>0.1155183825435325</v>
       </c>
       <c r="C24">
-        <v>151.5950234886101</v>
+        <v>150.1087075006969</v>
       </c>
       <c r="D24">
-        <v>179.02102348861</v>
+        <v>179.1827075006968</v>
       </c>
       <c r="E24">
-        <v>-73.944</v>
+        <v>-72.29599999999999</v>
       </c>
       <c r="F24">
-        <v>36.256</v>
+        <v>37.904</v>
       </c>
       <c r="G24">
         <v>8.83</v>
@@ -3249,28 +3249,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M24">
-        <v>1.8780608</v>
+        <v>1.9634272</v>
       </c>
       <c r="N24">
-        <v>18.38860586666667</v>
+        <v>18.30323946666666</v>
       </c>
       <c r="O24">
-        <v>1.838860586666667</v>
+        <v>1.830323946666667</v>
       </c>
       <c r="P24">
-        <v>16.54974528</v>
+        <v>16.47291552</v>
       </c>
       <c r="Q24">
-        <v>29.94974528</v>
+        <v>29.87291552</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.135031986100274</v>
+        <v>0.1360984188877046</v>
       </c>
       <c r="T24">
-        <v>1.380390445798986</v>
+        <v>1.396887821854269</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.79127292719526</v>
+        <v>10.32208714775198</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1155183825435325</v>
+        <v>0.1154554159288513</v>
       </c>
       <c r="C25">
-        <v>150.1087075006969</v>
+        <v>148.6226838287437</v>
       </c>
       <c r="D25">
-        <v>179.1827075006968</v>
+        <v>179.3446838287437</v>
       </c>
       <c r="E25">
-        <v>-72.29599999999999</v>
+        <v>-70.648</v>
       </c>
       <c r="F25">
-        <v>37.904</v>
+        <v>39.55200000000001</v>
       </c>
       <c r="G25">
         <v>8.83</v>
@@ -3331,28 +3331,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M25">
-        <v>1.9634272</v>
+        <v>2.0487936</v>
       </c>
       <c r="N25">
-        <v>18.30323946666666</v>
+        <v>18.21787306666667</v>
       </c>
       <c r="O25">
-        <v>1.830323946666667</v>
+        <v>1.821787306666667</v>
       </c>
       <c r="P25">
-        <v>16.47291552</v>
+        <v>16.39608576</v>
       </c>
       <c r="Q25">
-        <v>29.87291552</v>
+        <v>29.79608576</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1360984188877046</v>
+        <v>0.137192915695857</v>
       </c>
       <c r="T25">
-        <v>1.396887821854269</v>
+        <v>1.41381933938469</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.32208714775198</v>
+        <v>9.892000183262319</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1154554159288513</v>
+        <v>0.1157749493141701</v>
       </c>
       <c r="C26">
-        <v>148.6226838287437</v>
+        <v>146.1557248366416</v>
       </c>
       <c r="D26">
-        <v>179.3446838287437</v>
+        <v>178.5257248366416</v>
       </c>
       <c r="E26">
-        <v>-70.648</v>
+        <v>-69</v>
       </c>
       <c r="F26">
-        <v>39.552</v>
+        <v>41.2</v>
       </c>
       <c r="G26">
         <v>8.83</v>
@@ -3413,45 +3413,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M26">
-        <v>2.0487936</v>
+        <v>2.2042</v>
       </c>
       <c r="N26">
-        <v>18.21787306666667</v>
+        <v>18.06246666666667</v>
       </c>
       <c r="O26">
-        <v>1.821787306666667</v>
+        <v>1.806246666666667</v>
       </c>
       <c r="P26">
-        <v>16.39608576</v>
+        <v>16.25622</v>
       </c>
       <c r="Q26">
-        <v>29.79608576</v>
+        <v>29.65622</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.137192915695857</v>
+        <v>0.1383165990855602</v>
       </c>
       <c r="T26">
-        <v>1.41381933938469</v>
+        <v>1.431202364049256</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.89200018326232</v>
+        <v>9.194567946042403</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1157749493141701</v>
+        <v>0.1157272826994889</v>
       </c>
       <c r="C27">
-        <v>146.1557248366416</v>
+        <v>144.6294186392313</v>
       </c>
       <c r="D27">
-        <v>178.5257248366416</v>
+        <v>178.6474186392313</v>
       </c>
       <c r="E27">
-        <v>-69</v>
+        <v>-67.352</v>
       </c>
       <c r="F27">
-        <v>41.2</v>
+        <v>42.84800000000001</v>
       </c>
       <c r="G27">
         <v>8.83</v>
@@ -3495,28 +3495,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M27">
-        <v>2.2042</v>
+        <v>2.292368</v>
       </c>
       <c r="N27">
-        <v>18.06246666666667</v>
+        <v>17.97429866666667</v>
       </c>
       <c r="O27">
-        <v>1.806246666666667</v>
+        <v>1.797429866666667</v>
       </c>
       <c r="P27">
-        <v>16.25622</v>
+        <v>16.1768688</v>
       </c>
       <c r="Q27">
-        <v>29.65622</v>
+        <v>29.5768688</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1383165990855602</v>
+        <v>0.1394706522966067</v>
       </c>
       <c r="T27">
-        <v>1.431202364049256</v>
+        <v>1.449055200191242</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.194567946042403</v>
+        <v>8.840930717348463</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1157272826994889</v>
+        <v>0.1156796160848077</v>
       </c>
       <c r="C28">
-        <v>144.6294186392313</v>
+        <v>143.103278462527</v>
       </c>
       <c r="D28">
-        <v>178.6474186392313</v>
+        <v>178.769278462527</v>
       </c>
       <c r="E28">
-        <v>-67.352</v>
+        <v>-65.70399999999999</v>
       </c>
       <c r="F28">
-        <v>42.84800000000001</v>
+        <v>44.49600000000001</v>
       </c>
       <c r="G28">
         <v>8.83</v>
@@ -3577,28 +3577,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M28">
-        <v>2.292368</v>
+        <v>2.380536000000001</v>
       </c>
       <c r="N28">
-        <v>17.97429866666667</v>
+        <v>17.88613066666667</v>
       </c>
       <c r="O28">
-        <v>1.797429866666667</v>
+        <v>1.788613066666667</v>
       </c>
       <c r="P28">
-        <v>16.1768688</v>
+        <v>16.0975176</v>
       </c>
       <c r="Q28">
-        <v>29.5768688</v>
+        <v>29.4975176</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1394706522966067</v>
+        <v>0.1406563234038462</v>
       </c>
       <c r="T28">
-        <v>1.449055200191242</v>
+        <v>1.46739715513164</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.840930717348463</v>
+        <v>8.513488838928151</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1156796160848077</v>
+        <v>0.1156319494701265</v>
       </c>
       <c r="C29">
-        <v>143.103278462527</v>
+        <v>141.5773046465012</v>
       </c>
       <c r="D29">
-        <v>178.769278462527</v>
+        <v>178.8913046465012</v>
       </c>
       <c r="E29">
-        <v>-65.70399999999999</v>
+        <v>-64.056</v>
       </c>
       <c r="F29">
-        <v>44.49600000000001</v>
+        <v>46.14400000000001</v>
       </c>
       <c r="G29">
         <v>8.83</v>
@@ -3659,28 +3659,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M29">
-        <v>2.380536000000001</v>
+        <v>2.468704</v>
       </c>
       <c r="N29">
-        <v>17.88613066666667</v>
+        <v>17.79796266666667</v>
       </c>
       <c r="O29">
-        <v>1.788613066666667</v>
+        <v>1.779796266666667</v>
       </c>
       <c r="P29">
-        <v>16.0975176</v>
+        <v>16.0181664</v>
       </c>
       <c r="Q29">
-        <v>29.4975176</v>
+        <v>29.4181664</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1406563234038462</v>
+        <v>0.1418749298196202</v>
       </c>
       <c r="T29">
-        <v>1.46739715513164</v>
+        <v>1.486248608820381</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.513488838928151</v>
+        <v>8.20943566610929</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1156319494701265</v>
+        <v>0.1155842828554453</v>
       </c>
       <c r="C30">
-        <v>141.5773046465012</v>
+        <v>140.0514975320548</v>
       </c>
       <c r="D30">
-        <v>178.8913046465012</v>
+        <v>179.0134975320548</v>
       </c>
       <c r="E30">
-        <v>-64.056</v>
+        <v>-62.40799999999999</v>
       </c>
       <c r="F30">
-        <v>46.14400000000001</v>
+        <v>47.79200000000001</v>
       </c>
       <c r="G30">
         <v>8.83</v>
@@ -3741,28 +3741,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M30">
-        <v>2.468704</v>
+        <v>2.556872</v>
       </c>
       <c r="N30">
-        <v>17.79796266666667</v>
+        <v>17.70979466666667</v>
       </c>
       <c r="O30">
-        <v>1.779796266666667</v>
+        <v>1.770979466666667</v>
       </c>
       <c r="P30">
-        <v>16.0181664</v>
+        <v>15.9388152</v>
       </c>
       <c r="Q30">
-        <v>29.4181664</v>
+        <v>29.3388152</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1418749298196202</v>
+        <v>0.1431278631766836</v>
       </c>
       <c r="T30">
-        <v>1.486248608820381</v>
+        <v>1.505631089373594</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.20943566610929</v>
+        <v>7.926351677622762</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1155842828554453</v>
+        <v>0.1155366162407641</v>
       </c>
       <c r="C31">
-        <v>140.0514975320548</v>
+        <v>138.5258574610215</v>
       </c>
       <c r="D31">
-        <v>179.0134975320548</v>
+        <v>179.1358574610215</v>
       </c>
       <c r="E31">
-        <v>-62.408</v>
+        <v>-60.76</v>
       </c>
       <c r="F31">
-        <v>47.792</v>
+        <v>49.44</v>
       </c>
       <c r="G31">
         <v>8.83</v>
@@ -3823,28 +3823,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M31">
-        <v>2.556872</v>
+        <v>2.64504</v>
       </c>
       <c r="N31">
-        <v>17.70979466666667</v>
+        <v>17.62162666666666</v>
       </c>
       <c r="O31">
-        <v>1.770979466666667</v>
+        <v>1.762162666666667</v>
       </c>
       <c r="P31">
-        <v>15.9388152</v>
+        <v>15.859464</v>
       </c>
       <c r="Q31">
-        <v>29.3388152</v>
+        <v>29.259464</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1431278631766836</v>
+        <v>0.144416594629663</v>
       </c>
       <c r="T31">
-        <v>1.505631089373594</v>
+        <v>1.52556735508547</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.926351677622762</v>
+        <v>7.662139955035335</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1155366162407641</v>
+        <v>0.1157121496260829</v>
       </c>
       <c r="C32">
-        <v>138.5258574610215</v>
+        <v>136.4280883771027</v>
       </c>
       <c r="D32">
-        <v>179.1358574610215</v>
+        <v>178.6860883771027</v>
       </c>
       <c r="E32">
-        <v>-60.76</v>
+        <v>-59.112</v>
       </c>
       <c r="F32">
-        <v>49.44</v>
+        <v>51.088</v>
       </c>
       <c r="G32">
         <v>8.83</v>
@@ -3905,45 +3905,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M32">
-        <v>2.64504</v>
+        <v>2.7740784</v>
       </c>
       <c r="N32">
-        <v>17.62162666666666</v>
+        <v>17.49258826666667</v>
       </c>
       <c r="O32">
-        <v>1.762162666666667</v>
+        <v>1.749258826666667</v>
       </c>
       <c r="P32">
-        <v>15.859464</v>
+        <v>15.74332944</v>
       </c>
       <c r="Q32">
-        <v>29.259464</v>
+        <v>29.14332944</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.144416594629663</v>
+        <v>0.1457426806175115</v>
       </c>
       <c r="T32">
-        <v>1.52556735508547</v>
+        <v>1.546081483571604</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.662139955035335</v>
+        <v>7.30572959533756</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1157121496260829</v>
+        <v>0.1156716830114017</v>
       </c>
       <c r="C33">
-        <v>136.4280883771027</v>
+        <v>134.8835755234774</v>
       </c>
       <c r="D33">
-        <v>178.6860883771027</v>
+        <v>178.7895755234774</v>
       </c>
       <c r="E33">
-        <v>-59.112</v>
+        <v>-57.464</v>
       </c>
       <c r="F33">
-        <v>51.088</v>
+        <v>52.736</v>
       </c>
       <c r="G33">
         <v>8.83</v>
@@ -3987,28 +3987,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M33">
-        <v>2.7740784</v>
+        <v>2.8635648</v>
       </c>
       <c r="N33">
-        <v>17.49258826666667</v>
+        <v>17.40310186666667</v>
       </c>
       <c r="O33">
-        <v>1.749258826666667</v>
+        <v>1.740310186666667</v>
       </c>
       <c r="P33">
-        <v>15.74332944</v>
+        <v>15.66279168</v>
       </c>
       <c r="Q33">
-        <v>29.14332944</v>
+        <v>29.06279168</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1457426806175115</v>
+        <v>0.1471077691344143</v>
       </c>
       <c r="T33">
-        <v>1.546081483571604</v>
+        <v>1.567198968777918</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.30572959533756</v>
+        <v>7.077425545483261</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1156716830114017</v>
+        <v>0.1156312163967205</v>
       </c>
       <c r="C34">
-        <v>134.8835755234774</v>
+        <v>133.3391826097499</v>
       </c>
       <c r="D34">
-        <v>178.7895755234774</v>
+        <v>178.8931826097499</v>
       </c>
       <c r="E34">
-        <v>-57.464</v>
+        <v>-55.816</v>
       </c>
       <c r="F34">
-        <v>52.736</v>
+        <v>54.38400000000001</v>
       </c>
       <c r="G34">
         <v>8.83</v>
@@ -4069,28 +4069,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M34">
-        <v>2.8635648</v>
+        <v>2.9530512</v>
       </c>
       <c r="N34">
-        <v>17.40310186666667</v>
+        <v>17.31361546666666</v>
       </c>
       <c r="O34">
-        <v>1.740310186666667</v>
+        <v>1.731361546666667</v>
       </c>
       <c r="P34">
-        <v>15.66279168</v>
+        <v>15.58225392</v>
       </c>
       <c r="Q34">
-        <v>29.06279168</v>
+        <v>28.98225392</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1471077691344143</v>
+        <v>0.1485136065622694</v>
       </c>
       <c r="T34">
-        <v>1.567198968777918</v>
+        <v>1.588946826676958</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.077425545483261</v>
+        <v>6.86295810471104</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1156312163967205</v>
+        <v>0.1155907497820393</v>
       </c>
       <c r="C35">
-        <v>133.3391826097499</v>
+        <v>131.7949098445534</v>
       </c>
       <c r="D35">
-        <v>178.8931826097499</v>
+        <v>178.9969098445534</v>
       </c>
       <c r="E35">
-        <v>-55.816</v>
+        <v>-54.16799999999999</v>
       </c>
       <c r="F35">
-        <v>54.38400000000001</v>
+        <v>56.03200000000001</v>
       </c>
       <c r="G35">
         <v>8.83</v>
@@ -4151,28 +4151,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M35">
-        <v>2.9530512</v>
+        <v>3.042537600000001</v>
       </c>
       <c r="N35">
-        <v>17.31361546666666</v>
+        <v>17.22412906666667</v>
       </c>
       <c r="O35">
-        <v>1.731361546666667</v>
+        <v>1.722412906666667</v>
       </c>
       <c r="P35">
-        <v>15.58225392</v>
+        <v>15.50171616</v>
       </c>
       <c r="Q35">
-        <v>28.98225392</v>
+        <v>28.90171616</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1485136065622694</v>
+        <v>0.149962045124302</v>
       </c>
       <c r="T35">
-        <v>1.588946826676958</v>
+        <v>1.611353710572939</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.86295810471104</v>
+        <v>6.661106395748951</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1155907497820393</v>
+        <v>0.1155502831673581</v>
       </c>
       <c r="C36">
-        <v>131.7949098445534</v>
+        <v>130.2507574370059</v>
       </c>
       <c r="D36">
-        <v>178.9969098445534</v>
+        <v>179.1007574370059</v>
       </c>
       <c r="E36">
-        <v>-54.16799999999999</v>
+        <v>-52.52</v>
       </c>
       <c r="F36">
-        <v>56.03200000000001</v>
+        <v>57.68000000000001</v>
       </c>
       <c r="G36">
         <v>8.83</v>
@@ -4233,28 +4233,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M36">
-        <v>3.042537600000001</v>
+        <v>3.132024</v>
       </c>
       <c r="N36">
-        <v>17.22412906666667</v>
+        <v>17.13464266666666</v>
       </c>
       <c r="O36">
-        <v>1.722412906666667</v>
+        <v>1.713464266666667</v>
       </c>
       <c r="P36">
-        <v>15.50171616</v>
+        <v>15.4211784</v>
       </c>
       <c r="Q36">
-        <v>28.90171616</v>
+        <v>28.8211784</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.149962045124302</v>
+        <v>0.1514550510267048</v>
       </c>
       <c r="T36">
-        <v>1.611353710572939</v>
+        <v>1.634450037050333</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.661106395748951</v>
+        <v>6.470789070156123</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1155502831673581</v>
+        <v>0.1155098165526769</v>
       </c>
       <c r="C37">
-        <v>130.2507574370059</v>
+        <v>128.7067255967103</v>
       </c>
       <c r="D37">
-        <v>179.1007574370059</v>
+        <v>179.2047255967103</v>
       </c>
       <c r="E37">
-        <v>-52.52</v>
+        <v>-50.87199999999999</v>
       </c>
       <c r="F37">
-        <v>57.68000000000001</v>
+        <v>59.32800000000001</v>
       </c>
       <c r="G37">
         <v>8.83</v>
@@ -4315,28 +4315,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M37">
-        <v>3.132024</v>
+        <v>3.221510400000001</v>
       </c>
       <c r="N37">
-        <v>17.13464266666666</v>
+        <v>17.04515626666667</v>
       </c>
       <c r="O37">
-        <v>1.713464266666667</v>
+        <v>1.704515626666667</v>
       </c>
       <c r="P37">
-        <v>15.4211784</v>
+        <v>15.34064064</v>
       </c>
       <c r="Q37">
-        <v>28.8211784</v>
+        <v>28.74064064</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1514550510267048</v>
+        <v>0.1529947133635577</v>
       </c>
       <c r="T37">
-        <v>1.634450037050333</v>
+        <v>1.658268123730147</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.470789070156123</v>
+        <v>6.291044929318454</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1155098165526769</v>
+        <v>0.1154693499379957</v>
       </c>
       <c r="C38">
-        <v>128.7067255967103</v>
+        <v>127.1628145337569</v>
       </c>
       <c r="D38">
-        <v>179.2047255967103</v>
+        <v>179.3088145337568</v>
       </c>
       <c r="E38">
-        <v>-50.872</v>
+        <v>-49.224</v>
       </c>
       <c r="F38">
-        <v>59.328</v>
+        <v>60.97600000000001</v>
       </c>
       <c r="G38">
         <v>8.83</v>
@@ -4397,28 +4397,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M38">
-        <v>3.2215104</v>
+        <v>3.3109968</v>
       </c>
       <c r="N38">
-        <v>17.04515626666667</v>
+        <v>16.95566986666666</v>
       </c>
       <c r="O38">
-        <v>1.704515626666667</v>
+        <v>1.695566986666666</v>
       </c>
       <c r="P38">
-        <v>15.34064064</v>
+        <v>15.26010288</v>
       </c>
       <c r="Q38">
-        <v>28.74064064</v>
+        <v>28.66010288</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1529947133635577</v>
+        <v>0.1545832538698345</v>
       </c>
       <c r="T38">
-        <v>1.658268123730147</v>
+        <v>1.682842340145828</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.291044929318454</v>
+        <v>6.121016687985522</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1154693499379957</v>
+        <v>0.1157708833233145</v>
       </c>
       <c r="C39">
-        <v>127.1628145337569</v>
+        <v>124.7420989226928</v>
       </c>
       <c r="D39">
-        <v>179.3088145337568</v>
+        <v>178.5360989226928</v>
       </c>
       <c r="E39">
-        <v>-49.224</v>
+        <v>-47.576</v>
       </c>
       <c r="F39">
-        <v>60.97600000000001</v>
+        <v>62.624</v>
       </c>
       <c r="G39">
         <v>8.83</v>
@@ -4479,45 +4479,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M39">
-        <v>3.3109968</v>
+        <v>3.4631072</v>
       </c>
       <c r="N39">
-        <v>16.95566986666666</v>
+        <v>16.80355946666667</v>
       </c>
       <c r="O39">
-        <v>1.695566986666666</v>
+        <v>1.680355946666667</v>
       </c>
       <c r="P39">
-        <v>15.26010288</v>
+        <v>15.12320352</v>
       </c>
       <c r="Q39">
-        <v>28.66010288</v>
+        <v>28.52320352</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1545832538698345</v>
+        <v>0.1562230376182492</v>
       </c>
       <c r="T39">
-        <v>1.682842340145828</v>
+        <v>1.70820927322008</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.121016687985522</v>
+        <v>5.852162666713483</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1157708833233145</v>
+        <v>0.1157394167086333</v>
       </c>
       <c r="C40">
-        <v>124.7420989226928</v>
+        <v>123.174424537287</v>
       </c>
       <c r="D40">
-        <v>178.5360989226928</v>
+        <v>178.616424537287</v>
       </c>
       <c r="E40">
-        <v>-47.576</v>
+        <v>-45.928</v>
       </c>
       <c r="F40">
-        <v>62.624</v>
+        <v>64.27200000000001</v>
       </c>
       <c r="G40">
         <v>8.83</v>
@@ -4561,28 +4561,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M40">
-        <v>3.4631072</v>
+        <v>3.554241600000001</v>
       </c>
       <c r="N40">
-        <v>16.80355946666667</v>
+        <v>16.71242506666666</v>
       </c>
       <c r="O40">
-        <v>1.680355946666667</v>
+        <v>1.671242506666667</v>
       </c>
       <c r="P40">
-        <v>15.12320352</v>
+        <v>15.04118256</v>
       </c>
       <c r="Q40">
-        <v>28.52320352</v>
+        <v>28.44118256</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1562230376182492</v>
+        <v>0.1579165847682514</v>
       </c>
       <c r="T40">
-        <v>1.70820927322008</v>
+        <v>1.734407909018077</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.852162666713483</v>
+        <v>5.702107213720829</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1157394167086333</v>
+        <v>0.1157079500939521</v>
       </c>
       <c r="C41">
-        <v>123.174424537287</v>
+        <v>121.6068224634042</v>
       </c>
       <c r="D41">
-        <v>178.616424537287</v>
+        <v>178.6968224634042</v>
       </c>
       <c r="E41">
-        <v>-45.928</v>
+        <v>-44.28</v>
       </c>
       <c r="F41">
-        <v>64.27200000000001</v>
+        <v>65.92</v>
       </c>
       <c r="G41">
         <v>8.83</v>
@@ -4643,28 +4643,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M41">
-        <v>3.554241600000001</v>
+        <v>3.645376</v>
       </c>
       <c r="N41">
-        <v>16.71242506666666</v>
+        <v>16.62129066666667</v>
       </c>
       <c r="O41">
-        <v>1.671242506666667</v>
+        <v>1.662129066666667</v>
       </c>
       <c r="P41">
-        <v>15.04118256</v>
+        <v>14.9591616</v>
       </c>
       <c r="Q41">
-        <v>28.44118256</v>
+        <v>28.3591616</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1579165847682514</v>
+        <v>0.1596665834899202</v>
       </c>
       <c r="T41">
-        <v>1.734407909018077</v>
+        <v>1.761479832676007</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.702107213720829</v>
+        <v>5.55955453337781</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1157079500939521</v>
+        <v>0.1156764834792709</v>
       </c>
       <c r="C42">
-        <v>121.6068224634042</v>
+        <v>120.0392927987335</v>
       </c>
       <c r="D42">
-        <v>178.6968224634042</v>
+        <v>178.7772927987335</v>
       </c>
       <c r="E42">
-        <v>-44.28</v>
+        <v>-42.63199999999999</v>
       </c>
       <c r="F42">
-        <v>65.92</v>
+        <v>67.56800000000001</v>
       </c>
       <c r="G42">
         <v>8.83</v>
@@ -4725,28 +4725,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M42">
-        <v>3.645376</v>
+        <v>3.736510400000001</v>
       </c>
       <c r="N42">
-        <v>16.62129066666667</v>
+        <v>16.53015626666667</v>
       </c>
       <c r="O42">
-        <v>1.662129066666667</v>
+        <v>1.653015626666667</v>
       </c>
       <c r="P42">
-        <v>14.9591616</v>
+        <v>14.87714064</v>
       </c>
       <c r="Q42">
-        <v>28.3591616</v>
+        <v>28.27714064</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1596665834899202</v>
+        <v>0.1614759042021541</v>
       </c>
       <c r="T42">
-        <v>1.761479832676007</v>
+        <v>1.789469448661325</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.55955453337781</v>
+        <v>5.423955642319814</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1156764834792709</v>
+        <v>0.1156450168645897</v>
       </c>
       <c r="C43">
-        <v>120.0392927987335</v>
+        <v>118.4718356411406</v>
       </c>
       <c r="D43">
-        <v>178.7772927987335</v>
+        <v>178.8578356411406</v>
       </c>
       <c r="E43">
-        <v>-42.63199999999999</v>
+        <v>-40.98399999999999</v>
       </c>
       <c r="F43">
-        <v>67.56800000000001</v>
+        <v>69.21600000000001</v>
       </c>
       <c r="G43">
         <v>8.83</v>
@@ -4807,28 +4807,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M43">
-        <v>3.736510400000001</v>
+        <v>3.827644800000001</v>
       </c>
       <c r="N43">
-        <v>16.53015626666667</v>
+        <v>16.43902186666666</v>
       </c>
       <c r="O43">
-        <v>1.653015626666667</v>
+        <v>1.643902186666667</v>
       </c>
       <c r="P43">
-        <v>14.87714064</v>
+        <v>14.79511968</v>
       </c>
       <c r="Q43">
-        <v>28.27714064</v>
+        <v>28.19511968</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1614759042021541</v>
+        <v>0.1633476152837754</v>
       </c>
       <c r="T43">
-        <v>1.789469448661325</v>
+        <v>1.81842422381855</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.423955642319814</v>
+        <v>5.294813841312198</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1156450168645897</v>
+        <v>0.1156135502499085</v>
       </c>
       <c r="C44">
-        <v>118.4718356411406</v>
+        <v>116.9044510886674</v>
       </c>
       <c r="D44">
-        <v>178.8578356411406</v>
+        <v>178.9384510886674</v>
       </c>
       <c r="E44">
-        <v>-40.98399999999999</v>
+        <v>-39.336</v>
       </c>
       <c r="F44">
-        <v>69.21600000000001</v>
+        <v>70.864</v>
       </c>
       <c r="G44">
         <v>8.83</v>
@@ -4889,28 +4889,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M44">
-        <v>3.827644800000001</v>
+        <v>3.9187792</v>
       </c>
       <c r="N44">
-        <v>16.43902186666666</v>
+        <v>16.34788746666667</v>
       </c>
       <c r="O44">
-        <v>1.643902186666667</v>
+        <v>1.634788746666667</v>
       </c>
       <c r="P44">
-        <v>14.79511968</v>
+        <v>14.71309872</v>
       </c>
       <c r="Q44">
-        <v>28.19511968</v>
+        <v>28.11309872</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1633476152837754</v>
+        <v>0.165285000438436</v>
       </c>
       <c r="T44">
-        <v>1.81842422381855</v>
+        <v>1.848394955998836</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.294813841312198</v>
+        <v>5.171678635700288</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1156135502499085</v>
+        <v>0.1155820836352273</v>
       </c>
       <c r="C45">
-        <v>116.9044510886674</v>
+        <v>115.3371392395327</v>
       </c>
       <c r="D45">
-        <v>178.9384510886674</v>
+        <v>179.0191392395327</v>
       </c>
       <c r="E45">
-        <v>-39.336</v>
+        <v>-37.688</v>
       </c>
       <c r="F45">
-        <v>70.864</v>
+        <v>72.512</v>
       </c>
       <c r="G45">
         <v>8.83</v>
@@ -4971,28 +4971,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M45">
-        <v>3.9187792</v>
+        <v>4.0099136</v>
       </c>
       <c r="N45">
-        <v>16.34788746666667</v>
+        <v>16.25675306666666</v>
       </c>
       <c r="O45">
-        <v>1.634788746666667</v>
+        <v>1.625675306666666</v>
       </c>
       <c r="P45">
-        <v>14.71309872</v>
+        <v>14.63107776</v>
       </c>
       <c r="Q45">
-        <v>28.11309872</v>
+        <v>28.03107776</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.165285000438436</v>
+        <v>0.1672915779200488</v>
       </c>
       <c r="T45">
-        <v>1.848394955998836</v>
+        <v>1.879436071471275</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.171678635700288</v>
+        <v>5.054140484888918</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1155820836352273</v>
+        <v>0.1155506170205461</v>
       </c>
       <c r="C46">
-        <v>115.3371392395327</v>
+        <v>113.7699001921326</v>
       </c>
       <c r="D46">
-        <v>179.0191392395327</v>
+        <v>179.0999001921326</v>
       </c>
       <c r="E46">
-        <v>-37.688</v>
+        <v>-36.03999999999999</v>
       </c>
       <c r="F46">
-        <v>72.512</v>
+        <v>74.16000000000001</v>
       </c>
       <c r="G46">
         <v>8.83</v>
@@ -5053,28 +5053,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M46">
-        <v>4.0099136</v>
+        <v>4.101048</v>
       </c>
       <c r="N46">
-        <v>16.25675306666666</v>
+        <v>16.16561866666667</v>
       </c>
       <c r="O46">
-        <v>1.625675306666666</v>
+        <v>1.616561866666667</v>
       </c>
       <c r="P46">
-        <v>14.63107776</v>
+        <v>14.5490568</v>
       </c>
       <c r="Q46">
-        <v>28.03107776</v>
+        <v>27.9490568</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1672915779200488</v>
+        <v>0.1693711218555384</v>
       </c>
       <c r="T46">
-        <v>1.879436071471275</v>
+        <v>1.911605954779076</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.054140484888918</v>
+        <v>4.941826251891387</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1155506170205461</v>
+        <v>0.1155191504058649</v>
       </c>
       <c r="C47">
-        <v>113.7699001921326</v>
+        <v>112.2027340450408</v>
       </c>
       <c r="D47">
-        <v>179.0999001921326</v>
+        <v>179.1807340450408</v>
       </c>
       <c r="E47">
-        <v>-36.03999999999999</v>
+        <v>-34.392</v>
       </c>
       <c r="F47">
-        <v>74.16000000000001</v>
+        <v>75.80800000000001</v>
       </c>
       <c r="G47">
         <v>8.83</v>
@@ -5135,28 +5135,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M47">
-        <v>4.101048</v>
+        <v>4.1921824</v>
       </c>
       <c r="N47">
-        <v>16.16561866666667</v>
+        <v>16.07448426666667</v>
       </c>
       <c r="O47">
-        <v>1.616561866666667</v>
+        <v>1.607448426666667</v>
       </c>
       <c r="P47">
-        <v>14.5490568</v>
+        <v>14.46703584</v>
       </c>
       <c r="Q47">
-        <v>27.9490568</v>
+        <v>27.86703584</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1693711218555384</v>
+        <v>0.1715276859367869</v>
       </c>
       <c r="T47">
-        <v>1.911605954779076</v>
+        <v>1.944967315246424</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.941826251891387</v>
+        <v>4.834395246415486</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1155191504058649</v>
+        <v>0.1154876837911837</v>
       </c>
       <c r="C48">
-        <v>112.2027340450408</v>
+        <v>110.6356408970088</v>
       </c>
       <c r="D48">
-        <v>179.1807340450408</v>
+        <v>179.2616408970088</v>
       </c>
       <c r="E48">
-        <v>-34.392</v>
+        <v>-32.744</v>
       </c>
       <c r="F48">
-        <v>75.80800000000001</v>
+        <v>77.456</v>
       </c>
       <c r="G48">
         <v>8.83</v>
@@ -5217,28 +5217,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M48">
-        <v>4.1921824</v>
+        <v>4.283316800000001</v>
       </c>
       <c r="N48">
-        <v>16.07448426666667</v>
+        <v>15.98334986666666</v>
       </c>
       <c r="O48">
-        <v>1.607448426666667</v>
+        <v>1.598334986666667</v>
       </c>
       <c r="P48">
-        <v>14.46703584</v>
+        <v>14.38501488</v>
       </c>
       <c r="Q48">
-        <v>27.86703584</v>
+        <v>27.78501488</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1715276859367869</v>
+        <v>0.1737656297946863</v>
       </c>
       <c r="T48">
-        <v>1.944967315246424</v>
+        <v>1.979587594976692</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.834395246415486</v>
+        <v>4.731535773087497</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1154876837911837</v>
+        <v>0.1154562171765025</v>
       </c>
       <c r="C49">
-        <v>110.6356408970088</v>
+        <v>109.0686208469669</v>
       </c>
       <c r="D49">
-        <v>179.2616408970088</v>
+        <v>179.3426208469669</v>
       </c>
       <c r="E49">
-        <v>-32.744</v>
+        <v>-31.09599999999999</v>
       </c>
       <c r="F49">
-        <v>77.456</v>
+        <v>79.10400000000001</v>
       </c>
       <c r="G49">
         <v>8.83</v>
@@ -5299,28 +5299,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M49">
-        <v>4.283316800000001</v>
+        <v>4.374451200000001</v>
       </c>
       <c r="N49">
-        <v>15.98334986666666</v>
+        <v>15.89221546666666</v>
       </c>
       <c r="O49">
-        <v>1.598334986666667</v>
+        <v>1.589221546666667</v>
       </c>
       <c r="P49">
-        <v>14.38501488</v>
+        <v>14.30299392</v>
       </c>
       <c r="Q49">
-        <v>27.78501488</v>
+        <v>27.70299392</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1737656297946863</v>
+        <v>0.176089648416351</v>
       </c>
       <c r="T49">
-        <v>1.979587594976692</v>
+        <v>2.015539423927355</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.731535773087497</v>
+        <v>4.632962111148173</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1154562171765025</v>
+        <v>0.1154247505618213</v>
       </c>
       <c r="C50">
-        <v>109.068620846967</v>
+        <v>107.5016739940241</v>
       </c>
       <c r="D50">
-        <v>179.342620846967</v>
+        <v>179.4236739940241</v>
       </c>
       <c r="E50">
-        <v>-31.096</v>
+        <v>-29.44799999999999</v>
       </c>
       <c r="F50">
-        <v>79.104</v>
+        <v>80.75200000000001</v>
       </c>
       <c r="G50">
         <v>8.83</v>
@@ -5381,28 +5381,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M50">
-        <v>4.3744512</v>
+        <v>4.465585600000001</v>
       </c>
       <c r="N50">
-        <v>15.89221546666667</v>
+        <v>15.80108106666667</v>
       </c>
       <c r="O50">
-        <v>1.589221546666667</v>
+        <v>1.580108106666667</v>
       </c>
       <c r="P50">
-        <v>14.30299392</v>
+        <v>14.22097296</v>
       </c>
       <c r="Q50">
-        <v>27.70299392</v>
+        <v>27.62097296</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.176089648416351</v>
+        <v>0.1785048050231791</v>
       </c>
       <c r="T50">
-        <v>2.015539423927354</v>
+        <v>2.05290112852314</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.632962111148174</v>
+        <v>4.538411863981885</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1154247505618213</v>
+        <v>0.1165182839471401</v>
       </c>
       <c r="C51">
-        <v>107.5016739940241</v>
+        <v>103.0792037060336</v>
       </c>
       <c r="D51">
-        <v>179.4236739940241</v>
+        <v>176.6492037060336</v>
       </c>
       <c r="E51">
-        <v>-29.44799999999999</v>
+        <v>-27.8</v>
       </c>
       <c r="F51">
-        <v>80.75200000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G51">
         <v>8.83</v>
@@ -5463,45 +5463,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M51">
-        <v>4.465585600000001</v>
+        <v>4.762720000000001</v>
       </c>
       <c r="N51">
-        <v>15.80108106666667</v>
+        <v>15.50394666666666</v>
       </c>
       <c r="O51">
-        <v>1.580108106666667</v>
+        <v>1.550394666666667</v>
       </c>
       <c r="P51">
-        <v>14.22097296</v>
+        <v>13.953552</v>
       </c>
       <c r="Q51">
-        <v>27.62097296</v>
+        <v>27.353552</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1785048050231791</v>
+        <v>0.1810165678942802</v>
       </c>
       <c r="T51">
-        <v>2.05290112852314</v>
+        <v>2.091757301302758</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.1</v>
       </c>
       <c r="W51">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.538411863981885</v>
+        <v>4.255271497519624</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1165182839471401</v>
+        <v>0.1165093173324589</v>
       </c>
       <c r="C52">
-        <v>103.0792037060336</v>
+        <v>101.4536045069906</v>
       </c>
       <c r="D52">
-        <v>176.6492037060336</v>
+        <v>176.6716045069906</v>
       </c>
       <c r="E52">
-        <v>-27.8</v>
+        <v>-26.152</v>
       </c>
       <c r="F52">
-        <v>82.40000000000001</v>
+        <v>84.048</v>
       </c>
       <c r="G52">
         <v>8.83</v>
@@ -5545,28 +5545,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M52">
-        <v>4.762720000000001</v>
+        <v>4.857974400000001</v>
       </c>
       <c r="N52">
-        <v>15.50394666666666</v>
+        <v>15.40869226666667</v>
       </c>
       <c r="O52">
-        <v>1.550394666666667</v>
+        <v>1.540869226666667</v>
       </c>
       <c r="P52">
-        <v>13.953552</v>
+        <v>13.86782304</v>
       </c>
       <c r="Q52">
-        <v>27.353552</v>
+        <v>27.26782304</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1810165678942802</v>
+        <v>0.1836308516988957</v>
       </c>
       <c r="T52">
-        <v>2.091757301302758</v>
+        <v>2.132199440318279</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.255271497519624</v>
+        <v>4.171834801489828</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1165093173324589</v>
+        <v>0.1165003507177777</v>
       </c>
       <c r="C53">
-        <v>101.4536045069906</v>
+        <v>99.82801098993788</v>
       </c>
       <c r="D53">
-        <v>176.6716045069906</v>
+        <v>176.6940109899379</v>
       </c>
       <c r="E53">
-        <v>-26.152</v>
+        <v>-24.50399999999999</v>
       </c>
       <c r="F53">
-        <v>84.048</v>
+        <v>85.69600000000001</v>
       </c>
       <c r="G53">
         <v>8.83</v>
@@ -5627,28 +5627,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M53">
-        <v>4.857974400000001</v>
+        <v>4.953228800000001</v>
       </c>
       <c r="N53">
-        <v>15.40869226666667</v>
+        <v>15.31343786666666</v>
       </c>
       <c r="O53">
-        <v>1.540869226666667</v>
+        <v>1.531343786666667</v>
       </c>
       <c r="P53">
-        <v>13.86782304</v>
+        <v>13.78209408</v>
       </c>
       <c r="Q53">
-        <v>27.26782304</v>
+        <v>27.18209408</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1836308516988957</v>
+        <v>0.1863540639953702</v>
       </c>
       <c r="T53">
-        <v>2.132199440318279</v>
+        <v>2.174326668459446</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.171834801489828</v>
+        <v>4.091607209153485</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1165003507177777</v>
+        <v>0.1164913841030965</v>
       </c>
       <c r="C54">
-        <v>99.82801098993788</v>
+        <v>98.20242315703756</v>
       </c>
       <c r="D54">
-        <v>176.6940109899379</v>
+        <v>176.7164231570376</v>
       </c>
       <c r="E54">
-        <v>-24.50399999999999</v>
+        <v>-22.85599999999999</v>
       </c>
       <c r="F54">
-        <v>85.69600000000001</v>
+        <v>87.34400000000001</v>
       </c>
       <c r="G54">
         <v>8.83</v>
@@ -5709,28 +5709,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M54">
-        <v>4.953228800000001</v>
+        <v>5.048483200000001</v>
       </c>
       <c r="N54">
-        <v>15.31343786666666</v>
+        <v>15.21818346666667</v>
       </c>
       <c r="O54">
-        <v>1.531343786666667</v>
+        <v>1.521818346666667</v>
       </c>
       <c r="P54">
-        <v>13.78209408</v>
+        <v>13.69636512</v>
       </c>
       <c r="Q54">
-        <v>27.18209408</v>
+        <v>27.09636512</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1863540639953702</v>
+        <v>0.1891931576661628</v>
       </c>
       <c r="T54">
-        <v>2.174326668459446</v>
+        <v>2.21824654460662</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.091607209153485</v>
+        <v>4.014407073131721</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1164913841030965</v>
+        <v>0.1181834174884153</v>
       </c>
       <c r="C55">
-        <v>98.20242315703756</v>
+        <v>92.42350342305713</v>
       </c>
       <c r="D55">
-        <v>176.7164231570376</v>
+        <v>172.5855034230571</v>
       </c>
       <c r="E55">
-        <v>-22.85599999999999</v>
+        <v>-21.20799999999998</v>
       </c>
       <c r="F55">
-        <v>87.34400000000001</v>
+        <v>88.99200000000002</v>
       </c>
       <c r="G55">
         <v>8.83</v>
@@ -5791,45 +5791,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M55">
-        <v>5.048483200000001</v>
+        <v>5.455209600000001</v>
       </c>
       <c r="N55">
-        <v>15.21818346666667</v>
+        <v>14.81145706666667</v>
       </c>
       <c r="O55">
-        <v>1.521818346666667</v>
+        <v>1.481145706666667</v>
       </c>
       <c r="P55">
-        <v>13.69636512</v>
+        <v>13.33031136</v>
       </c>
       <c r="Q55">
-        <v>27.09636512</v>
+        <v>26.73031136</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1891931576661628</v>
+        <v>0.1921556901922072</v>
       </c>
       <c r="T55">
-        <v>2.21824654460662</v>
+        <v>2.264075980586281</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.1</v>
       </c>
       <c r="W55">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.014407073131721</v>
+        <v>3.715103204589364</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1181834174884153</v>
+        <v>0.1182059508737341</v>
       </c>
       <c r="C56">
-        <v>92.42350342305713</v>
+        <v>90.72179325694313</v>
       </c>
       <c r="D56">
-        <v>172.5855034230571</v>
+        <v>172.5317932569431</v>
       </c>
       <c r="E56">
-        <v>-21.20799999999998</v>
+        <v>-19.55999999999999</v>
       </c>
       <c r="F56">
-        <v>88.99200000000002</v>
+        <v>90.64000000000001</v>
       </c>
       <c r="G56">
         <v>8.83</v>
@@ -5873,28 +5873,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M56">
-        <v>5.455209600000001</v>
+        <v>5.556232000000001</v>
       </c>
       <c r="N56">
-        <v>14.81145706666667</v>
+        <v>14.71043466666666</v>
       </c>
       <c r="O56">
-        <v>1.481145706666667</v>
+        <v>1.471043466666667</v>
       </c>
       <c r="P56">
-        <v>13.33031136</v>
+        <v>13.2393912</v>
       </c>
       <c r="Q56">
-        <v>26.73031136</v>
+        <v>26.6393912</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1921556901922072</v>
+        <v>0.1952498908305203</v>
       </c>
       <c r="T56">
-        <v>2.264075980586281</v>
+        <v>2.31194228038726</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.715103204589364</v>
+        <v>3.64755587359683</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1182059508737341</v>
+        <v>0.1182284842590529</v>
       </c>
       <c r="C57">
-        <v>90.72179325694313</v>
+        <v>89.02011651060542</v>
       </c>
       <c r="D57">
-        <v>172.5317932569431</v>
+        <v>172.4781165106054</v>
       </c>
       <c r="E57">
-        <v>-19.55999999999999</v>
+        <v>-17.91199999999999</v>
       </c>
       <c r="F57">
-        <v>90.64000000000001</v>
+        <v>92.28800000000001</v>
       </c>
       <c r="G57">
         <v>8.83</v>
@@ -5955,28 +5955,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M57">
-        <v>5.556232000000001</v>
+        <v>5.657254400000001</v>
       </c>
       <c r="N57">
-        <v>14.71043466666666</v>
+        <v>14.60941226666666</v>
       </c>
       <c r="O57">
-        <v>1.471043466666667</v>
+        <v>1.460941226666667</v>
       </c>
       <c r="P57">
-        <v>13.2393912</v>
+        <v>13.14847104</v>
       </c>
       <c r="Q57">
-        <v>26.6393912</v>
+        <v>26.54847104</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1952498908305203</v>
+        <v>0.198484736952393</v>
       </c>
       <c r="T57">
-        <v>2.31194228038726</v>
+        <v>2.361984321088282</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.64755587359683</v>
+        <v>3.582420947282601</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1182284842590529</v>
+        <v>0.1182510176443717</v>
       </c>
       <c r="C58">
-        <v>89.02011651060542</v>
+        <v>87.31847315286159</v>
       </c>
       <c r="D58">
-        <v>172.4781165106054</v>
+        <v>172.4244731528616</v>
       </c>
       <c r="E58">
-        <v>-17.91199999999999</v>
+        <v>-16.26399999999998</v>
       </c>
       <c r="F58">
-        <v>92.28800000000001</v>
+        <v>93.93600000000002</v>
       </c>
       <c r="G58">
         <v>8.83</v>
@@ -6037,28 +6037,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M58">
-        <v>5.657254400000001</v>
+        <v>5.758276800000002</v>
       </c>
       <c r="N58">
-        <v>14.60941226666666</v>
+        <v>14.50838986666666</v>
       </c>
       <c r="O58">
-        <v>1.460941226666667</v>
+        <v>1.450838986666667</v>
       </c>
       <c r="P58">
-        <v>13.14847104</v>
+        <v>13.05755088</v>
       </c>
       <c r="Q58">
-        <v>26.54847104</v>
+        <v>26.45755088</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.198484736952393</v>
+        <v>0.2018700410334226</v>
       </c>
       <c r="T58">
-        <v>2.361984321088282</v>
+        <v>2.414353898566097</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.582420947282601</v>
+        <v>3.519571456979397</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1182510176443717</v>
+        <v>0.1197351510296905</v>
       </c>
       <c r="C59">
-        <v>87.31847315286159</v>
+        <v>82.20931951364871</v>
       </c>
       <c r="D59">
-        <v>172.4244731528616</v>
+        <v>168.9633195136487</v>
       </c>
       <c r="E59">
-        <v>-16.26399999999998</v>
+        <v>-14.61599999999999</v>
       </c>
       <c r="F59">
-        <v>93.93600000000002</v>
+        <v>95.58400000000002</v>
       </c>
       <c r="G59">
         <v>8.83</v>
@@ -6119,45 +6119,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M59">
-        <v>5.758276800000002</v>
+        <v>6.126934400000001</v>
       </c>
       <c r="N59">
-        <v>14.50838986666666</v>
+        <v>14.13973226666666</v>
       </c>
       <c r="O59">
-        <v>1.450838986666667</v>
+        <v>1.413973226666666</v>
       </c>
       <c r="P59">
-        <v>13.05755088</v>
+        <v>12.72575904</v>
       </c>
       <c r="Q59">
-        <v>26.45755088</v>
+        <v>26.12575904</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2018700410334226</v>
+        <v>0.2054165500706918</v>
       </c>
       <c r="T59">
-        <v>2.414353898566097</v>
+        <v>2.469217265447618</v>
       </c>
       <c r="U59">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.1</v>
       </c>
       <c r="W59">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.519571456979397</v>
+        <v>3.307798867026658</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1197351510296905</v>
+        <v>0.1197828844150093</v>
       </c>
       <c r="C60">
-        <v>82.20931951364872</v>
+        <v>80.4523052288063</v>
       </c>
       <c r="D60">
-        <v>168.9633195136487</v>
+        <v>168.8543052288063</v>
       </c>
       <c r="E60">
-        <v>-14.616</v>
+        <v>-12.968</v>
       </c>
       <c r="F60">
-        <v>95.584</v>
+        <v>97.232</v>
       </c>
       <c r="G60">
         <v>8.83</v>
@@ -6201,28 +6201,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M60">
-        <v>6.126934400000001</v>
+        <v>6.232571200000001</v>
       </c>
       <c r="N60">
-        <v>14.13973226666667</v>
+        <v>14.03409546666667</v>
       </c>
       <c r="O60">
-        <v>1.413973226666667</v>
+        <v>1.403409546666667</v>
       </c>
       <c r="P60">
-        <v>12.72575904</v>
+        <v>12.63068592</v>
       </c>
       <c r="Q60">
-        <v>26.12575904</v>
+        <v>26.03068592</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2054165500706917</v>
+        <v>0.2091360595488032</v>
       </c>
       <c r="T60">
-        <v>2.469217265447617</v>
+        <v>2.526756894128236</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.307798867026659</v>
+        <v>3.251734479449936</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1197828844150093</v>
+        <v>0.1198306178003281</v>
       </c>
       <c r="C61">
-        <v>80.4523052288063</v>
+        <v>78.69543152419986</v>
       </c>
       <c r="D61">
-        <v>168.8543052288063</v>
+        <v>168.7454315241999</v>
       </c>
       <c r="E61">
-        <v>-12.968</v>
+        <v>-11.31999999999999</v>
       </c>
       <c r="F61">
-        <v>97.232</v>
+        <v>98.88000000000001</v>
       </c>
       <c r="G61">
         <v>8.83</v>
@@ -6283,28 +6283,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M61">
-        <v>6.232571200000001</v>
+        <v>6.338208000000001</v>
       </c>
       <c r="N61">
-        <v>14.03409546666667</v>
+        <v>13.92845866666666</v>
       </c>
       <c r="O61">
-        <v>1.403409546666667</v>
+        <v>1.392845866666667</v>
       </c>
       <c r="P61">
-        <v>12.63068592</v>
+        <v>12.5356128</v>
       </c>
       <c r="Q61">
-        <v>26.03068592</v>
+        <v>25.9356128</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2091360595488032</v>
+        <v>0.2130415445008202</v>
       </c>
       <c r="T61">
-        <v>2.526756894128236</v>
+        <v>2.587173504242885</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.251734479449936</v>
+        <v>3.197538904792437</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1198306178003281</v>
+        <v>0.1198783511856469</v>
       </c>
       <c r="C62">
-        <v>78.69543152419986</v>
+        <v>76.93869812807513</v>
       </c>
       <c r="D62">
-        <v>168.7454315241999</v>
+        <v>168.6366981280751</v>
       </c>
       <c r="E62">
-        <v>-11.31999999999999</v>
+        <v>-9.671999999999997</v>
       </c>
       <c r="F62">
-        <v>98.88000000000001</v>
+        <v>100.528</v>
       </c>
       <c r="G62">
         <v>8.83</v>
@@ -6365,28 +6365,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M62">
-        <v>6.338208000000001</v>
+        <v>6.443844800000001</v>
       </c>
       <c r="N62">
-        <v>13.92845866666666</v>
+        <v>13.82282186666666</v>
       </c>
       <c r="O62">
-        <v>1.392845866666667</v>
+        <v>1.382282186666667</v>
       </c>
       <c r="P62">
-        <v>12.5356128</v>
+        <v>12.44053968</v>
       </c>
       <c r="Q62">
-        <v>25.9356128</v>
+        <v>25.84053968</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2130415445008202</v>
+        <v>0.217147310732428</v>
       </c>
       <c r="T62">
-        <v>2.587173504242885</v>
+        <v>2.650688402055723</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.197538904792437</v>
+        <v>3.145120234222069</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1198783511856469</v>
+        <v>0.1199260845709657</v>
       </c>
       <c r="C63">
-        <v>76.93869812807513</v>
+        <v>75.18210476937797</v>
       </c>
       <c r="D63">
-        <v>168.6366981280751</v>
+        <v>168.528104769378</v>
       </c>
       <c r="E63">
-        <v>-9.671999999999997</v>
+        <v>-8.024000000000001</v>
       </c>
       <c r="F63">
-        <v>100.528</v>
+        <v>102.176</v>
       </c>
       <c r="G63">
         <v>8.83</v>
@@ -6447,28 +6447,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M63">
-        <v>6.443844800000001</v>
+        <v>6.549481600000001</v>
       </c>
       <c r="N63">
-        <v>13.82282186666666</v>
+        <v>13.71718506666667</v>
       </c>
       <c r="O63">
-        <v>1.382282186666667</v>
+        <v>1.371718506666667</v>
       </c>
       <c r="P63">
-        <v>12.44053968</v>
+        <v>12.34546656</v>
       </c>
       <c r="Q63">
-        <v>25.84053968</v>
+        <v>25.74546656</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.217147310732428</v>
+        <v>0.221469169923594</v>
       </c>
       <c r="T63">
-        <v>2.650688402055723</v>
+        <v>2.717546189227129</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.145120234222069</v>
+        <v>3.09439248850881</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1199260845709657</v>
+        <v>0.1199738179562845</v>
       </c>
       <c r="C64">
-        <v>75.18210476937797</v>
+        <v>73.42565117775152</v>
       </c>
       <c r="D64">
-        <v>168.528104769378</v>
+        <v>168.4196511777515</v>
       </c>
       <c r="E64">
-        <v>-8.024000000000001</v>
+        <v>-6.375999999999991</v>
       </c>
       <c r="F64">
-        <v>102.176</v>
+        <v>103.824</v>
       </c>
       <c r="G64">
         <v>8.83</v>
@@ -6529,28 +6529,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M64">
-        <v>6.549481600000001</v>
+        <v>6.655118400000001</v>
       </c>
       <c r="N64">
-        <v>13.71718506666667</v>
+        <v>13.61154826666666</v>
       </c>
       <c r="O64">
-        <v>1.371718506666667</v>
+        <v>1.361154826666667</v>
       </c>
       <c r="P64">
-        <v>12.34546656</v>
+        <v>12.25039344</v>
       </c>
       <c r="Q64">
-        <v>25.74546656</v>
+        <v>25.65039344</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.221469169923594</v>
+        <v>0.2260246431250933</v>
       </c>
       <c r="T64">
-        <v>2.717546189227129</v>
+        <v>2.788017910840234</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.09439248850881</v>
+        <v>3.045275147421369</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1199738179562845</v>
+        <v>0.1245143513416033</v>
       </c>
       <c r="C65">
-        <v>73.42565117775152</v>
+        <v>62.06258606087553</v>
       </c>
       <c r="D65">
-        <v>168.4196511777515</v>
+        <v>158.7045860608755</v>
       </c>
       <c r="E65">
-        <v>-6.375999999999991</v>
+        <v>-4.727999999999994</v>
       </c>
       <c r="F65">
-        <v>103.824</v>
+        <v>105.472</v>
       </c>
       <c r="G65">
         <v>8.83</v>
@@ -6611,45 +6611,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M65">
-        <v>6.655118400000001</v>
+        <v>7.583436800000001</v>
       </c>
       <c r="N65">
-        <v>13.61154826666666</v>
+        <v>12.68322986666666</v>
       </c>
       <c r="O65">
-        <v>1.361154826666667</v>
+        <v>1.268322986666667</v>
       </c>
       <c r="P65">
-        <v>12.25039344</v>
+        <v>11.41490688</v>
       </c>
       <c r="Q65">
-        <v>25.65039344</v>
+        <v>24.81490688</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2260246431250933</v>
+        <v>0.2308331981711203</v>
       </c>
       <c r="T65">
-        <v>2.788017910840234</v>
+        <v>2.862404728098511</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.1</v>
       </c>
       <c r="W65">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.045275147421369</v>
+        <v>2.672491009177615</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1245143513416033</v>
+        <v>0.1246322847269221</v>
       </c>
       <c r="C66">
-        <v>62.06258606087553</v>
+        <v>60.17716342160267</v>
       </c>
       <c r="D66">
-        <v>158.7045860608755</v>
+        <v>158.4671634216027</v>
       </c>
       <c r="E66">
-        <v>-4.727999999999994</v>
+        <v>-3.079999999999998</v>
       </c>
       <c r="F66">
-        <v>105.472</v>
+        <v>107.12</v>
       </c>
       <c r="G66">
         <v>8.83</v>
@@ -6693,28 +6693,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M66">
-        <v>7.583436800000001</v>
+        <v>7.701928000000001</v>
       </c>
       <c r="N66">
-        <v>12.68322986666666</v>
+        <v>12.56473866666667</v>
       </c>
       <c r="O66">
-        <v>1.268322986666667</v>
+        <v>1.256473866666667</v>
       </c>
       <c r="P66">
-        <v>11.41490688</v>
+        <v>11.3082648</v>
       </c>
       <c r="Q66">
-        <v>24.81490688</v>
+        <v>24.7082648</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2308331981711203</v>
+        <v>0.2359165277912061</v>
       </c>
       <c r="T66">
-        <v>2.862404728098511</v>
+        <v>2.94104222062869</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.672491009177615</v>
+        <v>2.631375762882575</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1246322847269221</v>
+        <v>0.1247502181122409</v>
       </c>
       <c r="C67">
-        <v>60.17716342160267</v>
+        <v>58.29245009146838</v>
       </c>
       <c r="D67">
-        <v>158.4671634216027</v>
+        <v>158.2304500914684</v>
       </c>
       <c r="E67">
-        <v>-3.079999999999998</v>
+        <v>-1.431999999999988</v>
       </c>
       <c r="F67">
-        <v>107.12</v>
+        <v>108.768</v>
       </c>
       <c r="G67">
         <v>8.83</v>
@@ -6775,28 +6775,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M67">
-        <v>7.701928000000001</v>
+        <v>7.820419200000002</v>
       </c>
       <c r="N67">
-        <v>12.56473866666667</v>
+        <v>12.44624746666666</v>
       </c>
       <c r="O67">
-        <v>1.256473866666667</v>
+        <v>1.244624746666666</v>
       </c>
       <c r="P67">
-        <v>11.3082648</v>
+        <v>11.20162272</v>
       </c>
       <c r="Q67">
-        <v>24.7082648</v>
+        <v>24.60162272</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2359165277912061</v>
+        <v>0.2412988768007086</v>
       </c>
       <c r="T67">
-        <v>2.94104222062869</v>
+        <v>3.024305448013585</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.631375762882575</v>
+        <v>2.591506433141929</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1247502181122409</v>
+        <v>0.1248681514975597</v>
       </c>
       <c r="C68">
-        <v>58.29245009146838</v>
+        <v>56.4084428965818</v>
       </c>
       <c r="D68">
-        <v>158.2304500914684</v>
+        <v>157.9944428965818</v>
       </c>
       <c r="E68">
-        <v>-1.431999999999988</v>
+        <v>0.2160000000000082</v>
       </c>
       <c r="F68">
-        <v>108.768</v>
+        <v>110.416</v>
       </c>
       <c r="G68">
         <v>8.83</v>
@@ -6857,28 +6857,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M68">
-        <v>7.820419200000002</v>
+        <v>7.938910400000001</v>
       </c>
       <c r="N68">
-        <v>12.44624746666666</v>
+        <v>12.32775626666666</v>
       </c>
       <c r="O68">
-        <v>1.244624746666666</v>
+        <v>1.232775626666667</v>
       </c>
       <c r="P68">
-        <v>11.20162272</v>
+        <v>11.09498064</v>
       </c>
       <c r="Q68">
-        <v>24.60162272</v>
+        <v>24.49498064</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2412988768007086</v>
+        <v>0.247007428780484</v>
       </c>
       <c r="T68">
-        <v>3.024305448013585</v>
+        <v>3.112614931603626</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.591506433141929</v>
+        <v>2.552827232647274</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1248681514975597</v>
+        <v>0.1249860848828785</v>
       </c>
       <c r="C69">
-        <v>56.4084428965818</v>
+        <v>54.52513868195987</v>
       </c>
       <c r="D69">
-        <v>157.9944428965818</v>
+        <v>157.7591386819599</v>
       </c>
       <c r="E69">
-        <v>0.2160000000000082</v>
+        <v>1.864000000000019</v>
       </c>
       <c r="F69">
-        <v>110.416</v>
+        <v>112.064</v>
       </c>
       <c r="G69">
         <v>8.83</v>
@@ -6939,28 +6939,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M69">
-        <v>7.938910400000001</v>
+        <v>8.057401600000002</v>
       </c>
       <c r="N69">
-        <v>12.32775626666666</v>
+        <v>12.20926506666666</v>
       </c>
       <c r="O69">
-        <v>1.232775626666667</v>
+        <v>1.220926506666666</v>
       </c>
       <c r="P69">
-        <v>11.09498064</v>
+        <v>10.98833856</v>
       </c>
       <c r="Q69">
-        <v>24.49498064</v>
+        <v>24.38833856</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.247007428780484</v>
+        <v>0.2530727652589954</v>
       </c>
       <c r="T69">
-        <v>3.112614931603626</v>
+        <v>3.206443757918044</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.552827232647274</v>
+        <v>2.515285655696578</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1249860848828785</v>
+        <v>0.1275259182681973</v>
       </c>
       <c r="C70">
-        <v>54.52513868195987</v>
+        <v>47.97438646143814</v>
       </c>
       <c r="D70">
-        <v>157.7591386819599</v>
+        <v>152.8563864614381</v>
       </c>
       <c r="E70">
-        <v>1.864000000000019</v>
+        <v>3.512000000000015</v>
       </c>
       <c r="F70">
-        <v>112.064</v>
+        <v>113.712</v>
       </c>
       <c r="G70">
         <v>8.83</v>
@@ -7021,45 +7021,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M70">
-        <v>8.057401600000002</v>
+        <v>8.619369600000002</v>
       </c>
       <c r="N70">
-        <v>12.20926506666666</v>
+        <v>11.64729706666666</v>
       </c>
       <c r="O70">
-        <v>1.220926506666666</v>
+        <v>1.164729706666666</v>
       </c>
       <c r="P70">
-        <v>10.98833856</v>
+        <v>10.48256736</v>
       </c>
       <c r="Q70">
-        <v>24.38833856</v>
+        <v>23.88256736</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2530727652589954</v>
+        <v>0.2595294137683785</v>
       </c>
       <c r="T70">
-        <v>3.206443757918044</v>
+        <v>3.306326056897909</v>
       </c>
       <c r="U70">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.1</v>
       </c>
       <c r="W70">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.515285655696578</v>
+        <v>2.351293378423715</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1275259182681973</v>
+        <v>0.1276789516535161</v>
       </c>
       <c r="C71">
-        <v>47.97438646143814</v>
+        <v>46.04069484209771</v>
       </c>
       <c r="D71">
-        <v>152.8563864614381</v>
+        <v>152.5706948420977</v>
       </c>
       <c r="E71">
-        <v>3.512000000000015</v>
+        <v>5.160000000000011</v>
       </c>
       <c r="F71">
-        <v>113.712</v>
+        <v>115.36</v>
       </c>
       <c r="G71">
         <v>8.83</v>
@@ -7103,28 +7103,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M71">
-        <v>8.619369600000002</v>
+        <v>8.744288000000001</v>
       </c>
       <c r="N71">
-        <v>11.64729706666666</v>
+        <v>11.52237866666666</v>
       </c>
       <c r="O71">
-        <v>1.164729706666666</v>
+        <v>1.152237866666667</v>
       </c>
       <c r="P71">
-        <v>10.48256736</v>
+        <v>10.3701408</v>
       </c>
       <c r="Q71">
-        <v>23.88256736</v>
+        <v>23.7701408</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2595294137683785</v>
+        <v>0.2664165055117204</v>
       </c>
       <c r="T71">
-        <v>3.306326056897909</v>
+        <v>3.412867175809764</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.351293378423715</v>
+        <v>2.317703473017662</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1276789516535161</v>
+        <v>0.1278319850388349</v>
       </c>
       <c r="C72">
-        <v>46.04069484209771</v>
+        <v>44.10806915711548</v>
       </c>
       <c r="D72">
-        <v>152.5706948420977</v>
+        <v>152.2860691571155</v>
       </c>
       <c r="E72">
-        <v>5.160000000000011</v>
+        <v>6.808000000000021</v>
       </c>
       <c r="F72">
-        <v>115.36</v>
+        <v>117.008</v>
       </c>
       <c r="G72">
         <v>8.83</v>
@@ -7185,28 +7185,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M72">
-        <v>8.744288000000001</v>
+        <v>8.869206400000003</v>
       </c>
       <c r="N72">
-        <v>11.52237866666666</v>
+        <v>11.39746026666666</v>
       </c>
       <c r="O72">
-        <v>1.152237866666667</v>
+        <v>1.139746026666666</v>
       </c>
       <c r="P72">
-        <v>10.3701408</v>
+        <v>10.25771424</v>
       </c>
       <c r="Q72">
-        <v>23.7701408</v>
+        <v>23.65771424</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2664165055117204</v>
+        <v>0.2737785690994308</v>
       </c>
       <c r="T72">
-        <v>3.412867175809764</v>
+        <v>3.526755958094851</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.317703473017662</v>
+        <v>2.285059762130088</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1278319850388349</v>
+        <v>0.1279850184241537</v>
       </c>
       <c r="C73">
-        <v>44.10806915711551</v>
+        <v>42.17650345199232</v>
       </c>
       <c r="D73">
-        <v>152.2860691571155</v>
+        <v>152.0025034519923</v>
       </c>
       <c r="E73">
-        <v>6.807999999999993</v>
+        <v>8.456000000000003</v>
       </c>
       <c r="F73">
-        <v>117.008</v>
+        <v>118.656</v>
       </c>
       <c r="G73">
         <v>8.83</v>
@@ -7267,28 +7267,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M73">
-        <v>8.869206400000001</v>
+        <v>8.994124800000002</v>
       </c>
       <c r="N73">
-        <v>11.39746026666666</v>
+        <v>11.27254186666666</v>
       </c>
       <c r="O73">
-        <v>1.139746026666667</v>
+        <v>1.127254186666667</v>
       </c>
       <c r="P73">
-        <v>10.25771424</v>
+        <v>10.14528768</v>
       </c>
       <c r="Q73">
-        <v>23.65771424</v>
+        <v>23.54528768</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2737785690994307</v>
+        <v>0.2816664943719775</v>
       </c>
       <c r="T73">
-        <v>3.52675595809485</v>
+        <v>3.6487796534003</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.285059762130089</v>
+        <v>2.253322820989393</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1279850184241537</v>
+        <v>0.1281380518094725</v>
       </c>
       <c r="C74">
-        <v>42.17650345199232</v>
+        <v>40.24599181649702</v>
       </c>
       <c r="D74">
-        <v>152.0025034519923</v>
+        <v>151.719991816497</v>
       </c>
       <c r="E74">
-        <v>8.456000000000003</v>
+        <v>10.104</v>
       </c>
       <c r="F74">
-        <v>118.656</v>
+        <v>120.304</v>
       </c>
       <c r="G74">
         <v>8.83</v>
@@ -7349,28 +7349,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M74">
-        <v>8.994124800000002</v>
+        <v>9.1190432</v>
       </c>
       <c r="N74">
-        <v>11.27254186666666</v>
+        <v>11.14762346666667</v>
       </c>
       <c r="O74">
-        <v>1.127254186666667</v>
+        <v>1.114762346666667</v>
       </c>
       <c r="P74">
-        <v>10.14528768</v>
+        <v>10.03286112</v>
       </c>
       <c r="Q74">
-        <v>23.54528768</v>
+        <v>23.43286112</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2816664943719775</v>
+        <v>0.2901387104054537</v>
       </c>
       <c r="T74">
-        <v>3.6487796534003</v>
+        <v>3.779842140950598</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.253322820989393</v>
+        <v>2.222455385085429</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1281380518094725</v>
+        <v>0.1282910851947913</v>
       </c>
       <c r="C75">
-        <v>40.24599181649702</v>
+        <v>38.3165283842559</v>
       </c>
       <c r="D75">
-        <v>151.719991816497</v>
+        <v>151.4385283842559</v>
       </c>
       <c r="E75">
-        <v>10.104</v>
+        <v>11.75200000000001</v>
       </c>
       <c r="F75">
-        <v>120.304</v>
+        <v>121.952</v>
       </c>
       <c r="G75">
         <v>8.83</v>
@@ -7431,28 +7431,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M75">
-        <v>9.1190432</v>
+        <v>9.243961600000002</v>
       </c>
       <c r="N75">
-        <v>11.14762346666667</v>
+        <v>11.02270506666666</v>
       </c>
       <c r="O75">
-        <v>1.114762346666667</v>
+        <v>1.102270506666666</v>
       </c>
       <c r="P75">
-        <v>10.03286112</v>
+        <v>9.920434559999997</v>
       </c>
       <c r="Q75">
-        <v>23.43286112</v>
+        <v>23.32043456</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2901387104054537</v>
+        <v>0.299262635364582</v>
       </c>
       <c r="T75">
-        <v>3.779842140950598</v>
+        <v>3.920986358312458</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.222455385085429</v>
+        <v>2.192422204205896</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1282910851947913</v>
+        <v>0.1284441185801101</v>
       </c>
       <c r="C76">
-        <v>38.3165283842559</v>
+        <v>36.38810733234673</v>
       </c>
       <c r="D76">
-        <v>151.4385283842559</v>
+        <v>151.1581073323467</v>
       </c>
       <c r="E76">
-        <v>11.75200000000001</v>
+        <v>13.40000000000001</v>
       </c>
       <c r="F76">
-        <v>121.952</v>
+        <v>123.6</v>
       </c>
       <c r="G76">
         <v>8.83</v>
@@ -7513,28 +7513,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M76">
-        <v>9.243961600000002</v>
+        <v>9.368880000000001</v>
       </c>
       <c r="N76">
-        <v>11.02270506666666</v>
+        <v>10.89778666666666</v>
       </c>
       <c r="O76">
-        <v>1.102270506666666</v>
+        <v>1.089778666666666</v>
       </c>
       <c r="P76">
-        <v>9.920434559999997</v>
+        <v>9.808007999999999</v>
       </c>
       <c r="Q76">
-        <v>23.32043456</v>
+        <v>23.208008</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.299262635364582</v>
+        <v>0.3091164743204404</v>
       </c>
       <c r="T76">
-        <v>3.920986358312458</v>
+        <v>4.073422113063266</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.192422204205896</v>
+        <v>2.163189908149818</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1284441185801101</v>
+        <v>0.1285971519654289</v>
       </c>
       <c r="C77">
-        <v>36.38810733234673</v>
+        <v>34.46072288089714</v>
       </c>
       <c r="D77">
-        <v>151.1581073323467</v>
+        <v>150.8787228808971</v>
       </c>
       <c r="E77">
-        <v>13.40000000000001</v>
+        <v>15.048</v>
       </c>
       <c r="F77">
-        <v>123.6</v>
+        <v>125.248</v>
       </c>
       <c r="G77">
         <v>8.83</v>
@@ -7595,28 +7595,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M77">
-        <v>9.368880000000001</v>
+        <v>9.493798400000001</v>
       </c>
       <c r="N77">
-        <v>10.89778666666666</v>
+        <v>10.77286826666666</v>
       </c>
       <c r="O77">
-        <v>1.089778666666666</v>
+        <v>1.077286826666666</v>
       </c>
       <c r="P77">
-        <v>9.808007999999999</v>
+        <v>9.695581439999998</v>
       </c>
       <c r="Q77">
-        <v>23.208008</v>
+        <v>23.09558144</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3091164743204404</v>
+        <v>0.3197914665226205</v>
       </c>
       <c r="T77">
-        <v>4.073422113063266</v>
+        <v>4.238560847376642</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.163189908149818</v>
+        <v>2.134726883042583</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1285971519654289</v>
+        <v>0.1287501853507477</v>
       </c>
       <c r="C78">
-        <v>34.46072288089714</v>
+        <v>32.53436929268742</v>
       </c>
       <c r="D78">
-        <v>150.8787228808971</v>
+        <v>150.6003692926874</v>
       </c>
       <c r="E78">
-        <v>15.048</v>
+        <v>16.69600000000001</v>
       </c>
       <c r="F78">
-        <v>125.248</v>
+        <v>126.896</v>
       </c>
       <c r="G78">
         <v>8.83</v>
@@ -7677,28 +7677,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M78">
-        <v>9.493798400000001</v>
+        <v>9.618716800000001</v>
       </c>
       <c r="N78">
-        <v>10.77286826666666</v>
+        <v>10.64794986666666</v>
       </c>
       <c r="O78">
-        <v>1.077286826666666</v>
+        <v>1.064794986666666</v>
       </c>
       <c r="P78">
-        <v>9.695581439999998</v>
+        <v>9.583154879999999</v>
       </c>
       <c r="Q78">
-        <v>23.09558144</v>
+        <v>22.98315488</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3197914665226205</v>
+        <v>0.3313947189162944</v>
       </c>
       <c r="T78">
-        <v>4.238560847376642</v>
+        <v>4.418059471630311</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.134726883042583</v>
+        <v>2.107003157288784</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1287501853507477</v>
+        <v>0.1289032187360665</v>
       </c>
       <c r="C79">
-        <v>32.53436929268742</v>
+        <v>30.60904087275802</v>
       </c>
       <c r="D79">
-        <v>150.6003692926874</v>
+        <v>150.323040872758</v>
       </c>
       <c r="E79">
-        <v>16.69600000000001</v>
+        <v>18.34400000000001</v>
       </c>
       <c r="F79">
-        <v>126.896</v>
+        <v>128.544</v>
       </c>
       <c r="G79">
         <v>8.83</v>
@@ -7759,28 +7759,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M79">
-        <v>9.618716800000001</v>
+        <v>9.743635200000002</v>
       </c>
       <c r="N79">
-        <v>10.64794986666666</v>
+        <v>10.52303146666666</v>
       </c>
       <c r="O79">
-        <v>1.064794986666666</v>
+        <v>1.052303146666666</v>
       </c>
       <c r="P79">
-        <v>9.583154879999999</v>
+        <v>9.470728319999997</v>
       </c>
       <c r="Q79">
-        <v>22.98315488</v>
+        <v>22.87072832</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3313947189162944</v>
+        <v>0.344052812436666</v>
       </c>
       <c r="T79">
-        <v>4.418059471630311</v>
+        <v>4.613876152634314</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.107003157288784</v>
+        <v>2.079990296297901</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1289032187360665</v>
+        <v>0.1290562521213853</v>
       </c>
       <c r="C80">
-        <v>30.60904087275802</v>
+        <v>28.68473196802094</v>
       </c>
       <c r="D80">
-        <v>150.323040872758</v>
+        <v>150.0467319680209</v>
       </c>
       <c r="E80">
-        <v>18.34400000000001</v>
+        <v>19.992</v>
       </c>
       <c r="F80">
-        <v>128.544</v>
+        <v>130.192</v>
       </c>
       <c r="G80">
         <v>8.83</v>
@@ -7841,28 +7841,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M80">
-        <v>9.743635200000002</v>
+        <v>9.868553600000002</v>
       </c>
       <c r="N80">
-        <v>10.52303146666666</v>
+        <v>10.39811306666666</v>
       </c>
       <c r="O80">
-        <v>1.052303146666666</v>
+        <v>1.039811306666666</v>
       </c>
       <c r="P80">
-        <v>9.470728319999997</v>
+        <v>9.358301759999998</v>
       </c>
       <c r="Q80">
-        <v>22.87072832</v>
+        <v>22.75830176</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.344052812436666</v>
+        <v>0.3579164386732634</v>
       </c>
       <c r="T80">
-        <v>4.613876152634314</v>
+        <v>4.828342041352984</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.079990296297901</v>
+        <v>2.053661305205523</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1290562521213853</v>
+        <v>0.1292092855067041</v>
       </c>
       <c r="C81">
-        <v>28.68473196802094</v>
+        <v>26.76143696687572</v>
       </c>
       <c r="D81">
-        <v>150.0467319680209</v>
+        <v>149.7714369668757</v>
       </c>
       <c r="E81">
-        <v>19.992</v>
+        <v>21.64</v>
       </c>
       <c r="F81">
-        <v>130.192</v>
+        <v>131.84</v>
       </c>
       <c r="G81">
         <v>8.83</v>
@@ -7923,28 +7923,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M81">
-        <v>9.868553600000002</v>
+        <v>9.993472000000001</v>
       </c>
       <c r="N81">
-        <v>10.39811306666666</v>
+        <v>10.27319466666667</v>
       </c>
       <c r="O81">
-        <v>1.039811306666666</v>
+        <v>1.027319466666667</v>
       </c>
       <c r="P81">
-        <v>9.358301759999998</v>
+        <v>9.245875199999999</v>
       </c>
       <c r="Q81">
-        <v>22.75830176</v>
+        <v>22.6458752</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3579164386732634</v>
+        <v>0.3731664275335207</v>
       </c>
       <c r="T81">
-        <v>4.828342041352984</v>
+        <v>5.064254518943522</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.053661305205523</v>
+        <v>2.027990538890454</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1292092855067041</v>
+        <v>0.1293623188920229</v>
       </c>
       <c r="C82">
-        <v>26.76143696687572</v>
+        <v>24.83915029882957</v>
       </c>
       <c r="D82">
-        <v>149.7714369668757</v>
+        <v>149.4971502988296</v>
       </c>
       <c r="E82">
-        <v>21.64</v>
+        <v>23.28800000000003</v>
       </c>
       <c r="F82">
-        <v>131.84</v>
+        <v>133.488</v>
       </c>
       <c r="G82">
         <v>8.83</v>
@@ -8005,28 +8005,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M82">
-        <v>9.993472000000001</v>
+        <v>10.1183904</v>
       </c>
       <c r="N82">
-        <v>10.27319466666667</v>
+        <v>10.14827626666666</v>
       </c>
       <c r="O82">
-        <v>1.027319466666667</v>
+        <v>1.014827626666666</v>
       </c>
       <c r="P82">
-        <v>9.245875199999999</v>
+        <v>9.133448639999997</v>
       </c>
       <c r="Q82">
-        <v>22.6458752</v>
+        <v>22.53344864</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3731664275335207</v>
+        <v>0.390021678379068</v>
       </c>
       <c r="T82">
-        <v>5.064254518943522</v>
+        <v>5.324999888912009</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.027990538890454</v>
+        <v>2.002953618657238</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1293623188920229</v>
+        <v>0.1399949522773417</v>
       </c>
       <c r="C83">
-        <v>24.83915029882957</v>
+        <v>6.316059300352407</v>
       </c>
       <c r="D83">
-        <v>149.4971502988296</v>
+        <v>132.6220593003524</v>
       </c>
       <c r="E83">
-        <v>23.28800000000003</v>
+        <v>24.93600000000002</v>
       </c>
       <c r="F83">
-        <v>133.488</v>
+        <v>135.136</v>
       </c>
       <c r="G83">
         <v>8.83</v>
@@ -8087,45 +8087,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M83">
-        <v>10.1183904</v>
+        <v>12.16224</v>
       </c>
       <c r="N83">
-        <v>10.14827626666666</v>
+        <v>8.104426666666663</v>
       </c>
       <c r="O83">
-        <v>1.014827626666666</v>
+        <v>0.8104426666666664</v>
       </c>
       <c r="P83">
-        <v>9.133448639999997</v>
+        <v>7.293983999999996</v>
       </c>
       <c r="Q83">
-        <v>22.53344864</v>
+        <v>20.693984</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.390021678379068</v>
+        <v>0.4087497348741207</v>
       </c>
       <c r="T83">
-        <v>5.324999888912009</v>
+        <v>5.614716966654774</v>
       </c>
       <c r="U83">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V83">
         <v>0.1</v>
       </c>
       <c r="W83">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.002953618657238</v>
+        <v>1.666359705668254</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1399949522773417</v>
+        <v>0.1402757856626605</v>
       </c>
       <c r="C84">
-        <v>6.316059300352407</v>
+        <v>4.273834456176388</v>
       </c>
       <c r="D84">
-        <v>132.6220593003524</v>
+        <v>132.2278344561764</v>
       </c>
       <c r="E84">
-        <v>24.93600000000002</v>
+        <v>26.58400000000002</v>
       </c>
       <c r="F84">
-        <v>135.136</v>
+        <v>136.784</v>
       </c>
       <c r="G84">
         <v>8.83</v>
@@ -8169,28 +8169,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M84">
-        <v>12.16224</v>
+        <v>12.31056</v>
       </c>
       <c r="N84">
-        <v>8.104426666666663</v>
+        <v>7.956106666666665</v>
       </c>
       <c r="O84">
-        <v>0.8104426666666664</v>
+        <v>0.7956106666666666</v>
       </c>
       <c r="P84">
-        <v>7.293983999999996</v>
+        <v>7.160495999999998</v>
       </c>
       <c r="Q84">
-        <v>20.693984</v>
+        <v>20.560496</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4087497348741207</v>
+        <v>0.4296810921332973</v>
       </c>
       <c r="T84">
-        <v>5.614716966654774</v>
+        <v>5.938518406484923</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.666359705668254</v>
+        <v>1.646283082708395</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1402757856626605</v>
+        <v>0.1405566190479793</v>
       </c>
       <c r="C85">
-        <v>4.273834456176388</v>
+        <v>2.233946366913699</v>
       </c>
       <c r="D85">
-        <v>132.2278344561764</v>
+        <v>131.8359463669137</v>
       </c>
       <c r="E85">
-        <v>26.58400000000002</v>
+        <v>28.23200000000001</v>
       </c>
       <c r="F85">
-        <v>136.784</v>
+        <v>138.432</v>
       </c>
       <c r="G85">
         <v>8.83</v>
@@ -8251,28 +8251,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M85">
-        <v>12.31056</v>
+        <v>12.45888</v>
       </c>
       <c r="N85">
-        <v>7.956106666666665</v>
+        <v>7.807786666666665</v>
       </c>
       <c r="O85">
-        <v>0.7956106666666666</v>
+        <v>0.7807786666666665</v>
       </c>
       <c r="P85">
-        <v>7.160495999999998</v>
+        <v>7.027007999999999</v>
       </c>
       <c r="Q85">
-        <v>20.560496</v>
+        <v>20.427008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4296810921332973</v>
+        <v>0.453228869049871</v>
       </c>
       <c r="T85">
-        <v>5.938518406484923</v>
+        <v>6.302795026293841</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.646283082708395</v>
+        <v>1.626684474580915</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1405566190479793</v>
+        <v>0.1408374524332981</v>
       </c>
       <c r="C86">
-        <v>2.233946366913699</v>
+        <v>0.1963743174008243</v>
       </c>
       <c r="D86">
-        <v>131.8359463669137</v>
+        <v>131.4463743174008</v>
       </c>
       <c r="E86">
-        <v>28.23200000000001</v>
+        <v>29.88000000000001</v>
       </c>
       <c r="F86">
-        <v>138.432</v>
+        <v>140.08</v>
       </c>
       <c r="G86">
         <v>8.83</v>
@@ -8333,28 +8333,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M86">
-        <v>12.45888</v>
+        <v>12.6072</v>
       </c>
       <c r="N86">
-        <v>7.807786666666665</v>
+        <v>7.659466666666665</v>
       </c>
       <c r="O86">
-        <v>0.7807786666666665</v>
+        <v>0.7659466666666666</v>
       </c>
       <c r="P86">
-        <v>7.027007999999999</v>
+        <v>6.893519999999999</v>
       </c>
       <c r="Q86">
-        <v>20.427008</v>
+        <v>20.29352</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4532288690498706</v>
+        <v>0.4799163495553207</v>
       </c>
       <c r="T86">
-        <v>6.302795026293837</v>
+        <v>6.715641862077276</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.626684474580915</v>
+        <v>1.60754701017408</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1408374524332981</v>
+        <v>0.1411182858186169</v>
       </c>
       <c r="C87">
-        <v>0.1963743174008243</v>
+        <v>-1.838902163396199</v>
       </c>
       <c r="D87">
-        <v>131.4463743174008</v>
+        <v>131.0590978366038</v>
       </c>
       <c r="E87">
-        <v>29.88000000000001</v>
+        <v>31.52800000000001</v>
       </c>
       <c r="F87">
-        <v>140.08</v>
+        <v>141.728</v>
       </c>
       <c r="G87">
         <v>8.83</v>
@@ -8415,28 +8415,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M87">
-        <v>12.6072</v>
+        <v>12.75552</v>
       </c>
       <c r="N87">
-        <v>7.659466666666665</v>
+        <v>7.511146666666665</v>
       </c>
       <c r="O87">
-        <v>0.7659466666666666</v>
+        <v>0.7511146666666666</v>
       </c>
       <c r="P87">
-        <v>6.893519999999999</v>
+        <v>6.760031999999999</v>
       </c>
       <c r="Q87">
-        <v>20.29352</v>
+        <v>20.160032</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4799163495553207</v>
+        <v>0.510416327275835</v>
       </c>
       <c r="T87">
-        <v>6.715641862077276</v>
+        <v>7.18746681725835</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.60754701017408</v>
+        <v>1.588854603079033</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1411182858186169</v>
+        <v>0.1413991192039357</v>
       </c>
       <c r="C88">
-        <v>-1.838902163396199</v>
+        <v>-3.871903305967066</v>
       </c>
       <c r="D88">
-        <v>131.0590978366038</v>
+        <v>130.6740966940329</v>
       </c>
       <c r="E88">
-        <v>31.52800000000001</v>
+        <v>33.176</v>
       </c>
       <c r="F88">
-        <v>141.728</v>
+        <v>143.376</v>
       </c>
       <c r="G88">
         <v>8.83</v>
@@ -8497,28 +8497,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M88">
-        <v>12.75552</v>
+        <v>12.90384</v>
       </c>
       <c r="N88">
-        <v>7.511146666666665</v>
+        <v>7.362826666666665</v>
       </c>
       <c r="O88">
-        <v>0.7511146666666666</v>
+        <v>0.7362826666666665</v>
       </c>
       <c r="P88">
-        <v>6.760031999999999</v>
+        <v>6.626543999999998</v>
       </c>
       <c r="Q88">
-        <v>20.160032</v>
+        <v>20.026544</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.510416327275835</v>
+        <v>0.5456086092610439</v>
       </c>
       <c r="T88">
-        <v>7.18746681725835</v>
+        <v>7.731880227082665</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.588854603079033</v>
+        <v>1.570591906491917</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1413991192039357</v>
+        <v>0.1416799525892545</v>
       </c>
       <c r="C89">
-        <v>-3.871903305967066</v>
+        <v>-5.902649103780192</v>
       </c>
       <c r="D89">
-        <v>130.6740966940329</v>
+        <v>130.2913508962198</v>
       </c>
       <c r="E89">
-        <v>33.176</v>
+        <v>34.824</v>
       </c>
       <c r="F89">
-        <v>143.376</v>
+        <v>145.024</v>
       </c>
       <c r="G89">
         <v>8.83</v>
@@ -8579,28 +8579,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M89">
-        <v>12.90384</v>
+        <v>13.05216</v>
       </c>
       <c r="N89">
-        <v>7.362826666666665</v>
+        <v>7.214506666666667</v>
       </c>
       <c r="O89">
-        <v>0.7362826666666665</v>
+        <v>0.7214506666666667</v>
       </c>
       <c r="P89">
-        <v>6.626543999999998</v>
+        <v>6.493056</v>
       </c>
       <c r="Q89">
-        <v>20.026544</v>
+        <v>19.893056</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5456086092610439</v>
+        <v>0.5866662715771209</v>
       </c>
       <c r="T89">
-        <v>7.731880227082665</v>
+        <v>8.367029205211034</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.570591906491917</v>
+        <v>1.552744271190873</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1416799525892545</v>
+        <v>0.1419607859745733</v>
       </c>
       <c r="C90">
-        <v>-5.902649103780192</v>
+        <v>-7.93115931674393</v>
       </c>
       <c r="D90">
-        <v>130.2913508962198</v>
+        <v>129.9108406832561</v>
       </c>
       <c r="E90">
-        <v>34.824</v>
+        <v>36.47200000000002</v>
       </c>
       <c r="F90">
-        <v>145.024</v>
+        <v>146.672</v>
       </c>
       <c r="G90">
         <v>8.83</v>
@@ -8661,28 +8661,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M90">
-        <v>13.05216</v>
+        <v>13.20048</v>
       </c>
       <c r="N90">
-        <v>7.214506666666667</v>
+        <v>7.066186666666663</v>
       </c>
       <c r="O90">
-        <v>0.7214506666666667</v>
+        <v>0.7066186666666664</v>
       </c>
       <c r="P90">
-        <v>6.493056</v>
+        <v>6.359567999999997</v>
       </c>
       <c r="Q90">
-        <v>19.893056</v>
+        <v>19.759568</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5866662715771209</v>
+        <v>0.6351889634052119</v>
       </c>
       <c r="T90">
-        <v>8.367029205211034</v>
+        <v>9.117659815726379</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.552744271190873</v>
+        <v>1.535297706346031</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1419607859745733</v>
+        <v>0.1422416193598921</v>
       </c>
       <c r="C91">
-        <v>-7.93115931674393</v>
+        <v>-9.957453474606893</v>
       </c>
       <c r="D91">
-        <v>129.9108406832561</v>
+        <v>129.5325465253931</v>
       </c>
       <c r="E91">
-        <v>36.47200000000002</v>
+        <v>38.12000000000002</v>
       </c>
       <c r="F91">
-        <v>146.672</v>
+        <v>148.32</v>
       </c>
       <c r="G91">
         <v>8.83</v>
@@ -8743,28 +8743,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M91">
-        <v>13.20048</v>
+        <v>13.3488</v>
       </c>
       <c r="N91">
-        <v>7.066186666666663</v>
+        <v>6.917866666666665</v>
       </c>
       <c r="O91">
-        <v>0.7066186666666664</v>
+        <v>0.6917866666666665</v>
       </c>
       <c r="P91">
-        <v>6.359567999999997</v>
+        <v>6.226079999999999</v>
       </c>
       <c r="Q91">
-        <v>19.759568</v>
+        <v>19.62608</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6351889634052119</v>
+        <v>0.6934161935989211</v>
       </c>
       <c r="T91">
-        <v>9.117659815726379</v>
+        <v>10.01841654834479</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.535297706346031</v>
+        <v>1.518238842942187</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1422416193598921</v>
+        <v>0.1425224527452109</v>
       </c>
       <c r="C92">
-        <v>-9.957453474606893</v>
+        <v>-11.98155088029941</v>
       </c>
       <c r="D92">
-        <v>129.5325465253931</v>
+        <v>129.1564491197006</v>
       </c>
       <c r="E92">
-        <v>38.12000000000002</v>
+        <v>39.76800000000001</v>
       </c>
       <c r="F92">
-        <v>148.32</v>
+        <v>149.968</v>
       </c>
       <c r="G92">
         <v>8.83</v>
@@ -8825,28 +8825,28 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M92">
-        <v>13.3488</v>
+        <v>13.49712</v>
       </c>
       <c r="N92">
-        <v>6.917866666666665</v>
+        <v>6.769546666666665</v>
       </c>
       <c r="O92">
-        <v>0.6917866666666665</v>
+        <v>0.6769546666666666</v>
       </c>
       <c r="P92">
-        <v>6.226079999999999</v>
+        <v>6.092591999999998</v>
       </c>
       <c r="Q92">
-        <v>19.62608</v>
+        <v>19.492592</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6934161935989211</v>
+        <v>0.7645828082801214</v>
       </c>
       <c r="T92">
-        <v>10.01841654834479</v>
+        <v>11.1193414437673</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.518238842942187</v>
+        <v>1.501554899613152</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1425224527452109</v>
+        <v>0.1916271079708715</v>
       </c>
       <c r="C93">
-        <v>-11.98155088029941</v>
+        <v>-57.12066163770605</v>
       </c>
       <c r="D93">
-        <v>129.1564491197006</v>
+        <v>85.66533836229397</v>
       </c>
       <c r="E93">
-        <v>39.76800000000001</v>
+        <v>41.41600000000001</v>
       </c>
       <c r="F93">
-        <v>149.968</v>
+        <v>151.616</v>
       </c>
       <c r="G93">
         <v>8.83</v>
@@ -8907,45 +8907,45 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M93">
-        <v>13.49712</v>
+        <v>22.2572288</v>
       </c>
       <c r="N93">
-        <v>6.769546666666665</v>
+        <v>-1.990562133333338</v>
       </c>
       <c r="O93">
-        <v>0.6769546666666666</v>
+        <v>-0.1990562133333338</v>
       </c>
       <c r="P93">
-        <v>6.092591999999998</v>
+        <v>-1.791505920000004</v>
       </c>
       <c r="Q93">
-        <v>19.492592</v>
+        <v>11.60849408</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7645828082801214</v>
+        <v>0.86086053248379</v>
       </c>
       <c r="T93">
-        <v>11.1193414437673</v>
+        <v>12.60872721721257</v>
       </c>
       <c r="U93">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1</v>
+        <v>0.09105655896688569</v>
       </c>
       <c r="W93">
-        <v>0.081</v>
+        <v>0.1334328971436612</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.501554899613152</v>
+        <v>0.9105655896688568</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1916271079708715</v>
+        <v>0.1926371079708715</v>
       </c>
       <c r="C94">
-        <v>-57.12066163770605</v>
+        <v>-59.35789955543379</v>
       </c>
       <c r="D94">
-        <v>85.66533836229397</v>
+        <v>85.07610044456622</v>
       </c>
       <c r="E94">
-        <v>41.41600000000001</v>
+        <v>43.06400000000001</v>
       </c>
       <c r="F94">
-        <v>151.616</v>
+        <v>153.264</v>
       </c>
       <c r="G94">
         <v>8.83</v>
@@ -8989,37 +8989,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M94">
-        <v>22.2572288</v>
+        <v>22.4991552</v>
       </c>
       <c r="N94">
-        <v>-1.990562133333338</v>
+        <v>-2.232488533333338</v>
       </c>
       <c r="O94">
-        <v>-0.1990562133333338</v>
+        <v>-0.2232488533333339</v>
       </c>
       <c r="P94">
-        <v>-1.791505920000004</v>
+        <v>-2.009239680000005</v>
       </c>
       <c r="Q94">
-        <v>11.60849408</v>
+        <v>11.39076031999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.86086053248379</v>
+        <v>0.977297751410046</v>
       </c>
       <c r="T94">
-        <v>12.60872721721257</v>
+        <v>14.40997396252865</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.09105655896688569</v>
+        <v>0.09007745618229551</v>
       </c>
       <c r="W94">
-        <v>0.1334328971436612</v>
+        <v>0.133576629432439</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9105655896688568</v>
+        <v>0.9007745618229551</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1926371079708715</v>
+        <v>0.1936471079708715</v>
       </c>
       <c r="C95">
-        <v>-59.35789955543379</v>
+        <v>-61.58708685512678</v>
       </c>
       <c r="D95">
-        <v>85.07610044456622</v>
+        <v>84.49491314487322</v>
       </c>
       <c r="E95">
-        <v>43.06400000000001</v>
+        <v>44.712</v>
       </c>
       <c r="F95">
-        <v>153.264</v>
+        <v>154.912</v>
       </c>
       <c r="G95">
         <v>8.83</v>
@@ -9071,37 +9071,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M95">
-        <v>22.4991552</v>
+        <v>22.7410816</v>
       </c>
       <c r="N95">
-        <v>-2.232488533333338</v>
+        <v>-2.474414933333339</v>
       </c>
       <c r="O95">
-        <v>-0.2232488533333339</v>
+        <v>-0.2474414933333339</v>
       </c>
       <c r="P95">
-        <v>-2.009239680000005</v>
+        <v>-2.226973440000005</v>
       </c>
       <c r="Q95">
-        <v>11.39076031999999</v>
+        <v>11.17302655999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.977297751410046</v>
+        <v>1.132547376645054</v>
       </c>
       <c r="T95">
-        <v>14.40997396252865</v>
+        <v>16.81163628961676</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.09007745618229551</v>
+        <v>0.08911918537184556</v>
       </c>
       <c r="W95">
-        <v>0.133576629432439</v>
+        <v>0.1337173035874131</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9007745618229551</v>
+        <v>0.8911918537184556</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1936471079708715</v>
+        <v>0.1946571079708715</v>
       </c>
       <c r="C96">
-        <v>-61.58708685512678</v>
+        <v>-63.80838740784897</v>
       </c>
       <c r="D96">
-        <v>84.49491314487322</v>
+        <v>83.92161259215106</v>
       </c>
       <c r="E96">
-        <v>44.712</v>
+        <v>46.36000000000003</v>
       </c>
       <c r="F96">
-        <v>154.912</v>
+        <v>156.56</v>
       </c>
       <c r="G96">
         <v>8.83</v>
@@ -9153,37 +9153,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M96">
-        <v>22.7410816</v>
+        <v>22.98300800000001</v>
       </c>
       <c r="N96">
-        <v>-2.474414933333339</v>
+        <v>-2.716341333333339</v>
       </c>
       <c r="O96">
-        <v>-0.2474414933333339</v>
+        <v>-0.271634133333334</v>
       </c>
       <c r="P96">
-        <v>-2.226973440000005</v>
+        <v>-2.444707200000006</v>
       </c>
       <c r="Q96">
-        <v>11.17302655999999</v>
+        <v>10.9552928</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.132547376645054</v>
+        <v>1.349896851974065</v>
       </c>
       <c r="T96">
-        <v>16.81163628961676</v>
+        <v>20.17396354754012</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.08911918537184556</v>
+        <v>0.08818108868372088</v>
       </c>
       <c r="W96">
-        <v>0.1337173035874131</v>
+        <v>0.1338550161812298</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8911918537184556</v>
+        <v>0.8818108868372087</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1946571079708715</v>
+        <v>0.1956671079708714</v>
       </c>
       <c r="C97">
-        <v>-63.80838740784897</v>
+        <v>-66.02196066715645</v>
       </c>
       <c r="D97">
-        <v>83.92161259215106</v>
+        <v>83.35603933284358</v>
       </c>
       <c r="E97">
-        <v>46.36000000000003</v>
+        <v>48.00800000000002</v>
       </c>
       <c r="F97">
-        <v>156.56</v>
+        <v>158.208</v>
       </c>
       <c r="G97">
         <v>8.83</v>
@@ -9235,37 +9235,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M97">
-        <v>22.98300800000001</v>
+        <v>23.22493440000001</v>
       </c>
       <c r="N97">
-        <v>-2.716341333333339</v>
+        <v>-2.95826773333334</v>
       </c>
       <c r="O97">
-        <v>-0.271634133333334</v>
+        <v>-0.295826773333334</v>
       </c>
       <c r="P97">
-        <v>-2.444707200000006</v>
+        <v>-2.662440960000006</v>
       </c>
       <c r="Q97">
-        <v>10.9552928</v>
+        <v>10.73755903999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.349896851974065</v>
+        <v>1.675921064967582</v>
       </c>
       <c r="T97">
-        <v>20.17396354754012</v>
+        <v>25.21745443442516</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.08818108868372088</v>
+        <v>0.08726253567659878</v>
       </c>
       <c r="W97">
-        <v>0.1338550161812298</v>
+        <v>0.1339898597626753</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8818108868372087</v>
+        <v>0.8726253567659877</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1956671079708715</v>
+        <v>0.1966771079708715</v>
       </c>
       <c r="C98">
-        <v>-66.02196066715642</v>
+        <v>-68.22796181695593</v>
       </c>
       <c r="D98">
-        <v>83.35603933284358</v>
+        <v>82.79803818304407</v>
       </c>
       <c r="E98">
-        <v>48.008</v>
+        <v>49.65599999999999</v>
       </c>
       <c r="F98">
-        <v>158.208</v>
+        <v>159.856</v>
       </c>
       <c r="G98">
         <v>8.83</v>
@@ -9317,37 +9317,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M98">
-        <v>23.2249344</v>
+        <v>23.4668608</v>
       </c>
       <c r="N98">
-        <v>-2.958267733333336</v>
+        <v>-3.200194133333337</v>
       </c>
       <c r="O98">
-        <v>-0.2958267733333337</v>
+        <v>-0.3200194133333337</v>
       </c>
       <c r="P98">
-        <v>-2.662440960000003</v>
+        <v>-2.880174720000003</v>
       </c>
       <c r="Q98">
-        <v>10.73755904</v>
+        <v>10.51982528</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.675921064967578</v>
+        <v>2.219294753290104</v>
       </c>
       <c r="T98">
-        <v>25.2174544344251</v>
+        <v>33.62327257923346</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.08726253567659879</v>
+        <v>0.08636292190673694</v>
       </c>
       <c r="W98">
-        <v>0.1339898597626753</v>
+        <v>0.134121923064091</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8726253567659878</v>
+        <v>0.8636292190673693</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1966771079708715</v>
+        <v>0.1976871079708715</v>
       </c>
       <c r="C99">
-        <v>-68.22796181695593</v>
+        <v>-70.42654191346362</v>
       </c>
       <c r="D99">
-        <v>82.79803818304407</v>
+        <v>82.2474580865364</v>
       </c>
       <c r="E99">
-        <v>49.65599999999999</v>
+        <v>51.30400000000002</v>
       </c>
       <c r="F99">
-        <v>159.856</v>
+        <v>161.504</v>
       </c>
       <c r="G99">
         <v>8.83</v>
@@ -9399,37 +9399,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M99">
-        <v>23.4668608</v>
+        <v>23.7087872</v>
       </c>
       <c r="N99">
-        <v>-3.200194133333337</v>
+        <v>-3.442120533333338</v>
       </c>
       <c r="O99">
-        <v>-0.3200194133333337</v>
+        <v>-0.3442120533333338</v>
       </c>
       <c r="P99">
-        <v>-2.880174720000003</v>
+        <v>-3.097908480000004</v>
       </c>
       <c r="Q99">
-        <v>10.51982528</v>
+        <v>10.30209152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.219294753290104</v>
+        <v>3.306042129935156</v>
       </c>
       <c r="T99">
-        <v>33.62327257923346</v>
+        <v>50.43490886885019</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.08636292190673694</v>
+        <v>0.08548166760156616</v>
       </c>
       <c r="W99">
-        <v>0.134121923064091</v>
+        <v>0.1342512911960901</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8636292190673693</v>
+        <v>0.8548166760156615</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1976871079708715</v>
+        <v>0.1986971079708715</v>
       </c>
       <c r="C100">
-        <v>-70.42654191346362</v>
+        <v>-72.61784802153747</v>
       </c>
       <c r="D100">
-        <v>82.2474580865364</v>
+        <v>81.70415197846255</v>
       </c>
       <c r="E100">
-        <v>51.30400000000002</v>
+        <v>52.95200000000001</v>
       </c>
       <c r="F100">
-        <v>161.504</v>
+        <v>163.152</v>
       </c>
       <c r="G100">
         <v>8.83</v>
@@ -9481,37 +9481,37 @@
         <v>20.26666666666667</v>
       </c>
       <c r="M100">
-        <v>23.7087872</v>
+        <v>23.9507136</v>
       </c>
       <c r="N100">
-        <v>-3.442120533333338</v>
+        <v>-3.684046933333338</v>
       </c>
       <c r="O100">
-        <v>-0.3442120533333338</v>
+        <v>-0.3684046933333338</v>
       </c>
       <c r="P100">
-        <v>-3.097908480000004</v>
+        <v>-3.315642240000004</v>
       </c>
       <c r="Q100">
-        <v>10.30209152</v>
+        <v>10.08435776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.306042129935156</v>
+        <v>6.566284259870312</v>
       </c>
       <c r="T100">
-        <v>50.43490886885019</v>
+        <v>100.8698177377004</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.08548166760156616</v>
+        <v>0.08461821641367155</v>
       </c>
       <c r="W100">
-        <v>0.1342512911960901</v>
+        <v>0.134378045830473</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8548166760156615</v>
+        <v>0.8461821641367154</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1986971079708715</v>
-      </c>
-      <c r="C101">
-        <v>-72.61784802153747</v>
-      </c>
-      <c r="D101">
-        <v>81.70415197846255</v>
-      </c>
-      <c r="E101">
-        <v>52.95200000000001</v>
-      </c>
-      <c r="F101">
-        <v>163.152</v>
-      </c>
-      <c r="G101">
-        <v>8.83</v>
-      </c>
-      <c r="H101">
-        <v>54.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.66666666666666</v>
-      </c>
-      <c r="K101">
-        <v>13.4</v>
-      </c>
-      <c r="L101">
-        <v>20.26666666666667</v>
-      </c>
-      <c r="M101">
-        <v>23.9507136</v>
-      </c>
-      <c r="N101">
-        <v>-3.684046933333338</v>
-      </c>
-      <c r="O101">
-        <v>-0.3684046933333338</v>
-      </c>
-      <c r="P101">
-        <v>-3.315642240000004</v>
-      </c>
-      <c r="Q101">
-        <v>10.08435776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.566284259870312</v>
-      </c>
-      <c r="T101">
-        <v>100.8698177377004</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.08461821641367155</v>
-      </c>
-      <c r="W101">
-        <v>0.134378045830473</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8461821641367154</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
